--- a/GBDS FEBRUARY FILES 2026/DSSR GBDS MONTH OF FEBRUARY 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/DSSR GBDS MONTH OF FEBRUARY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB28A1C1-12DE-4D66-B899-3D8E3AA72377}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D618D7C-1FEB-41AF-A8F1-846D8D65B12D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,6 +27,7 @@
     <sheet name="02,12" sheetId="81" r:id="rId12"/>
     <sheet name="02,13" sheetId="70" r:id="rId13"/>
     <sheet name="02,14" sheetId="82" r:id="rId14"/>
+    <sheet name="02,16" sheetId="83" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'02,02'!$A$1:$W$61</definedName>
@@ -42,6 +43,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="11">'02,12'!$A$1:$W$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="12">'02,13'!$A$1:$W$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'02,14'!$A$1:$W$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'02,16'!$A$1:$W$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$Q$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -60,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1435" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="79">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -1183,7 +1185,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="169">
+  <cellXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1577,6 +1579,15 @@
     </xf>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="62" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2044,11 +2055,11 @@
       <c r="J1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="153"/>
-      <c r="L1" s="154"/>
-      <c r="M1" s="154"/>
-      <c r="N1" s="154"/>
-      <c r="O1" s="155"/>
+      <c r="K1" s="156"/>
+      <c r="L1" s="157"/>
+      <c r="M1" s="157"/>
+      <c r="N1" s="157"/>
+      <c r="O1" s="158"/>
     </row>
     <row r="2" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -2067,44 +2078,44 @@
     <row r="3" spans="1:51" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:51" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="147" t="s">
+      <c r="B4" s="150" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="156" t="s">
+      <c r="C4" s="159" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="157" t="s">
+      <c r="D4" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="158"/>
-      <c r="F4" s="159" t="s">
+      <c r="E4" s="161"/>
+      <c r="F4" s="162" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="161" t="s">
+      <c r="G4" s="164" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="163" t="s">
+      <c r="I4" s="166" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="164"/>
-      <c r="K4" s="164"/>
-      <c r="L4" s="164"/>
-      <c r="M4" s="164"/>
-      <c r="N4" s="164"/>
-      <c r="O4" s="165"/>
+      <c r="J4" s="167"/>
+      <c r="K4" s="167"/>
+      <c r="L4" s="167"/>
+      <c r="M4" s="167"/>
+      <c r="N4" s="167"/>
+      <c r="O4" s="168"/>
     </row>
     <row r="5" spans="1:51" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53"/>
-      <c r="B5" s="147"/>
-      <c r="C5" s="156"/>
+      <c r="B5" s="150"/>
+      <c r="C5" s="159"/>
       <c r="D5" s="52" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="160"/>
-      <c r="G5" s="162"/>
+      <c r="F5" s="163"/>
+      <c r="G5" s="165"/>
       <c r="I5" s="4" t="s">
         <v>10</v>
       </c>
@@ -3785,7 +3796,7 @@
     </row>
     <row r="59" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="60" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F60" s="148" t="s">
+      <c r="F60" s="151" t="s">
         <v>65</v>
       </c>
       <c r="G60" s="24" t="s">
@@ -3797,7 +3808,7 @@
       <c r="L60" s="35"/>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F61" s="149"/>
+      <c r="F61" s="152"/>
       <c r="G61" s="25" t="s">
         <v>51</v>
       </c>
@@ -3807,7 +3818,7 @@
       <c r="L61" s="38"/>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F62" s="150"/>
+      <c r="F62" s="153"/>
       <c r="G62" s="25" t="s">
         <v>52</v>
       </c>
@@ -3817,7 +3828,7 @@
       <c r="L62" s="41"/>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F63" s="151" t="s">
+      <c r="F63" s="154" t="s">
         <v>64</v>
       </c>
       <c r="G63" s="25" t="s">
@@ -3829,7 +3840,7 @@
       <c r="L63" s="41"/>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F64" s="151"/>
+      <c r="F64" s="154"/>
       <c r="G64" s="25" t="s">
         <v>51</v>
       </c>
@@ -3839,7 +3850,7 @@
       <c r="L64" s="38"/>
     </row>
     <row r="65" spans="2:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F65" s="152"/>
+      <c r="F65" s="155"/>
       <c r="G65" s="26" t="s">
         <v>52</v>
       </c>
@@ -4137,15 +4148,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="153">
+      <c r="P1" s="156">
         <v>46063</v>
       </c>
-      <c r="Q1" s="154"/>
-      <c r="R1" s="154"/>
-      <c r="S1" s="154"/>
-      <c r="T1" s="154"/>
-      <c r="U1" s="154"/>
-      <c r="V1" s="155"/>
+      <c r="Q1" s="157"/>
+      <c r="R1" s="157"/>
+      <c r="S1" s="157"/>
+      <c r="T1" s="157"/>
+      <c r="U1" s="157"/>
+      <c r="V1" s="158"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -4168,60 +4179,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="147" t="s">
+      <c r="B4" s="150" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="156" t="s">
+      <c r="C4" s="159" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="166" t="s">
+      <c r="D4" s="169" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="157" t="s">
+      <c r="E4" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="158"/>
-      <c r="G4" s="159" t="s">
+      <c r="F4" s="161"/>
+      <c r="G4" s="162" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="167" t="s">
+      <c r="H4" s="170" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="161" t="s">
+      <c r="I4" s="164" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="167" t="s">
+      <c r="J4" s="170" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="163" t="s">
+      <c r="L4" s="166" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="164"/>
-      <c r="N4" s="164"/>
-      <c r="O4" s="164"/>
-      <c r="P4" s="164"/>
-      <c r="Q4" s="164"/>
-      <c r="R4" s="164"/>
-      <c r="S4" s="164"/>
-      <c r="T4" s="164"/>
-      <c r="U4" s="164"/>
-      <c r="V4" s="165"/>
+      <c r="M4" s="167"/>
+      <c r="N4" s="167"/>
+      <c r="O4" s="167"/>
+      <c r="P4" s="167"/>
+      <c r="Q4" s="167"/>
+      <c r="R4" s="167"/>
+      <c r="S4" s="167"/>
+      <c r="T4" s="167"/>
+      <c r="U4" s="167"/>
+      <c r="V4" s="168"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53"/>
-      <c r="B5" s="147"/>
-      <c r="C5" s="156"/>
-      <c r="D5" s="166"/>
+      <c r="B5" s="150"/>
+      <c r="C5" s="159"/>
+      <c r="D5" s="169"/>
       <c r="E5" s="52" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="160"/>
-      <c r="H5" s="168"/>
-      <c r="I5" s="162"/>
-      <c r="J5" s="168"/>
+      <c r="G5" s="163"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="165"/>
+      <c r="J5" s="171"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -7148,7 +7159,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="148" t="s">
+      <c r="G62" s="151" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="74"/>
@@ -7166,7 +7177,7 @@
       <c r="S62" s="35"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="149"/>
+      <c r="G63" s="152"/>
       <c r="H63" s="75"/>
       <c r="I63" s="75"/>
       <c r="J63" s="25" t="s">
@@ -7182,7 +7193,7 @@
       <c r="S63" s="38"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="150"/>
+      <c r="G64" s="153"/>
       <c r="H64" s="76"/>
       <c r="I64" s="76"/>
       <c r="J64" s="25" t="s">
@@ -7198,7 +7209,7 @@
       <c r="S64" s="41"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="151" t="s">
+      <c r="G65" s="154" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="77"/>
@@ -7216,7 +7227,7 @@
       <c r="S65" s="41"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="151"/>
+      <c r="G66" s="154"/>
       <c r="H66" s="77"/>
       <c r="I66" s="77"/>
       <c r="J66" s="25" t="s">
@@ -7232,7 +7243,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="152"/>
+      <c r="G67" s="155"/>
       <c r="H67" s="78"/>
       <c r="I67" s="78"/>
       <c r="J67" s="26" t="s">
@@ -7624,15 +7635,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="153">
+      <c r="P1" s="156">
         <v>46064</v>
       </c>
-      <c r="Q1" s="154"/>
-      <c r="R1" s="154"/>
-      <c r="S1" s="154"/>
-      <c r="T1" s="154"/>
-      <c r="U1" s="154"/>
-      <c r="V1" s="155"/>
+      <c r="Q1" s="157"/>
+      <c r="R1" s="157"/>
+      <c r="S1" s="157"/>
+      <c r="T1" s="157"/>
+      <c r="U1" s="157"/>
+      <c r="V1" s="158"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -7655,60 +7666,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="147" t="s">
+      <c r="B4" s="150" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="156" t="s">
+      <c r="C4" s="159" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="166" t="s">
+      <c r="D4" s="169" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="157" t="s">
+      <c r="E4" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="158"/>
-      <c r="G4" s="159" t="s">
+      <c r="F4" s="161"/>
+      <c r="G4" s="162" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="167" t="s">
+      <c r="H4" s="170" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="161" t="s">
+      <c r="I4" s="164" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="167" t="s">
+      <c r="J4" s="170" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="163" t="s">
+      <c r="L4" s="166" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="164"/>
-      <c r="N4" s="164"/>
-      <c r="O4" s="164"/>
-      <c r="P4" s="164"/>
-      <c r="Q4" s="164"/>
-      <c r="R4" s="164"/>
-      <c r="S4" s="164"/>
-      <c r="T4" s="164"/>
-      <c r="U4" s="164"/>
-      <c r="V4" s="165"/>
+      <c r="M4" s="167"/>
+      <c r="N4" s="167"/>
+      <c r="O4" s="167"/>
+      <c r="P4" s="167"/>
+      <c r="Q4" s="167"/>
+      <c r="R4" s="167"/>
+      <c r="S4" s="167"/>
+      <c r="T4" s="167"/>
+      <c r="U4" s="167"/>
+      <c r="V4" s="168"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53"/>
-      <c r="B5" s="147"/>
-      <c r="C5" s="156"/>
-      <c r="D5" s="166"/>
+      <c r="B5" s="150"/>
+      <c r="C5" s="159"/>
+      <c r="D5" s="169"/>
       <c r="E5" s="52" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="146" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="160"/>
-      <c r="H5" s="168"/>
-      <c r="I5" s="162"/>
-      <c r="J5" s="168"/>
+      <c r="G5" s="163"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="165"/>
+      <c r="J5" s="171"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -10637,7 +10648,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="148" t="s">
+      <c r="G62" s="151" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="74"/>
@@ -10655,7 +10666,7 @@
       <c r="S62" s="35"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="149"/>
+      <c r="G63" s="152"/>
       <c r="H63" s="75"/>
       <c r="I63" s="75"/>
       <c r="J63" s="25" t="s">
@@ -10671,7 +10682,7 @@
       <c r="S63" s="38"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="150"/>
+      <c r="G64" s="153"/>
       <c r="H64" s="76"/>
       <c r="I64" s="76"/>
       <c r="J64" s="25" t="s">
@@ -10687,7 +10698,7 @@
       <c r="S64" s="41"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="151" t="s">
+      <c r="G65" s="154" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="77"/>
@@ -10705,7 +10716,7 @@
       <c r="S65" s="41"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="151"/>
+      <c r="G66" s="154"/>
       <c r="H66" s="77"/>
       <c r="I66" s="77"/>
       <c r="J66" s="25" t="s">
@@ -10721,7 +10732,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="152"/>
+      <c r="G67" s="155"/>
       <c r="H67" s="78"/>
       <c r="I67" s="78"/>
       <c r="J67" s="26" t="s">
@@ -11113,15 +11124,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="153">
+      <c r="P1" s="156">
         <v>46065</v>
       </c>
-      <c r="Q1" s="154"/>
-      <c r="R1" s="154"/>
-      <c r="S1" s="154"/>
-      <c r="T1" s="154"/>
-      <c r="U1" s="154"/>
-      <c r="V1" s="155"/>
+      <c r="Q1" s="157"/>
+      <c r="R1" s="157"/>
+      <c r="S1" s="157"/>
+      <c r="T1" s="157"/>
+      <c r="U1" s="157"/>
+      <c r="V1" s="158"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -11144,60 +11155,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="147" t="s">
+      <c r="B4" s="150" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="156" t="s">
+      <c r="C4" s="159" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="166" t="s">
+      <c r="D4" s="169" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="157" t="s">
+      <c r="E4" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="158"/>
-      <c r="G4" s="159" t="s">
+      <c r="F4" s="161"/>
+      <c r="G4" s="162" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="167" t="s">
+      <c r="H4" s="170" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="161" t="s">
+      <c r="I4" s="164" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="167" t="s">
+      <c r="J4" s="170" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="163" t="s">
+      <c r="L4" s="166" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="164"/>
-      <c r="N4" s="164"/>
-      <c r="O4" s="164"/>
-      <c r="P4" s="164"/>
-      <c r="Q4" s="164"/>
-      <c r="R4" s="164"/>
-      <c r="S4" s="164"/>
-      <c r="T4" s="164"/>
-      <c r="U4" s="164"/>
-      <c r="V4" s="165"/>
+      <c r="M4" s="167"/>
+      <c r="N4" s="167"/>
+      <c r="O4" s="167"/>
+      <c r="P4" s="167"/>
+      <c r="Q4" s="167"/>
+      <c r="R4" s="167"/>
+      <c r="S4" s="167"/>
+      <c r="T4" s="167"/>
+      <c r="U4" s="167"/>
+      <c r="V4" s="168"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53"/>
-      <c r="B5" s="147"/>
-      <c r="C5" s="156"/>
-      <c r="D5" s="166"/>
+      <c r="B5" s="150"/>
+      <c r="C5" s="159"/>
+      <c r="D5" s="169"/>
       <c r="E5" s="52" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="146" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="160"/>
-      <c r="H5" s="168"/>
-      <c r="I5" s="162"/>
-      <c r="J5" s="168"/>
+      <c r="G5" s="163"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="165"/>
+      <c r="J5" s="171"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -14108,7 +14119,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="148" t="s">
+      <c r="G62" s="151" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="74"/>
@@ -14126,7 +14137,7 @@
       <c r="S62" s="35"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="149"/>
+      <c r="G63" s="152"/>
       <c r="H63" s="75"/>
       <c r="I63" s="75"/>
       <c r="J63" s="25" t="s">
@@ -14142,7 +14153,7 @@
       <c r="S63" s="38"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="150"/>
+      <c r="G64" s="153"/>
       <c r="H64" s="76"/>
       <c r="I64" s="76"/>
       <c r="J64" s="25" t="s">
@@ -14158,7 +14169,7 @@
       <c r="S64" s="41"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="151" t="s">
+      <c r="G65" s="154" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="77"/>
@@ -14176,7 +14187,7 @@
       <c r="S65" s="41"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="151"/>
+      <c r="G66" s="154"/>
       <c r="H66" s="77"/>
       <c r="I66" s="77"/>
       <c r="J66" s="25" t="s">
@@ -14192,7 +14203,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="152"/>
+      <c r="G67" s="155"/>
       <c r="H67" s="78"/>
       <c r="I67" s="78"/>
       <c r="J67" s="26" t="s">
@@ -14584,15 +14595,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="153">
+      <c r="P1" s="156">
         <v>46066</v>
       </c>
-      <c r="Q1" s="154"/>
-      <c r="R1" s="154"/>
-      <c r="S1" s="154"/>
-      <c r="T1" s="154"/>
-      <c r="U1" s="154"/>
-      <c r="V1" s="155"/>
+      <c r="Q1" s="157"/>
+      <c r="R1" s="157"/>
+      <c r="S1" s="157"/>
+      <c r="T1" s="157"/>
+      <c r="U1" s="157"/>
+      <c r="V1" s="158"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -14615,60 +14626,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="147" t="s">
+      <c r="B4" s="150" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="156" t="s">
+      <c r="C4" s="159" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="166" t="s">
+      <c r="D4" s="169" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="157" t="s">
+      <c r="E4" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="158"/>
-      <c r="G4" s="159" t="s">
+      <c r="F4" s="161"/>
+      <c r="G4" s="162" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="167" t="s">
+      <c r="H4" s="170" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="161" t="s">
+      <c r="I4" s="164" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="167" t="s">
+      <c r="J4" s="170" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="163" t="s">
+      <c r="L4" s="166" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="164"/>
-      <c r="N4" s="164"/>
-      <c r="O4" s="164"/>
-      <c r="P4" s="164"/>
-      <c r="Q4" s="164"/>
-      <c r="R4" s="164"/>
-      <c r="S4" s="164"/>
-      <c r="T4" s="164"/>
-      <c r="U4" s="164"/>
-      <c r="V4" s="165"/>
+      <c r="M4" s="167"/>
+      <c r="N4" s="167"/>
+      <c r="O4" s="167"/>
+      <c r="P4" s="167"/>
+      <c r="Q4" s="167"/>
+      <c r="R4" s="167"/>
+      <c r="S4" s="167"/>
+      <c r="T4" s="167"/>
+      <c r="U4" s="167"/>
+      <c r="V4" s="168"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53"/>
-      <c r="B5" s="147"/>
-      <c r="C5" s="156"/>
-      <c r="D5" s="166"/>
+      <c r="B5" s="150"/>
+      <c r="C5" s="159"/>
+      <c r="D5" s="169"/>
       <c r="E5" s="52" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="115" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="160"/>
-      <c r="H5" s="168"/>
-      <c r="I5" s="162"/>
-      <c r="J5" s="168"/>
+      <c r="G5" s="163"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="165"/>
+      <c r="J5" s="171"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -17566,7 +17577,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="148" t="s">
+      <c r="G62" s="151" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="74"/>
@@ -17584,7 +17595,7 @@
       <c r="S62" s="35"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="149"/>
+      <c r="G63" s="152"/>
       <c r="H63" s="75"/>
       <c r="I63" s="75"/>
       <c r="J63" s="25" t="s">
@@ -17600,7 +17611,7 @@
       <c r="S63" s="38"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="150"/>
+      <c r="G64" s="153"/>
       <c r="H64" s="76"/>
       <c r="I64" s="76"/>
       <c r="J64" s="25" t="s">
@@ -17616,7 +17627,7 @@
       <c r="S64" s="41"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="151" t="s">
+      <c r="G65" s="154" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="77"/>
@@ -17634,7 +17645,7 @@
       <c r="S65" s="41"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="151"/>
+      <c r="G66" s="154"/>
       <c r="H66" s="77"/>
       <c r="I66" s="77"/>
       <c r="J66" s="25" t="s">
@@ -17650,7 +17661,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="152"/>
+      <c r="G67" s="155"/>
       <c r="H67" s="78"/>
       <c r="I67" s="78"/>
       <c r="J67" s="26" t="s">
@@ -18042,15 +18053,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="153">
+      <c r="P1" s="156">
         <v>46067</v>
       </c>
-      <c r="Q1" s="154"/>
-      <c r="R1" s="154"/>
-      <c r="S1" s="154"/>
-      <c r="T1" s="154"/>
-      <c r="U1" s="154"/>
-      <c r="V1" s="155"/>
+      <c r="Q1" s="157"/>
+      <c r="R1" s="157"/>
+      <c r="S1" s="157"/>
+      <c r="T1" s="157"/>
+      <c r="U1" s="157"/>
+      <c r="V1" s="158"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -18073,60 +18084,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="147" t="s">
+      <c r="B4" s="150" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="156" t="s">
+      <c r="C4" s="159" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="166" t="s">
+      <c r="D4" s="169" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="157" t="s">
+      <c r="E4" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="158"/>
-      <c r="G4" s="159" t="s">
+      <c r="F4" s="161"/>
+      <c r="G4" s="162" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="167" t="s">
+      <c r="H4" s="170" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="161" t="s">
+      <c r="I4" s="164" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="167" t="s">
+      <c r="J4" s="170" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="163" t="s">
+      <c r="L4" s="166" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="164"/>
-      <c r="N4" s="164"/>
-      <c r="O4" s="164"/>
-      <c r="P4" s="164"/>
-      <c r="Q4" s="164"/>
-      <c r="R4" s="164"/>
-      <c r="S4" s="164"/>
-      <c r="T4" s="164"/>
-      <c r="U4" s="164"/>
-      <c r="V4" s="165"/>
+      <c r="M4" s="167"/>
+      <c r="N4" s="167"/>
+      <c r="O4" s="167"/>
+      <c r="P4" s="167"/>
+      <c r="Q4" s="167"/>
+      <c r="R4" s="167"/>
+      <c r="S4" s="167"/>
+      <c r="T4" s="167"/>
+      <c r="U4" s="167"/>
+      <c r="V4" s="168"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53"/>
-      <c r="B5" s="147"/>
-      <c r="C5" s="156"/>
-      <c r="D5" s="166"/>
+      <c r="B5" s="150"/>
+      <c r="C5" s="159"/>
+      <c r="D5" s="169"/>
       <c r="E5" s="52" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="146" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="160"/>
-      <c r="H5" s="168"/>
-      <c r="I5" s="162"/>
-      <c r="J5" s="168"/>
+      <c r="G5" s="163"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="165"/>
+      <c r="J5" s="171"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -20926,7 +20937,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="148" t="s">
+      <c r="G62" s="151" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="74"/>
@@ -20944,7 +20955,7 @@
       <c r="S62" s="35"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="149"/>
+      <c r="G63" s="152"/>
       <c r="H63" s="75"/>
       <c r="I63" s="75"/>
       <c r="J63" s="25" t="s">
@@ -20960,7 +20971,7 @@
       <c r="S63" s="38"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="150"/>
+      <c r="G64" s="153"/>
       <c r="H64" s="76"/>
       <c r="I64" s="76"/>
       <c r="J64" s="25" t="s">
@@ -20976,7 +20987,7 @@
       <c r="S64" s="41"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="151" t="s">
+      <c r="G65" s="154" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="77"/>
@@ -20994,7 +21005,7 @@
       <c r="S65" s="41"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="151"/>
+      <c r="G66" s="154"/>
       <c r="H66" s="77"/>
       <c r="I66" s="77"/>
       <c r="J66" s="25" t="s">
@@ -21010,7 +21021,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="152"/>
+      <c r="G67" s="155"/>
       <c r="H67" s="78"/>
       <c r="I67" s="78"/>
       <c r="J67" s="26" t="s">
@@ -21054,6 +21065,3366 @@
         <v>55</v>
       </c>
       <c r="V69" s="144" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B70" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="23"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="11"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="11"/>
+      <c r="V70" s="23"/>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="23"/>
+      <c r="L71" s="23"/>
+      <c r="M71" s="23"/>
+      <c r="N71" s="23"/>
+      <c r="O71" s="23"/>
+      <c r="P71" s="23"/>
+      <c r="Q71" s="23"/>
+      <c r="R71" s="23"/>
+      <c r="S71" s="23"/>
+      <c r="V71" s="23"/>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B72" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="23"/>
+      <c r="L72" s="23"/>
+      <c r="M72" s="23"/>
+      <c r="N72" s="23"/>
+      <c r="O72" s="23"/>
+      <c r="P72" s="23"/>
+      <c r="Q72" s="23"/>
+      <c r="R72" s="23"/>
+      <c r="S72" s="23"/>
+      <c r="V72" s="23"/>
+    </row>
+    <row r="73" spans="2:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B74" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" s="23"/>
+      <c r="D74" s="23"/>
+      <c r="E74" s="23"/>
+      <c r="L74" s="23"/>
+      <c r="M74" s="23"/>
+      <c r="N74" s="23"/>
+      <c r="O74" s="23"/>
+      <c r="P74" s="23"/>
+      <c r="Q74" s="23"/>
+      <c r="R74" s="23"/>
+      <c r="S74" s="23"/>
+      <c r="V74" s="23"/>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="23"/>
+      <c r="D75" s="23"/>
+      <c r="E75" s="23"/>
+      <c r="L75" s="23"/>
+      <c r="M75" s="23"/>
+      <c r="N75" s="23"/>
+      <c r="O75" s="23"/>
+      <c r="P75" s="23"/>
+      <c r="Q75" s="23"/>
+      <c r="R75" s="23"/>
+      <c r="S75" s="23"/>
+      <c r="V75" s="23"/>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B76" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="23"/>
+      <c r="D76" s="23"/>
+      <c r="E76" s="23"/>
+      <c r="L76" s="23"/>
+      <c r="M76" s="23"/>
+      <c r="N76" s="23"/>
+      <c r="O76" s="23"/>
+      <c r="P76" s="23"/>
+      <c r="Q76" s="23"/>
+      <c r="R76" s="23"/>
+      <c r="S76" s="23"/>
+      <c r="V76" s="23"/>
+    </row>
+    <row r="77" spans="2:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B78" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" s="23"/>
+      <c r="D78" s="23"/>
+      <c r="E78" s="23"/>
+      <c r="L78" s="23"/>
+      <c r="M78" s="23"/>
+      <c r="N78" s="23"/>
+      <c r="O78" s="23"/>
+      <c r="P78" s="23"/>
+      <c r="Q78" s="23"/>
+      <c r="R78" s="23"/>
+      <c r="S78" s="23"/>
+      <c r="V78" s="23"/>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B79" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="23"/>
+      <c r="D79" s="23"/>
+      <c r="E79" s="23"/>
+      <c r="L79" s="23"/>
+      <c r="M79" s="23"/>
+      <c r="N79" s="23"/>
+      <c r="O79" s="23"/>
+      <c r="P79" s="23"/>
+      <c r="Q79" s="23"/>
+      <c r="R79" s="23"/>
+      <c r="S79" s="23"/>
+      <c r="V79" s="23"/>
+    </row>
+    <row r="80" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B80" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80" s="23"/>
+      <c r="D80" s="23"/>
+      <c r="E80" s="23"/>
+      <c r="L80" s="23"/>
+      <c r="M80" s="23"/>
+      <c r="N80" s="23"/>
+      <c r="O80" s="23"/>
+      <c r="P80" s="23"/>
+      <c r="Q80" s="23"/>
+      <c r="R80" s="23"/>
+      <c r="S80" s="23"/>
+      <c r="V80" s="23"/>
+    </row>
+    <row r="81" spans="2:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B82" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="23"/>
+      <c r="D82" s="23"/>
+      <c r="E82" s="23"/>
+      <c r="L82" s="23"/>
+      <c r="M82" s="23"/>
+      <c r="N82" s="23"/>
+      <c r="O82" s="23"/>
+      <c r="P82" s="23"/>
+      <c r="Q82" s="23"/>
+      <c r="R82" s="23"/>
+      <c r="S82" s="23"/>
+      <c r="V82" s="23"/>
+    </row>
+    <row r="83" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B83" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" s="23"/>
+      <c r="D83" s="23"/>
+      <c r="E83" s="23"/>
+      <c r="L83" s="23"/>
+      <c r="M83" s="23"/>
+      <c r="N83" s="23"/>
+      <c r="O83" s="23"/>
+      <c r="P83" s="23"/>
+      <c r="Q83" s="23"/>
+      <c r="R83" s="23"/>
+      <c r="S83" s="23"/>
+      <c r="V83" s="23"/>
+    </row>
+    <row r="84" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B84" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="23"/>
+      <c r="L84" s="23"/>
+      <c r="M84" s="23"/>
+      <c r="N84" s="23"/>
+      <c r="O84" s="23"/>
+      <c r="P84" s="23"/>
+      <c r="Q84" s="23"/>
+      <c r="R84" s="23"/>
+      <c r="S84" s="23"/>
+      <c r="V84" s="23"/>
+    </row>
+    <row r="85" spans="2:22" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B86" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" s="23"/>
+      <c r="D86" s="23"/>
+      <c r="E86" s="23"/>
+      <c r="L86" s="23"/>
+      <c r="M86" s="23"/>
+      <c r="N86" s="23"/>
+      <c r="O86" s="23"/>
+      <c r="P86" s="23"/>
+      <c r="Q86" s="23"/>
+      <c r="R86" s="23"/>
+      <c r="S86" s="23"/>
+      <c r="V86" s="23"/>
+    </row>
+    <row r="87" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B87" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" s="23"/>
+      <c r="D87" s="23"/>
+      <c r="E87" s="23"/>
+      <c r="L87" s="23"/>
+      <c r="M87" s="23"/>
+      <c r="N87" s="23"/>
+      <c r="O87" s="23"/>
+      <c r="P87" s="23"/>
+      <c r="Q87" s="23"/>
+      <c r="R87" s="23"/>
+      <c r="S87" s="23"/>
+      <c r="V87" s="23"/>
+    </row>
+    <row r="88" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B88" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="23"/>
+      <c r="D88" s="23"/>
+      <c r="E88" s="23"/>
+      <c r="L88" s="23"/>
+      <c r="M88" s="23"/>
+      <c r="N88" s="23"/>
+      <c r="O88" s="23"/>
+      <c r="P88" s="23"/>
+      <c r="Q88" s="23"/>
+      <c r="R88" s="23"/>
+      <c r="S88" s="23"/>
+      <c r="V88" s="23"/>
+    </row>
+    <row r="90" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B90" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C90" s="23"/>
+      <c r="D90" s="23"/>
+      <c r="E90" s="23"/>
+      <c r="L90" s="23"/>
+      <c r="M90" s="23"/>
+      <c r="N90" s="23"/>
+      <c r="O90" s="23"/>
+      <c r="P90" s="23"/>
+      <c r="Q90" s="23"/>
+      <c r="R90" s="23"/>
+      <c r="S90" s="23"/>
+      <c r="V90" s="23"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="P1:V1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:V4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56B3708C-D093-4A9C-9961-2E39923C8C8E}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BF90"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="1.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5703125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="1.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="2" style="2" customWidth="1"/>
+    <col min="24" max="24" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="53" width="7.28515625" style="2" customWidth="1"/>
+    <col min="54" max="54" width="1.5703125" style="2" customWidth="1"/>
+    <col min="55" max="55" width="9.42578125" style="2" customWidth="1"/>
+    <col min="56" max="56" width="1.28515625" style="2" customWidth="1"/>
+    <col min="57" max="57" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="59" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="156">
+        <v>46067</v>
+      </c>
+      <c r="Q1" s="157"/>
+      <c r="R1" s="157"/>
+      <c r="S1" s="157"/>
+      <c r="T1" s="157"/>
+      <c r="U1" s="157"/>
+      <c r="V1" s="158"/>
+    </row>
+    <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+    </row>
+    <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="53"/>
+      <c r="B4" s="150" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="159" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="169" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="160" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="161"/>
+      <c r="G4" s="162" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="170" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="164" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="170" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="166" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="167"/>
+      <c r="N4" s="167"/>
+      <c r="O4" s="167"/>
+      <c r="P4" s="167"/>
+      <c r="Q4" s="167"/>
+      <c r="R4" s="167"/>
+      <c r="S4" s="167"/>
+      <c r="T4" s="167"/>
+      <c r="U4" s="167"/>
+      <c r="V4" s="168"/>
+    </row>
+    <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="53"/>
+      <c r="B5" s="150"/>
+      <c r="C5" s="159"/>
+      <c r="D5" s="169"/>
+      <c r="E5" s="52" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="149" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="163"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="165"/>
+      <c r="J5" s="171"/>
+      <c r="L5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="90" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="90" t="s">
+        <v>75</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="90" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="130" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" s="124" t="s">
+        <v>75</v>
+      </c>
+      <c r="T5" s="7"/>
+      <c r="U5" s="8"/>
+      <c r="V5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ5" s="9"/>
+      <c r="AK5" s="9"/>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
+      <c r="AV5" s="9"/>
+      <c r="AW5" s="9"/>
+      <c r="AX5" s="9"/>
+      <c r="AY5" s="9"/>
+      <c r="AZ5" s="9"/>
+      <c r="BA5" s="9"/>
+      <c r="BB5" s="9"/>
+      <c r="BC5" s="9"/>
+      <c r="BD5" s="9"/>
+      <c r="BE5" s="9"/>
+      <c r="BF5" s="9"/>
+    </row>
+    <row r="6" spans="1:58" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="10"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="27"/>
+      <c r="P6" s="27"/>
+      <c r="Q6" s="84"/>
+      <c r="R6" s="131"/>
+      <c r="S6" s="126"/>
+      <c r="T6" s="44"/>
+      <c r="U6" s="28"/>
+      <c r="V6" s="30"/>
+      <c r="AJ6" s="9"/>
+      <c r="AK6" s="9"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="9"/>
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="9"/>
+      <c r="AU6" s="9"/>
+      <c r="AV6" s="9"/>
+      <c r="AW6" s="9"/>
+      <c r="AX6" s="9"/>
+      <c r="AY6" s="9"/>
+      <c r="AZ6" s="9"/>
+      <c r="BA6" s="9"/>
+      <c r="BB6" s="9"/>
+      <c r="BC6" s="9"/>
+      <c r="BD6" s="9"/>
+      <c r="BE6" s="9"/>
+      <c r="BF6" s="9"/>
+    </row>
+    <row r="7" spans="1:58" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="10"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="72"/>
+      <c r="I7" s="72"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="44"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="27"/>
+      <c r="N7" s="27"/>
+      <c r="O7" s="27"/>
+      <c r="P7" s="27"/>
+      <c r="Q7" s="84"/>
+      <c r="R7" s="131"/>
+      <c r="S7" s="126"/>
+      <c r="T7" s="44"/>
+      <c r="U7" s="28"/>
+      <c r="V7" s="30"/>
+      <c r="AJ7" s="9"/>
+      <c r="AK7" s="9"/>
+      <c r="AL7" s="9"/>
+      <c r="AM7" s="9"/>
+      <c r="AN7" s="9"/>
+      <c r="AO7" s="9"/>
+      <c r="AP7" s="9"/>
+      <c r="AQ7" s="9"/>
+      <c r="AR7" s="9"/>
+      <c r="AS7" s="9"/>
+      <c r="AT7" s="9"/>
+      <c r="AU7" s="9"/>
+      <c r="AV7" s="9"/>
+      <c r="AW7" s="9"/>
+      <c r="AX7" s="9"/>
+      <c r="AY7" s="9"/>
+      <c r="AZ7" s="9"/>
+      <c r="BA7" s="9"/>
+      <c r="BB7" s="9"/>
+      <c r="BC7" s="9"/>
+      <c r="BD7" s="9"/>
+      <c r="BE7" s="9"/>
+      <c r="BF7" s="9"/>
+    </row>
+    <row r="8" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="100"/>
+      <c r="D8" s="101"/>
+      <c r="E8" s="91"/>
+      <c r="F8" s="91"/>
+      <c r="G8" s="102"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="93">
+        <f>C8-G8</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="103">
+        <f t="shared" ref="J8:J12" si="0">D8-H8</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="44"/>
+      <c r="L8" s="91"/>
+      <c r="M8" s="91"/>
+      <c r="N8" s="91"/>
+      <c r="O8" s="91"/>
+      <c r="P8" s="91"/>
+      <c r="Q8" s="92"/>
+      <c r="R8" s="129">
+        <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="127">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="44"/>
+      <c r="U8" s="28"/>
+      <c r="V8" s="30"/>
+      <c r="AJ8" s="12"/>
+      <c r="AK8" s="12"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="12"/>
+      <c r="BE8" s="12"/>
+      <c r="BF8" s="12"/>
+    </row>
+    <row r="9" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f t="shared" ref="A9:A59" si="2">A8+1</f>
+        <v>2</v>
+      </c>
+      <c r="B9" s="54" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="104"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="106"/>
+      <c r="F9" s="106"/>
+      <c r="G9" s="107"/>
+      <c r="H9" s="108"/>
+      <c r="I9" s="93">
+        <f t="shared" ref="I9:J59" si="3">C9-G9</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="103">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="64"/>
+      <c r="L9" s="94"/>
+      <c r="M9" s="94"/>
+      <c r="N9" s="94"/>
+      <c r="O9" s="94"/>
+      <c r="P9" s="94"/>
+      <c r="Q9" s="95"/>
+      <c r="R9" s="129">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="127">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="64"/>
+      <c r="U9" s="67"/>
+      <c r="V9" s="66"/>
+      <c r="AJ9" s="12"/>
+      <c r="AK9" s="12"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+      <c r="BC9" s="12"/>
+      <c r="BD9" s="12"/>
+      <c r="BE9" s="12"/>
+      <c r="BF9" s="12"/>
+    </row>
+    <row r="10" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="100"/>
+      <c r="D10" s="101"/>
+      <c r="E10" s="91"/>
+      <c r="F10" s="91"/>
+      <c r="G10" s="102"/>
+      <c r="H10" s="93"/>
+      <c r="I10" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="103">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="44"/>
+      <c r="L10" s="91"/>
+      <c r="M10" s="91"/>
+      <c r="N10" s="91"/>
+      <c r="O10" s="91"/>
+      <c r="P10" s="91"/>
+      <c r="Q10" s="92"/>
+      <c r="R10" s="129">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="127">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="44"/>
+      <c r="U10" s="28"/>
+      <c r="V10" s="30"/>
+      <c r="AJ10" s="12"/>
+      <c r="AK10" s="12"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+      <c r="BC10" s="12"/>
+      <c r="BD10" s="12"/>
+      <c r="BE10" s="12"/>
+      <c r="BF10" s="12"/>
+    </row>
+    <row r="11" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="100"/>
+      <c r="D11" s="101"/>
+      <c r="E11" s="91"/>
+      <c r="F11" s="91"/>
+      <c r="G11" s="102"/>
+      <c r="H11" s="93"/>
+      <c r="I11" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="103">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="44"/>
+      <c r="L11" s="91"/>
+      <c r="M11" s="91"/>
+      <c r="N11" s="91"/>
+      <c r="O11" s="91"/>
+      <c r="P11" s="91"/>
+      <c r="Q11" s="92"/>
+      <c r="R11" s="129">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="127">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="44"/>
+      <c r="U11" s="28"/>
+      <c r="V11" s="30"/>
+      <c r="AJ11" s="12"/>
+      <c r="AK11" s="12"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+      <c r="BC11" s="12"/>
+      <c r="BD11" s="12"/>
+      <c r="BE11" s="12"/>
+      <c r="BF11" s="12"/>
+    </row>
+    <row r="12" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="100"/>
+      <c r="D12" s="101"/>
+      <c r="E12" s="91"/>
+      <c r="F12" s="91"/>
+      <c r="G12" s="102"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="103">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="44"/>
+      <c r="L12" s="91"/>
+      <c r="M12" s="91"/>
+      <c r="N12" s="91"/>
+      <c r="O12" s="91"/>
+      <c r="P12" s="91"/>
+      <c r="Q12" s="92"/>
+      <c r="R12" s="129">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="127">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="44"/>
+      <c r="U12" s="28"/>
+      <c r="V12" s="30"/>
+      <c r="AJ12" s="12"/>
+      <c r="AK12" s="12"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+      <c r="BC12" s="12"/>
+      <c r="BD12" s="12"/>
+      <c r="BE12" s="12"/>
+      <c r="BF12" s="12"/>
+    </row>
+    <row r="13" spans="1:58" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="B13" s="54" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="104"/>
+      <c r="D13" s="105"/>
+      <c r="E13" s="106"/>
+      <c r="F13" s="106"/>
+      <c r="G13" s="107"/>
+      <c r="H13" s="108"/>
+      <c r="I13" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="103">
+        <f>D13-H13</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="68"/>
+      <c r="L13" s="94"/>
+      <c r="M13" s="94"/>
+      <c r="N13" s="94"/>
+      <c r="O13" s="94"/>
+      <c r="P13" s="94"/>
+      <c r="Q13" s="95"/>
+      <c r="R13" s="129">
+        <f>L13+N13+P13</f>
+        <v>0</v>
+      </c>
+      <c r="S13" s="127">
+        <f>M13+O13+Q13</f>
+        <v>0</v>
+      </c>
+      <c r="T13" s="68"/>
+      <c r="U13" s="67"/>
+      <c r="V13" s="66"/>
+      <c r="W13" s="2"/>
+      <c r="AB13" s="2"/>
+      <c r="AE13" s="2"/>
+      <c r="AF13" s="2"/>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="2"/>
+      <c r="AI13" s="2"/>
+      <c r="AJ13" s="12"/>
+      <c r="AK13" s="12"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+      <c r="BC13" s="12"/>
+      <c r="BD13" s="12"/>
+      <c r="BE13" s="12"/>
+      <c r="BF13" s="12"/>
+    </row>
+    <row r="14" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="100"/>
+      <c r="D14" s="101"/>
+      <c r="E14" s="91"/>
+      <c r="F14" s="91"/>
+      <c r="G14" s="102"/>
+      <c r="H14" s="93"/>
+      <c r="I14" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="44"/>
+      <c r="L14" s="91"/>
+      <c r="M14" s="91"/>
+      <c r="N14" s="91"/>
+      <c r="O14" s="91"/>
+      <c r="P14" s="91"/>
+      <c r="Q14" s="92"/>
+      <c r="R14" s="129">
+        <f t="shared" ref="R14:S59" si="4">L14+N14+P14</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="44"/>
+      <c r="U14" s="28"/>
+      <c r="V14" s="30"/>
+      <c r="AJ14" s="12"/>
+      <c r="AK14" s="12"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+      <c r="BC14" s="12"/>
+      <c r="BD14" s="12"/>
+      <c r="BE14" s="12"/>
+      <c r="BF14" s="12"/>
+    </row>
+    <row r="15" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="100"/>
+      <c r="D15" s="101"/>
+      <c r="E15" s="91"/>
+      <c r="F15" s="91"/>
+      <c r="G15" s="102"/>
+      <c r="H15" s="93"/>
+      <c r="I15" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="44"/>
+      <c r="L15" s="91"/>
+      <c r="M15" s="91"/>
+      <c r="N15" s="91"/>
+      <c r="O15" s="91"/>
+      <c r="P15" s="91"/>
+      <c r="Q15" s="92"/>
+      <c r="R15" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="44"/>
+      <c r="U15" s="28"/>
+      <c r="V15" s="30"/>
+      <c r="AJ15" s="12"/>
+      <c r="AK15" s="12"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+      <c r="BC15" s="12"/>
+      <c r="BD15" s="12"/>
+      <c r="BE15" s="12"/>
+      <c r="BF15" s="12"/>
+    </row>
+    <row r="16" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="100"/>
+      <c r="D16" s="101"/>
+      <c r="E16" s="91"/>
+      <c r="F16" s="91"/>
+      <c r="G16" s="102"/>
+      <c r="H16" s="93"/>
+      <c r="I16" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="44"/>
+      <c r="L16" s="91"/>
+      <c r="M16" s="91"/>
+      <c r="N16" s="91"/>
+      <c r="O16" s="91"/>
+      <c r="P16" s="91"/>
+      <c r="Q16" s="92"/>
+      <c r="R16" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="44"/>
+      <c r="U16" s="28"/>
+      <c r="V16" s="30"/>
+      <c r="AJ16" s="12"/>
+      <c r="AK16" s="12"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+      <c r="BC16" s="12"/>
+      <c r="BD16" s="12"/>
+      <c r="BE16" s="12"/>
+      <c r="BF16" s="12"/>
+    </row>
+    <row r="17" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="100"/>
+      <c r="D17" s="101"/>
+      <c r="E17" s="91"/>
+      <c r="F17" s="91"/>
+      <c r="G17" s="102"/>
+      <c r="H17" s="93"/>
+      <c r="I17" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="44"/>
+      <c r="L17" s="91"/>
+      <c r="M17" s="91"/>
+      <c r="N17" s="91"/>
+      <c r="O17" s="91"/>
+      <c r="P17" s="91"/>
+      <c r="Q17" s="92"/>
+      <c r="R17" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="44"/>
+      <c r="U17" s="28"/>
+      <c r="V17" s="30"/>
+      <c r="AJ17" s="12"/>
+      <c r="AK17" s="12"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+      <c r="BC17" s="12"/>
+      <c r="BD17" s="12"/>
+      <c r="BE17" s="12"/>
+      <c r="BF17" s="12"/>
+    </row>
+    <row r="18" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <f t="shared" si="2"/>
+        <v>11</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="100"/>
+      <c r="D18" s="101"/>
+      <c r="E18" s="91"/>
+      <c r="F18" s="91"/>
+      <c r="G18" s="102"/>
+      <c r="H18" s="93"/>
+      <c r="I18" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="44"/>
+      <c r="L18" s="91"/>
+      <c r="M18" s="91"/>
+      <c r="N18" s="91"/>
+      <c r="O18" s="91"/>
+      <c r="P18" s="91"/>
+      <c r="Q18" s="92"/>
+      <c r="R18" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="44"/>
+      <c r="U18" s="28"/>
+      <c r="V18" s="30"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+      <c r="BC18" s="12"/>
+      <c r="BD18" s="12"/>
+      <c r="BE18" s="12"/>
+      <c r="BF18" s="12"/>
+    </row>
+    <row r="19" spans="1:58" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="100"/>
+      <c r="D19" s="101"/>
+      <c r="E19" s="91"/>
+      <c r="F19" s="91"/>
+      <c r="G19" s="102"/>
+      <c r="H19" s="93"/>
+      <c r="I19" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="44"/>
+      <c r="L19" s="91"/>
+      <c r="M19" s="91"/>
+      <c r="N19" s="91"/>
+      <c r="O19" s="91"/>
+      <c r="P19" s="91"/>
+      <c r="Q19" s="92"/>
+      <c r="R19" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="44"/>
+      <c r="U19" s="28"/>
+      <c r="V19" s="30"/>
+      <c r="AJ19" s="12"/>
+      <c r="AK19" s="12"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+      <c r="BC19" s="12"/>
+      <c r="BD19" s="12"/>
+      <c r="BE19" s="12"/>
+      <c r="BF19" s="12"/>
+    </row>
+    <row r="20" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <f t="shared" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="100"/>
+      <c r="D20" s="101"/>
+      <c r="E20" s="91"/>
+      <c r="F20" s="91"/>
+      <c r="G20" s="102"/>
+      <c r="H20" s="93"/>
+      <c r="I20" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="44"/>
+      <c r="L20" s="91"/>
+      <c r="M20" s="91"/>
+      <c r="N20" s="91"/>
+      <c r="O20" s="91"/>
+      <c r="P20" s="91"/>
+      <c r="Q20" s="92"/>
+      <c r="R20" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="44"/>
+      <c r="U20" s="28"/>
+      <c r="V20" s="30"/>
+      <c r="AJ20" s="12"/>
+      <c r="AK20" s="12"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+      <c r="BC20" s="12"/>
+      <c r="BD20" s="12"/>
+      <c r="BE20" s="12"/>
+      <c r="BF20" s="12"/>
+    </row>
+    <row r="21" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="100"/>
+      <c r="D21" s="101"/>
+      <c r="E21" s="91"/>
+      <c r="F21" s="91"/>
+      <c r="G21" s="102"/>
+      <c r="H21" s="93"/>
+      <c r="I21" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="44"/>
+      <c r="L21" s="91"/>
+      <c r="M21" s="91"/>
+      <c r="N21" s="91"/>
+      <c r="O21" s="91"/>
+      <c r="P21" s="91"/>
+      <c r="Q21" s="92"/>
+      <c r="R21" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="44"/>
+      <c r="U21" s="28"/>
+      <c r="V21" s="30"/>
+      <c r="AJ21" s="12"/>
+      <c r="AK21" s="12"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+      <c r="BC21" s="12"/>
+      <c r="BD21" s="12"/>
+      <c r="BE21" s="12"/>
+      <c r="BF21" s="12"/>
+    </row>
+    <row r="22" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="100"/>
+      <c r="D22" s="101"/>
+      <c r="E22" s="91"/>
+      <c r="F22" s="91"/>
+      <c r="G22" s="102"/>
+      <c r="H22" s="93"/>
+      <c r="I22" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="44"/>
+      <c r="L22" s="91"/>
+      <c r="M22" s="91"/>
+      <c r="N22" s="91"/>
+      <c r="O22" s="91"/>
+      <c r="P22" s="91"/>
+      <c r="Q22" s="92"/>
+      <c r="R22" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="44"/>
+      <c r="U22" s="28"/>
+      <c r="V22" s="30"/>
+      <c r="AJ22" s="12"/>
+      <c r="AK22" s="12"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+      <c r="BC22" s="12"/>
+      <c r="BD22" s="12"/>
+      <c r="BE22" s="12"/>
+      <c r="BF22" s="12"/>
+    </row>
+    <row r="23" spans="1:58" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="100"/>
+      <c r="D23" s="101"/>
+      <c r="E23" s="91"/>
+      <c r="F23" s="91"/>
+      <c r="G23" s="102"/>
+      <c r="H23" s="93"/>
+      <c r="I23" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="45"/>
+      <c r="L23" s="91"/>
+      <c r="M23" s="91"/>
+      <c r="N23" s="91"/>
+      <c r="O23" s="91"/>
+      <c r="P23" s="91"/>
+      <c r="Q23" s="92"/>
+      <c r="R23" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="45"/>
+      <c r="U23" s="28"/>
+      <c r="V23" s="30"/>
+      <c r="W23" s="2"/>
+      <c r="AB23" s="2"/>
+      <c r="AE23" s="2"/>
+      <c r="AF23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="12"/>
+      <c r="AK23" s="12"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+      <c r="BC23" s="12"/>
+      <c r="BD23" s="12"/>
+      <c r="BE23" s="12"/>
+      <c r="BF23" s="12"/>
+    </row>
+    <row r="24" spans="1:58" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <f t="shared" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="100"/>
+      <c r="D24" s="101"/>
+      <c r="E24" s="91"/>
+      <c r="F24" s="91"/>
+      <c r="G24" s="102"/>
+      <c r="H24" s="93"/>
+      <c r="I24" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="45"/>
+      <c r="L24" s="91"/>
+      <c r="M24" s="91"/>
+      <c r="N24" s="91"/>
+      <c r="O24" s="91"/>
+      <c r="P24" s="91"/>
+      <c r="Q24" s="92"/>
+      <c r="R24" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="45"/>
+      <c r="U24" s="28"/>
+      <c r="V24" s="30"/>
+      <c r="W24" s="2"/>
+      <c r="AB24" s="2"/>
+      <c r="AE24" s="2"/>
+      <c r="AF24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="12"/>
+      <c r="AK24" s="12"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+      <c r="BC24" s="12"/>
+      <c r="BD24" s="12"/>
+      <c r="BE24" s="12"/>
+      <c r="BF24" s="12"/>
+    </row>
+    <row r="25" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <f t="shared" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="100"/>
+      <c r="D25" s="101"/>
+      <c r="E25" s="91"/>
+      <c r="F25" s="91"/>
+      <c r="G25" s="102"/>
+      <c r="H25" s="93"/>
+      <c r="I25" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="44"/>
+      <c r="L25" s="91"/>
+      <c r="M25" s="91"/>
+      <c r="N25" s="91"/>
+      <c r="O25" s="91"/>
+      <c r="P25" s="91"/>
+      <c r="Q25" s="92"/>
+      <c r="R25" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="44"/>
+      <c r="U25" s="28"/>
+      <c r="V25" s="30"/>
+      <c r="AJ25" s="12"/>
+      <c r="AK25" s="12"/>
+      <c r="AL25" s="12"/>
+      <c r="AM25" s="12"/>
+      <c r="AN25" s="12"/>
+      <c r="AO25" s="12"/>
+      <c r="AP25" s="12"/>
+      <c r="AQ25" s="12"/>
+      <c r="AR25" s="12"/>
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="12"/>
+      <c r="AU25" s="12"/>
+      <c r="AV25" s="12"/>
+      <c r="AW25" s="12"/>
+      <c r="AX25" s="12"/>
+      <c r="AY25" s="12"/>
+      <c r="AZ25" s="12"/>
+      <c r="BA25" s="12"/>
+      <c r="BB25" s="12"/>
+      <c r="BC25" s="12"/>
+      <c r="BD25" s="12"/>
+      <c r="BE25" s="12"/>
+      <c r="BF25" s="12"/>
+    </row>
+    <row r="26" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <f t="shared" si="2"/>
+        <v>19</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="100"/>
+      <c r="D26" s="101"/>
+      <c r="E26" s="91"/>
+      <c r="F26" s="91"/>
+      <c r="G26" s="102"/>
+      <c r="H26" s="93"/>
+      <c r="I26" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="44"/>
+      <c r="L26" s="91"/>
+      <c r="M26" s="91"/>
+      <c r="N26" s="91"/>
+      <c r="O26" s="91"/>
+      <c r="P26" s="91"/>
+      <c r="Q26" s="92"/>
+      <c r="R26" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="44"/>
+      <c r="U26" s="28"/>
+      <c r="V26" s="30"/>
+      <c r="BC26" s="14" t="e">
+        <f>#REF!-BC25</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:58" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="100"/>
+      <c r="D27" s="101"/>
+      <c r="E27" s="91"/>
+      <c r="F27" s="91"/>
+      <c r="G27" s="102"/>
+      <c r="H27" s="93"/>
+      <c r="I27" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="45"/>
+      <c r="L27" s="91"/>
+      <c r="M27" s="91"/>
+      <c r="N27" s="91"/>
+      <c r="O27" s="91"/>
+      <c r="P27" s="91"/>
+      <c r="Q27" s="92"/>
+      <c r="R27" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="45"/>
+      <c r="U27" s="28"/>
+      <c r="V27" s="30"/>
+      <c r="W27" s="2"/>
+      <c r="AB27" s="2"/>
+      <c r="AE27" s="2"/>
+      <c r="AF27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+    </row>
+    <row r="28" spans="1:58" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <f t="shared" si="2"/>
+        <v>21</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="100"/>
+      <c r="D28" s="101"/>
+      <c r="E28" s="91"/>
+      <c r="F28" s="91"/>
+      <c r="G28" s="102"/>
+      <c r="H28" s="93"/>
+      <c r="I28" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="45"/>
+      <c r="L28" s="91"/>
+      <c r="M28" s="91"/>
+      <c r="N28" s="91"/>
+      <c r="O28" s="91"/>
+      <c r="P28" s="91"/>
+      <c r="Q28" s="92"/>
+      <c r="R28" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="45"/>
+      <c r="U28" s="28"/>
+      <c r="V28" s="30"/>
+      <c r="W28" s="2"/>
+      <c r="AB28" s="2"/>
+      <c r="AE28" s="2"/>
+      <c r="AF28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+    </row>
+    <row r="29" spans="1:58" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="100"/>
+      <c r="D29" s="101"/>
+      <c r="E29" s="91"/>
+      <c r="F29" s="91"/>
+      <c r="G29" s="102"/>
+      <c r="H29" s="93"/>
+      <c r="I29" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J29" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="45"/>
+      <c r="L29" s="91"/>
+      <c r="M29" s="91"/>
+      <c r="N29" s="91"/>
+      <c r="O29" s="91"/>
+      <c r="P29" s="91"/>
+      <c r="Q29" s="92"/>
+      <c r="R29" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S29" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="45"/>
+      <c r="U29" s="28"/>
+      <c r="V29" s="30"/>
+      <c r="W29" s="2"/>
+      <c r="AB29" s="2"/>
+      <c r="AE29" s="2"/>
+      <c r="AF29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+    </row>
+    <row r="30" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="100"/>
+      <c r="D30" s="101"/>
+      <c r="E30" s="91"/>
+      <c r="F30" s="91"/>
+      <c r="G30" s="102"/>
+      <c r="H30" s="93"/>
+      <c r="I30" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="44"/>
+      <c r="L30" s="91"/>
+      <c r="M30" s="91"/>
+      <c r="N30" s="91"/>
+      <c r="O30" s="91"/>
+      <c r="P30" s="91"/>
+      <c r="Q30" s="92"/>
+      <c r="R30" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="44"/>
+      <c r="U30" s="28"/>
+      <c r="V30" s="30"/>
+    </row>
+    <row r="31" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <f t="shared" si="2"/>
+        <v>24</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="100"/>
+      <c r="D31" s="101"/>
+      <c r="E31" s="91"/>
+      <c r="F31" s="91"/>
+      <c r="G31" s="102"/>
+      <c r="H31" s="93"/>
+      <c r="I31" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="44"/>
+      <c r="L31" s="91"/>
+      <c r="M31" s="91"/>
+      <c r="N31" s="91"/>
+      <c r="O31" s="91"/>
+      <c r="P31" s="91"/>
+      <c r="Q31" s="92"/>
+      <c r="R31" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T31" s="44"/>
+      <c r="U31" s="28"/>
+      <c r="V31" s="30"/>
+    </row>
+    <row r="32" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="100"/>
+      <c r="D32" s="101"/>
+      <c r="E32" s="91"/>
+      <c r="F32" s="91"/>
+      <c r="G32" s="102"/>
+      <c r="H32" s="93"/>
+      <c r="I32" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="44"/>
+      <c r="L32" s="91"/>
+      <c r="M32" s="91"/>
+      <c r="N32" s="91"/>
+      <c r="O32" s="91"/>
+      <c r="P32" s="91"/>
+      <c r="Q32" s="92"/>
+      <c r="R32" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T32" s="44"/>
+      <c r="U32" s="28"/>
+      <c r="V32" s="30"/>
+    </row>
+    <row r="33" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <f t="shared" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="100"/>
+      <c r="D33" s="101"/>
+      <c r="E33" s="91"/>
+      <c r="F33" s="91"/>
+      <c r="G33" s="102"/>
+      <c r="H33" s="93"/>
+      <c r="I33" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="44"/>
+      <c r="L33" s="91"/>
+      <c r="M33" s="91"/>
+      <c r="N33" s="91"/>
+      <c r="O33" s="91"/>
+      <c r="P33" s="91"/>
+      <c r="Q33" s="92"/>
+      <c r="R33" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T33" s="44"/>
+      <c r="U33" s="28"/>
+      <c r="V33" s="30"/>
+    </row>
+    <row r="34" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <f t="shared" si="2"/>
+        <v>27</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="100"/>
+      <c r="D34" s="101"/>
+      <c r="E34" s="91"/>
+      <c r="F34" s="91"/>
+      <c r="G34" s="102"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="44"/>
+      <c r="L34" s="91"/>
+      <c r="M34" s="91"/>
+      <c r="N34" s="91"/>
+      <c r="O34" s="91"/>
+      <c r="P34" s="91"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T34" s="44"/>
+      <c r="U34" s="28"/>
+      <c r="V34" s="30"/>
+    </row>
+    <row r="35" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <f t="shared" si="2"/>
+        <v>28</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="100"/>
+      <c r="D35" s="101"/>
+      <c r="E35" s="91"/>
+      <c r="F35" s="91"/>
+      <c r="G35" s="102"/>
+      <c r="H35" s="93"/>
+      <c r="I35" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K35" s="44"/>
+      <c r="L35" s="91"/>
+      <c r="M35" s="91"/>
+      <c r="N35" s="91"/>
+      <c r="O35" s="91"/>
+      <c r="P35" s="91"/>
+      <c r="Q35" s="92"/>
+      <c r="R35" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S35" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="44"/>
+      <c r="U35" s="28"/>
+      <c r="V35" s="30"/>
+    </row>
+    <row r="36" spans="1:24" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
+        <f t="shared" si="2"/>
+        <v>29</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="100"/>
+      <c r="D36" s="101"/>
+      <c r="E36" s="91"/>
+      <c r="F36" s="91"/>
+      <c r="G36" s="102"/>
+      <c r="H36" s="93"/>
+      <c r="I36" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="44"/>
+      <c r="L36" s="91"/>
+      <c r="M36" s="91"/>
+      <c r="N36" s="91"/>
+      <c r="O36" s="91"/>
+      <c r="P36" s="91"/>
+      <c r="Q36" s="92"/>
+      <c r="R36" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T36" s="44"/>
+      <c r="U36" s="28"/>
+      <c r="V36" s="30"/>
+    </row>
+    <row r="37" spans="1:24" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="100"/>
+      <c r="D37" s="101"/>
+      <c r="E37" s="91"/>
+      <c r="F37" s="91"/>
+      <c r="G37" s="102"/>
+      <c r="H37" s="93"/>
+      <c r="I37" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="44"/>
+      <c r="L37" s="91"/>
+      <c r="M37" s="91"/>
+      <c r="N37" s="91"/>
+      <c r="O37" s="91"/>
+      <c r="P37" s="91"/>
+      <c r="Q37" s="92"/>
+      <c r="R37" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="44"/>
+      <c r="U37" s="28"/>
+      <c r="V37" s="30"/>
+    </row>
+    <row r="38" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <f t="shared" si="2"/>
+        <v>31</v>
+      </c>
+      <c r="B38" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="104"/>
+      <c r="D38" s="105"/>
+      <c r="E38" s="106"/>
+      <c r="F38" s="106"/>
+      <c r="G38" s="107"/>
+      <c r="H38" s="108"/>
+      <c r="I38" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K38" s="64"/>
+      <c r="L38" s="94"/>
+      <c r="M38" s="94"/>
+      <c r="N38" s="94"/>
+      <c r="O38" s="94"/>
+      <c r="P38" s="94"/>
+      <c r="Q38" s="95"/>
+      <c r="R38" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S38" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="64"/>
+      <c r="U38" s="67"/>
+      <c r="V38" s="66"/>
+    </row>
+    <row r="39" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <f t="shared" si="2"/>
+        <v>32</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="100"/>
+      <c r="D39" s="101"/>
+      <c r="E39" s="91"/>
+      <c r="F39" s="91"/>
+      <c r="G39" s="102"/>
+      <c r="H39" s="93"/>
+      <c r="I39" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="44"/>
+      <c r="L39" s="91"/>
+      <c r="M39" s="91"/>
+      <c r="N39" s="91"/>
+      <c r="O39" s="91"/>
+      <c r="P39" s="91"/>
+      <c r="Q39" s="92"/>
+      <c r="R39" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T39" s="44"/>
+      <c r="U39" s="28"/>
+      <c r="V39" s="30"/>
+    </row>
+    <row r="40" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <f t="shared" si="2"/>
+        <v>33</v>
+      </c>
+      <c r="B40" s="117" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="118"/>
+      <c r="D40" s="119"/>
+      <c r="E40" s="120"/>
+      <c r="F40" s="120"/>
+      <c r="G40" s="121"/>
+      <c r="H40" s="116"/>
+      <c r="I40" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="44"/>
+      <c r="L40" s="91"/>
+      <c r="M40" s="91"/>
+      <c r="N40" s="91"/>
+      <c r="O40" s="91"/>
+      <c r="P40" s="91"/>
+      <c r="Q40" s="92"/>
+      <c r="R40" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="44"/>
+      <c r="U40" s="122"/>
+      <c r="V40" s="123"/>
+    </row>
+    <row r="41" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <f t="shared" si="2"/>
+        <v>34</v>
+      </c>
+      <c r="B41" s="54" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="104"/>
+      <c r="D41" s="105"/>
+      <c r="E41" s="106"/>
+      <c r="F41" s="106"/>
+      <c r="G41" s="107"/>
+      <c r="H41" s="108"/>
+      <c r="I41" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J41" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K41" s="64"/>
+      <c r="L41" s="91"/>
+      <c r="M41" s="91"/>
+      <c r="N41" s="91"/>
+      <c r="O41" s="91"/>
+      <c r="P41" s="91"/>
+      <c r="Q41" s="92"/>
+      <c r="R41" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S41" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T41" s="64"/>
+      <c r="U41" s="67"/>
+      <c r="V41" s="66"/>
+    </row>
+    <row r="42" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+      <c r="B42" s="59" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="109"/>
+      <c r="D42" s="110"/>
+      <c r="E42" s="96"/>
+      <c r="F42" s="96"/>
+      <c r="G42" s="111"/>
+      <c r="H42" s="112"/>
+      <c r="I42" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="69"/>
+      <c r="L42" s="96"/>
+      <c r="M42" s="96"/>
+      <c r="N42" s="96"/>
+      <c r="O42" s="96"/>
+      <c r="P42" s="96"/>
+      <c r="Q42" s="97"/>
+      <c r="R42" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S42" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="69"/>
+      <c r="U42" s="60"/>
+      <c r="V42" s="63"/>
+    </row>
+    <row r="43" spans="1:24" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="3">
+        <f t="shared" si="2"/>
+        <v>36</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="100"/>
+      <c r="D43" s="101"/>
+      <c r="E43" s="91"/>
+      <c r="F43" s="91"/>
+      <c r="G43" s="102"/>
+      <c r="H43" s="93"/>
+      <c r="I43" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="44"/>
+      <c r="L43" s="91"/>
+      <c r="M43" s="91"/>
+      <c r="N43" s="91"/>
+      <c r="O43" s="91"/>
+      <c r="P43" s="91"/>
+      <c r="Q43" s="92"/>
+      <c r="R43" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="44"/>
+      <c r="U43" s="28"/>
+      <c r="V43" s="30"/>
+    </row>
+    <row r="44" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <f t="shared" si="2"/>
+        <v>37</v>
+      </c>
+      <c r="B44" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="104"/>
+      <c r="D44" s="105"/>
+      <c r="E44" s="106"/>
+      <c r="F44" s="106"/>
+      <c r="G44" s="107"/>
+      <c r="H44" s="108"/>
+      <c r="I44" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J44" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K44" s="64"/>
+      <c r="L44" s="94"/>
+      <c r="M44" s="94"/>
+      <c r="N44" s="94"/>
+      <c r="O44" s="94"/>
+      <c r="P44" s="94"/>
+      <c r="Q44" s="95"/>
+      <c r="R44" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S44" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="64"/>
+      <c r="U44" s="67"/>
+      <c r="V44" s="66"/>
+      <c r="X44" s="50"/>
+    </row>
+    <row r="45" spans="1:24" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="3">
+        <f t="shared" si="2"/>
+        <v>38</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="100"/>
+      <c r="D45" s="101"/>
+      <c r="E45" s="91"/>
+      <c r="F45" s="91"/>
+      <c r="G45" s="102"/>
+      <c r="H45" s="93"/>
+      <c r="I45" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="44"/>
+      <c r="L45" s="91"/>
+      <c r="M45" s="91"/>
+      <c r="N45" s="91"/>
+      <c r="O45" s="91"/>
+      <c r="P45" s="91"/>
+      <c r="Q45" s="92"/>
+      <c r="R45" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T45" s="44"/>
+      <c r="U45" s="28"/>
+      <c r="V45" s="30"/>
+    </row>
+    <row r="46" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <f t="shared" si="2"/>
+        <v>39</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="100"/>
+      <c r="D46" s="101"/>
+      <c r="E46" s="91"/>
+      <c r="F46" s="91"/>
+      <c r="G46" s="102"/>
+      <c r="H46" s="93"/>
+      <c r="I46" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="44"/>
+      <c r="L46" s="91"/>
+      <c r="M46" s="91"/>
+      <c r="N46" s="91"/>
+      <c r="O46" s="91"/>
+      <c r="P46" s="91"/>
+      <c r="Q46" s="92"/>
+      <c r="R46" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="44"/>
+      <c r="U46" s="28"/>
+      <c r="V46" s="30"/>
+    </row>
+    <row r="47" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="100"/>
+      <c r="D47" s="101"/>
+      <c r="E47" s="91"/>
+      <c r="F47" s="91"/>
+      <c r="G47" s="102"/>
+      <c r="H47" s="93"/>
+      <c r="I47" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="44"/>
+      <c r="L47" s="91"/>
+      <c r="M47" s="91"/>
+      <c r="N47" s="91"/>
+      <c r="O47" s="91"/>
+      <c r="P47" s="91"/>
+      <c r="Q47" s="92"/>
+      <c r="R47" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="44"/>
+      <c r="U47" s="28"/>
+      <c r="V47" s="30"/>
+    </row>
+    <row r="48" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <f t="shared" si="2"/>
+        <v>41</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="100"/>
+      <c r="D48" s="101"/>
+      <c r="E48" s="91"/>
+      <c r="F48" s="91"/>
+      <c r="G48" s="102"/>
+      <c r="H48" s="93"/>
+      <c r="I48" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J48" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K48" s="44"/>
+      <c r="L48" s="91"/>
+      <c r="M48" s="91"/>
+      <c r="N48" s="91"/>
+      <c r="O48" s="91"/>
+      <c r="P48" s="91"/>
+      <c r="Q48" s="92"/>
+      <c r="R48" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S48" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T48" s="44"/>
+      <c r="U48" s="28"/>
+      <c r="V48" s="30"/>
+    </row>
+    <row r="49" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <f t="shared" si="2"/>
+        <v>42</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="100"/>
+      <c r="D49" s="101"/>
+      <c r="E49" s="91"/>
+      <c r="F49" s="91"/>
+      <c r="G49" s="102"/>
+      <c r="H49" s="93"/>
+      <c r="I49" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J49" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="44"/>
+      <c r="L49" s="91"/>
+      <c r="M49" s="91"/>
+      <c r="N49" s="91"/>
+      <c r="O49" s="91"/>
+      <c r="P49" s="91"/>
+      <c r="Q49" s="92"/>
+      <c r="R49" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T49" s="44"/>
+      <c r="U49" s="28"/>
+      <c r="V49" s="30"/>
+    </row>
+    <row r="50" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <f t="shared" si="2"/>
+        <v>43</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="100"/>
+      <c r="D50" s="101"/>
+      <c r="E50" s="91"/>
+      <c r="F50" s="91"/>
+      <c r="G50" s="102"/>
+      <c r="H50" s="93"/>
+      <c r="I50" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="44"/>
+      <c r="L50" s="91"/>
+      <c r="M50" s="91"/>
+      <c r="N50" s="91"/>
+      <c r="O50" s="91"/>
+      <c r="P50" s="91"/>
+      <c r="Q50" s="92"/>
+      <c r="R50" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T50" s="44"/>
+      <c r="U50" s="28"/>
+      <c r="V50" s="30"/>
+    </row>
+    <row r="51" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <f t="shared" si="2"/>
+        <v>44</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="100"/>
+      <c r="D51" s="101"/>
+      <c r="E51" s="91"/>
+      <c r="F51" s="91"/>
+      <c r="G51" s="102"/>
+      <c r="H51" s="93"/>
+      <c r="I51" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="44"/>
+      <c r="L51" s="91"/>
+      <c r="M51" s="91"/>
+      <c r="N51" s="91"/>
+      <c r="O51" s="91"/>
+      <c r="P51" s="91"/>
+      <c r="Q51" s="92"/>
+      <c r="R51" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T51" s="44"/>
+      <c r="U51" s="28"/>
+      <c r="V51" s="30"/>
+    </row>
+    <row r="52" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <f t="shared" si="2"/>
+        <v>45</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="100"/>
+      <c r="D52" s="101"/>
+      <c r="E52" s="91"/>
+      <c r="F52" s="91"/>
+      <c r="G52" s="102"/>
+      <c r="H52" s="93"/>
+      <c r="I52" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J52" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="44"/>
+      <c r="L52" s="91"/>
+      <c r="M52" s="91"/>
+      <c r="N52" s="91"/>
+      <c r="O52" s="91"/>
+      <c r="P52" s="91"/>
+      <c r="Q52" s="92"/>
+      <c r="R52" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T52" s="44"/>
+      <c r="U52" s="28"/>
+      <c r="V52" s="30"/>
+    </row>
+    <row r="53" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <f t="shared" si="2"/>
+        <v>46</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="100"/>
+      <c r="D53" s="101"/>
+      <c r="E53" s="91"/>
+      <c r="F53" s="91"/>
+      <c r="G53" s="102"/>
+      <c r="H53" s="93"/>
+      <c r="I53" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="44"/>
+      <c r="L53" s="91"/>
+      <c r="M53" s="91"/>
+      <c r="N53" s="91"/>
+      <c r="O53" s="91"/>
+      <c r="P53" s="91"/>
+      <c r="Q53" s="92"/>
+      <c r="R53" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="44"/>
+      <c r="U53" s="28"/>
+      <c r="V53" s="30"/>
+    </row>
+    <row r="54" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <f t="shared" si="2"/>
+        <v>47</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="100"/>
+      <c r="D54" s="101"/>
+      <c r="E54" s="91"/>
+      <c r="F54" s="91"/>
+      <c r="G54" s="102"/>
+      <c r="H54" s="93"/>
+      <c r="I54" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J54" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="44"/>
+      <c r="L54" s="91"/>
+      <c r="M54" s="91"/>
+      <c r="N54" s="91"/>
+      <c r="O54" s="91"/>
+      <c r="P54" s="91"/>
+      <c r="Q54" s="92"/>
+      <c r="R54" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T54" s="44"/>
+      <c r="U54" s="28"/>
+      <c r="V54" s="30"/>
+    </row>
+    <row r="55" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <f t="shared" si="2"/>
+        <v>48</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="100"/>
+      <c r="D55" s="101"/>
+      <c r="E55" s="91"/>
+      <c r="F55" s="91"/>
+      <c r="G55" s="102"/>
+      <c r="H55" s="93"/>
+      <c r="I55" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="44"/>
+      <c r="L55" s="91"/>
+      <c r="M55" s="91"/>
+      <c r="N55" s="91"/>
+      <c r="O55" s="91"/>
+      <c r="P55" s="91"/>
+      <c r="Q55" s="92"/>
+      <c r="R55" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="44"/>
+      <c r="U55" s="28"/>
+      <c r="V55" s="30"/>
+    </row>
+    <row r="56" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <f t="shared" si="2"/>
+        <v>49</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="100"/>
+      <c r="D56" s="101"/>
+      <c r="E56" s="91"/>
+      <c r="F56" s="91"/>
+      <c r="G56" s="102"/>
+      <c r="H56" s="93"/>
+      <c r="I56" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="44"/>
+      <c r="L56" s="91"/>
+      <c r="M56" s="91"/>
+      <c r="N56" s="91"/>
+      <c r="O56" s="91"/>
+      <c r="P56" s="91"/>
+      <c r="Q56" s="92"/>
+      <c r="R56" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T56" s="44"/>
+      <c r="U56" s="28"/>
+      <c r="V56" s="30"/>
+    </row>
+    <row r="57" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="100"/>
+      <c r="D57" s="101"/>
+      <c r="E57" s="91"/>
+      <c r="F57" s="91"/>
+      <c r="G57" s="102"/>
+      <c r="H57" s="93"/>
+      <c r="I57" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="44"/>
+      <c r="L57" s="91"/>
+      <c r="M57" s="91"/>
+      <c r="N57" s="91"/>
+      <c r="O57" s="91"/>
+      <c r="P57" s="91"/>
+      <c r="Q57" s="92"/>
+      <c r="R57" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T57" s="44"/>
+      <c r="U57" s="28"/>
+      <c r="V57" s="30"/>
+    </row>
+    <row r="58" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <f t="shared" si="2"/>
+        <v>51</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="100"/>
+      <c r="D58" s="101"/>
+      <c r="E58" s="91"/>
+      <c r="F58" s="91"/>
+      <c r="G58" s="102"/>
+      <c r="H58" s="93"/>
+      <c r="I58" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="44"/>
+      <c r="L58" s="91"/>
+      <c r="M58" s="91"/>
+      <c r="N58" s="91"/>
+      <c r="O58" s="91"/>
+      <c r="P58" s="91"/>
+      <c r="Q58" s="92"/>
+      <c r="R58" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T58" s="44"/>
+      <c r="U58" s="28"/>
+      <c r="V58" s="30"/>
+    </row>
+    <row r="59" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <f t="shared" si="2"/>
+        <v>52</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="100"/>
+      <c r="D59" s="101"/>
+      <c r="E59" s="91"/>
+      <c r="F59" s="91"/>
+      <c r="G59" s="102"/>
+      <c r="H59" s="93"/>
+      <c r="I59" s="93">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="103">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="44"/>
+      <c r="L59" s="91"/>
+      <c r="M59" s="91"/>
+      <c r="N59" s="91"/>
+      <c r="O59" s="91"/>
+      <c r="P59" s="91"/>
+      <c r="Q59" s="92"/>
+      <c r="R59" s="129">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="127">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T59" s="44"/>
+      <c r="U59" s="28"/>
+      <c r="V59" s="30"/>
+    </row>
+    <row r="60" spans="1:22" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="46">
+        <f>SUM(C8:C59)</f>
+        <v>0</v>
+      </c>
+      <c r="D60" s="71">
+        <f>SUM(D8:D59)</f>
+        <v>0</v>
+      </c>
+      <c r="E60" s="47">
+        <f>SUM(E8:E59)</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="47"/>
+      <c r="G60" s="31">
+        <f>SUM(G8:G59)</f>
+        <v>0</v>
+      </c>
+      <c r="H60" s="73">
+        <f>SUM(H8:H59)</f>
+        <v>0</v>
+      </c>
+      <c r="I60" s="73">
+        <f>SUM(I8:I59)</f>
+        <v>0</v>
+      </c>
+      <c r="J60" s="48">
+        <f>SUM(J8:J59)</f>
+        <v>0</v>
+      </c>
+      <c r="K60" s="49"/>
+      <c r="L60" s="98">
+        <f t="shared" ref="L60:S60" si="5">SUM(L8:L59)</f>
+        <v>0</v>
+      </c>
+      <c r="M60" s="98">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N60" s="98">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O60" s="98">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P60" s="98">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Q60" s="99">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R60" s="128">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S60" s="125">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T60" s="49"/>
+      <c r="U60" s="46"/>
+      <c r="V60" s="48"/>
+    </row>
+    <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G62" s="151" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" s="74"/>
+      <c r="I62" s="74"/>
+      <c r="J62" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="L62" s="33"/>
+      <c r="M62" s="79"/>
+      <c r="N62" s="34"/>
+      <c r="O62" s="34"/>
+      <c r="P62" s="34"/>
+      <c r="Q62" s="85"/>
+      <c r="R62" s="85"/>
+      <c r="S62" s="35"/>
+    </row>
+    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="G63" s="152"/>
+      <c r="H63" s="75"/>
+      <c r="I63" s="75"/>
+      <c r="J63" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="L63" s="36"/>
+      <c r="M63" s="80"/>
+      <c r="N63" s="37"/>
+      <c r="O63" s="37"/>
+      <c r="P63" s="37"/>
+      <c r="Q63" s="86"/>
+      <c r="R63" s="86"/>
+      <c r="S63" s="38"/>
+    </row>
+    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="G64" s="153"/>
+      <c r="H64" s="76"/>
+      <c r="I64" s="76"/>
+      <c r="J64" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="L64" s="39"/>
+      <c r="M64" s="81"/>
+      <c r="N64" s="40"/>
+      <c r="O64" s="40"/>
+      <c r="P64" s="40"/>
+      <c r="Q64" s="87"/>
+      <c r="R64" s="87"/>
+      <c r="S64" s="41"/>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="G65" s="154" t="s">
+        <v>64</v>
+      </c>
+      <c r="H65" s="77"/>
+      <c r="I65" s="77"/>
+      <c r="J65" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="L65" s="39"/>
+      <c r="M65" s="81"/>
+      <c r="N65" s="40"/>
+      <c r="O65" s="40"/>
+      <c r="P65" s="40"/>
+      <c r="Q65" s="87"/>
+      <c r="R65" s="87"/>
+      <c r="S65" s="41"/>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="G66" s="154"/>
+      <c r="H66" s="77"/>
+      <c r="I66" s="77"/>
+      <c r="J66" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="L66" s="36"/>
+      <c r="M66" s="80"/>
+      <c r="N66" s="37"/>
+      <c r="O66" s="37"/>
+      <c r="P66" s="37"/>
+      <c r="Q66" s="86"/>
+      <c r="R66" s="86"/>
+      <c r="S66" s="38"/>
+    </row>
+    <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G67" s="155"/>
+      <c r="H67" s="78"/>
+      <c r="I67" s="78"/>
+      <c r="J67" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="L67" s="42"/>
+      <c r="M67" s="82"/>
+      <c r="N67" s="43"/>
+      <c r="O67" s="43"/>
+      <c r="P67" s="43"/>
+      <c r="Q67" s="88"/>
+      <c r="R67" s="88"/>
+      <c r="S67" s="32"/>
+    </row>
+    <row r="68" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:22" ht="113.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="147" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="148"/>
+      <c r="E69" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L69" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="M69" s="83"/>
+      <c r="N69" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="O69" s="21"/>
+      <c r="P69" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q69" s="89"/>
+      <c r="R69" s="89"/>
+      <c r="S69" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="V69" s="147" t="s">
         <v>56</v>
       </c>
     </row>
@@ -21402,15 +24773,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="153">
+      <c r="P1" s="156">
         <v>46055</v>
       </c>
-      <c r="Q1" s="154"/>
-      <c r="R1" s="154"/>
-      <c r="S1" s="154"/>
-      <c r="T1" s="154"/>
-      <c r="U1" s="154"/>
-      <c r="V1" s="155"/>
+      <c r="Q1" s="157"/>
+      <c r="R1" s="157"/>
+      <c r="S1" s="157"/>
+      <c r="T1" s="157"/>
+      <c r="U1" s="157"/>
+      <c r="V1" s="158"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -21433,60 +24804,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="147" t="s">
+      <c r="B4" s="150" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="156" t="s">
+      <c r="C4" s="159" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="166" t="s">
+      <c r="D4" s="169" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="157" t="s">
+      <c r="E4" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="158"/>
-      <c r="G4" s="159" t="s">
+      <c r="F4" s="161"/>
+      <c r="G4" s="162" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="167" t="s">
+      <c r="H4" s="170" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="161" t="s">
+      <c r="I4" s="164" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="167" t="s">
+      <c r="J4" s="170" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="163" t="s">
+      <c r="L4" s="166" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="164"/>
-      <c r="N4" s="164"/>
-      <c r="O4" s="164"/>
-      <c r="P4" s="164"/>
-      <c r="Q4" s="164"/>
-      <c r="R4" s="164"/>
-      <c r="S4" s="164"/>
-      <c r="T4" s="164"/>
-      <c r="U4" s="164"/>
-      <c r="V4" s="165"/>
+      <c r="M4" s="167"/>
+      <c r="N4" s="167"/>
+      <c r="O4" s="167"/>
+      <c r="P4" s="167"/>
+      <c r="Q4" s="167"/>
+      <c r="R4" s="167"/>
+      <c r="S4" s="167"/>
+      <c r="T4" s="167"/>
+      <c r="U4" s="167"/>
+      <c r="V4" s="168"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53"/>
-      <c r="B5" s="147"/>
-      <c r="C5" s="156"/>
-      <c r="D5" s="166"/>
+      <c r="B5" s="150"/>
+      <c r="C5" s="159"/>
+      <c r="D5" s="169"/>
       <c r="E5" s="52" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="134" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="160"/>
-      <c r="H5" s="168"/>
-      <c r="I5" s="162"/>
-      <c r="J5" s="168"/>
+      <c r="G5" s="163"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="165"/>
+      <c r="J5" s="171"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -24410,7 +27781,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="148" t="s">
+      <c r="G62" s="151" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="74"/>
@@ -24428,7 +27799,7 @@
       <c r="S62" s="35"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="149"/>
+      <c r="G63" s="152"/>
       <c r="H63" s="75"/>
       <c r="I63" s="75"/>
       <c r="J63" s="25" t="s">
@@ -24444,7 +27815,7 @@
       <c r="S63" s="38"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="150"/>
+      <c r="G64" s="153"/>
       <c r="H64" s="76"/>
       <c r="I64" s="76"/>
       <c r="J64" s="25" t="s">
@@ -24460,7 +27831,7 @@
       <c r="S64" s="41"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="151" t="s">
+      <c r="G65" s="154" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="77"/>
@@ -24478,7 +27849,7 @@
       <c r="S65" s="41"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="151"/>
+      <c r="G66" s="154"/>
       <c r="H66" s="77"/>
       <c r="I66" s="77"/>
       <c r="J66" s="25" t="s">
@@ -24494,7 +27865,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="152"/>
+      <c r="G67" s="155"/>
       <c r="H67" s="78"/>
       <c r="I67" s="78"/>
       <c r="J67" s="26" t="s">
@@ -24886,15 +28257,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="153">
+      <c r="P1" s="156">
         <v>46056</v>
       </c>
-      <c r="Q1" s="154"/>
-      <c r="R1" s="154"/>
-      <c r="S1" s="154"/>
-      <c r="T1" s="154"/>
-      <c r="U1" s="154"/>
-      <c r="V1" s="155"/>
+      <c r="Q1" s="157"/>
+      <c r="R1" s="157"/>
+      <c r="S1" s="157"/>
+      <c r="T1" s="157"/>
+      <c r="U1" s="157"/>
+      <c r="V1" s="158"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -24917,60 +28288,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="147" t="s">
+      <c r="B4" s="150" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="156" t="s">
+      <c r="C4" s="159" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="166" t="s">
+      <c r="D4" s="169" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="157" t="s">
+      <c r="E4" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="158"/>
-      <c r="G4" s="159" t="s">
+      <c r="F4" s="161"/>
+      <c r="G4" s="162" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="167" t="s">
+      <c r="H4" s="170" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="161" t="s">
+      <c r="I4" s="164" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="167" t="s">
+      <c r="J4" s="170" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="163" t="s">
+      <c r="L4" s="166" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="164"/>
-      <c r="N4" s="164"/>
-      <c r="O4" s="164"/>
-      <c r="P4" s="164"/>
-      <c r="Q4" s="164"/>
-      <c r="R4" s="164"/>
-      <c r="S4" s="164"/>
-      <c r="T4" s="164"/>
-      <c r="U4" s="164"/>
-      <c r="V4" s="165"/>
+      <c r="M4" s="167"/>
+      <c r="N4" s="167"/>
+      <c r="O4" s="167"/>
+      <c r="P4" s="167"/>
+      <c r="Q4" s="167"/>
+      <c r="R4" s="167"/>
+      <c r="S4" s="167"/>
+      <c r="T4" s="167"/>
+      <c r="U4" s="167"/>
+      <c r="V4" s="168"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53"/>
-      <c r="B5" s="147"/>
-      <c r="C5" s="156"/>
-      <c r="D5" s="166"/>
+      <c r="B5" s="150"/>
+      <c r="C5" s="159"/>
+      <c r="D5" s="169"/>
       <c r="E5" s="52" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="134" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="160"/>
-      <c r="H5" s="168"/>
-      <c r="I5" s="162"/>
-      <c r="J5" s="168"/>
+      <c r="G5" s="163"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="165"/>
+      <c r="J5" s="171"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -27932,7 +31303,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="148" t="s">
+      <c r="G62" s="151" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="74"/>
@@ -27950,7 +31321,7 @@
       <c r="S62" s="35"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="149"/>
+      <c r="G63" s="152"/>
       <c r="H63" s="75"/>
       <c r="I63" s="75"/>
       <c r="J63" s="25" t="s">
@@ -27966,7 +31337,7 @@
       <c r="S63" s="38"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="150"/>
+      <c r="G64" s="153"/>
       <c r="H64" s="76"/>
       <c r="I64" s="76"/>
       <c r="J64" s="25" t="s">
@@ -27982,7 +31353,7 @@
       <c r="S64" s="41"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="151" t="s">
+      <c r="G65" s="154" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="77"/>
@@ -28000,7 +31371,7 @@
       <c r="S65" s="41"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="151"/>
+      <c r="G66" s="154"/>
       <c r="H66" s="77"/>
       <c r="I66" s="77"/>
       <c r="J66" s="25" t="s">
@@ -28016,7 +31387,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="152"/>
+      <c r="G67" s="155"/>
       <c r="H67" s="78"/>
       <c r="I67" s="78"/>
       <c r="J67" s="26" t="s">
@@ -28408,15 +31779,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="153">
+      <c r="P1" s="156">
         <v>46057</v>
       </c>
-      <c r="Q1" s="154"/>
-      <c r="R1" s="154"/>
-      <c r="S1" s="154"/>
-      <c r="T1" s="154"/>
-      <c r="U1" s="154"/>
-      <c r="V1" s="155"/>
+      <c r="Q1" s="157"/>
+      <c r="R1" s="157"/>
+      <c r="S1" s="157"/>
+      <c r="T1" s="157"/>
+      <c r="U1" s="157"/>
+      <c r="V1" s="158"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -28439,60 +31810,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="147" t="s">
+      <c r="B4" s="150" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="156" t="s">
+      <c r="C4" s="159" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="166" t="s">
+      <c r="D4" s="169" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="157" t="s">
+      <c r="E4" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="158"/>
-      <c r="G4" s="159" t="s">
+      <c r="F4" s="161"/>
+      <c r="G4" s="162" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="167" t="s">
+      <c r="H4" s="170" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="161" t="s">
+      <c r="I4" s="164" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="167" t="s">
+      <c r="J4" s="170" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="163" t="s">
+      <c r="L4" s="166" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="164"/>
-      <c r="N4" s="164"/>
-      <c r="O4" s="164"/>
-      <c r="P4" s="164"/>
-      <c r="Q4" s="164"/>
-      <c r="R4" s="164"/>
-      <c r="S4" s="164"/>
-      <c r="T4" s="164"/>
-      <c r="U4" s="164"/>
-      <c r="V4" s="165"/>
+      <c r="M4" s="167"/>
+      <c r="N4" s="167"/>
+      <c r="O4" s="167"/>
+      <c r="P4" s="167"/>
+      <c r="Q4" s="167"/>
+      <c r="R4" s="167"/>
+      <c r="S4" s="167"/>
+      <c r="T4" s="167"/>
+      <c r="U4" s="167"/>
+      <c r="V4" s="168"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53"/>
-      <c r="B5" s="147"/>
-      <c r="C5" s="156"/>
-      <c r="D5" s="166"/>
+      <c r="B5" s="150"/>
+      <c r="C5" s="159"/>
+      <c r="D5" s="169"/>
       <c r="E5" s="52" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="137" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="160"/>
-      <c r="H5" s="168"/>
-      <c r="I5" s="162"/>
-      <c r="J5" s="168"/>
+      <c r="G5" s="163"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="165"/>
+      <c r="J5" s="171"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -31430,7 +34801,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="148" t="s">
+      <c r="G62" s="151" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="74"/>
@@ -31448,7 +34819,7 @@
       <c r="S62" s="35"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="149"/>
+      <c r="G63" s="152"/>
       <c r="H63" s="75"/>
       <c r="I63" s="75"/>
       <c r="J63" s="25" t="s">
@@ -31464,7 +34835,7 @@
       <c r="S63" s="38"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="150"/>
+      <c r="G64" s="153"/>
       <c r="H64" s="76"/>
       <c r="I64" s="76"/>
       <c r="J64" s="25" t="s">
@@ -31480,7 +34851,7 @@
       <c r="S64" s="41"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="151" t="s">
+      <c r="G65" s="154" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="77"/>
@@ -31498,7 +34869,7 @@
       <c r="S65" s="41"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="151"/>
+      <c r="G66" s="154"/>
       <c r="H66" s="77"/>
       <c r="I66" s="77"/>
       <c r="J66" s="25" t="s">
@@ -31514,7 +34885,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="152"/>
+      <c r="G67" s="155"/>
       <c r="H67" s="78"/>
       <c r="I67" s="78"/>
       <c r="J67" s="26" t="s">
@@ -31906,15 +35277,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="153">
+      <c r="P1" s="156">
         <v>46058</v>
       </c>
-      <c r="Q1" s="154"/>
-      <c r="R1" s="154"/>
-      <c r="S1" s="154"/>
-      <c r="T1" s="154"/>
-      <c r="U1" s="154"/>
-      <c r="V1" s="155"/>
+      <c r="Q1" s="157"/>
+      <c r="R1" s="157"/>
+      <c r="S1" s="157"/>
+      <c r="T1" s="157"/>
+      <c r="U1" s="157"/>
+      <c r="V1" s="158"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -31937,60 +35308,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="147" t="s">
+      <c r="B4" s="150" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="156" t="s">
+      <c r="C4" s="159" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="166" t="s">
+      <c r="D4" s="169" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="157" t="s">
+      <c r="E4" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="158"/>
-      <c r="G4" s="159" t="s">
+      <c r="F4" s="161"/>
+      <c r="G4" s="162" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="167" t="s">
+      <c r="H4" s="170" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="161" t="s">
+      <c r="I4" s="164" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="167" t="s">
+      <c r="J4" s="170" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="163" t="s">
+      <c r="L4" s="166" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="164"/>
-      <c r="N4" s="164"/>
-      <c r="O4" s="164"/>
-      <c r="P4" s="164"/>
-      <c r="Q4" s="164"/>
-      <c r="R4" s="164"/>
-      <c r="S4" s="164"/>
-      <c r="T4" s="164"/>
-      <c r="U4" s="164"/>
-      <c r="V4" s="165"/>
+      <c r="M4" s="167"/>
+      <c r="N4" s="167"/>
+      <c r="O4" s="167"/>
+      <c r="P4" s="167"/>
+      <c r="Q4" s="167"/>
+      <c r="R4" s="167"/>
+      <c r="S4" s="167"/>
+      <c r="T4" s="167"/>
+      <c r="U4" s="167"/>
+      <c r="V4" s="168"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53"/>
-      <c r="B5" s="147"/>
-      <c r="C5" s="156"/>
-      <c r="D5" s="166"/>
+      <c r="B5" s="150"/>
+      <c r="C5" s="159"/>
+      <c r="D5" s="169"/>
       <c r="E5" s="52" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="137" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="160"/>
-      <c r="H5" s="168"/>
-      <c r="I5" s="162"/>
-      <c r="J5" s="168"/>
+      <c r="G5" s="163"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="165"/>
+      <c r="J5" s="171"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -34951,7 +38322,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="148" t="s">
+      <c r="G62" s="151" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="74"/>
@@ -34969,7 +38340,7 @@
       <c r="S62" s="35"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="149"/>
+      <c r="G63" s="152"/>
       <c r="H63" s="75"/>
       <c r="I63" s="75"/>
       <c r="J63" s="25" t="s">
@@ -34985,7 +38356,7 @@
       <c r="S63" s="38"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="150"/>
+      <c r="G64" s="153"/>
       <c r="H64" s="76"/>
       <c r="I64" s="76"/>
       <c r="J64" s="25" t="s">
@@ -35001,7 +38372,7 @@
       <c r="S64" s="41"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="151" t="s">
+      <c r="G65" s="154" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="77"/>
@@ -35019,7 +38390,7 @@
       <c r="S65" s="41"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="151"/>
+      <c r="G66" s="154"/>
       <c r="H66" s="77"/>
       <c r="I66" s="77"/>
       <c r="J66" s="25" t="s">
@@ -35035,7 +38406,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="152"/>
+      <c r="G67" s="155"/>
       <c r="H67" s="78"/>
       <c r="I67" s="78"/>
       <c r="J67" s="26" t="s">
@@ -35427,15 +38798,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="153">
+      <c r="P1" s="156">
         <v>46058</v>
       </c>
-      <c r="Q1" s="154"/>
-      <c r="R1" s="154"/>
-      <c r="S1" s="154"/>
-      <c r="T1" s="154"/>
-      <c r="U1" s="154"/>
-      <c r="V1" s="155"/>
+      <c r="Q1" s="157"/>
+      <c r="R1" s="157"/>
+      <c r="S1" s="157"/>
+      <c r="T1" s="157"/>
+      <c r="U1" s="157"/>
+      <c r="V1" s="158"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -35458,60 +38829,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="147" t="s">
+      <c r="B4" s="150" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="156" t="s">
+      <c r="C4" s="159" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="166" t="s">
+      <c r="D4" s="169" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="157" t="s">
+      <c r="E4" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="158"/>
-      <c r="G4" s="159" t="s">
+      <c r="F4" s="161"/>
+      <c r="G4" s="162" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="167" t="s">
+      <c r="H4" s="170" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="161" t="s">
+      <c r="I4" s="164" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="167" t="s">
+      <c r="J4" s="170" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="163" t="s">
+      <c r="L4" s="166" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="164"/>
-      <c r="N4" s="164"/>
-      <c r="O4" s="164"/>
-      <c r="P4" s="164"/>
-      <c r="Q4" s="164"/>
-      <c r="R4" s="164"/>
-      <c r="S4" s="164"/>
-      <c r="T4" s="164"/>
-      <c r="U4" s="164"/>
-      <c r="V4" s="165"/>
+      <c r="M4" s="167"/>
+      <c r="N4" s="167"/>
+      <c r="O4" s="167"/>
+      <c r="P4" s="167"/>
+      <c r="Q4" s="167"/>
+      <c r="R4" s="167"/>
+      <c r="S4" s="167"/>
+      <c r="T4" s="167"/>
+      <c r="U4" s="167"/>
+      <c r="V4" s="168"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53"/>
-      <c r="B5" s="147"/>
-      <c r="C5" s="156"/>
-      <c r="D5" s="166"/>
+      <c r="B5" s="150"/>
+      <c r="C5" s="159"/>
+      <c r="D5" s="169"/>
       <c r="E5" s="52" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="160"/>
-      <c r="H5" s="168"/>
-      <c r="I5" s="162"/>
-      <c r="J5" s="168"/>
+      <c r="G5" s="163"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="165"/>
+      <c r="J5" s="171"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -38320,7 +41691,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="148" t="s">
+      <c r="G62" s="151" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="74"/>
@@ -38338,7 +41709,7 @@
       <c r="S62" s="35"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="149"/>
+      <c r="G63" s="152"/>
       <c r="H63" s="75"/>
       <c r="I63" s="75"/>
       <c r="J63" s="25" t="s">
@@ -38354,7 +41725,7 @@
       <c r="S63" s="38"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="150"/>
+      <c r="G64" s="153"/>
       <c r="H64" s="76"/>
       <c r="I64" s="76"/>
       <c r="J64" s="25" t="s">
@@ -38370,7 +41741,7 @@
       <c r="S64" s="41"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="151" t="s">
+      <c r="G65" s="154" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="77"/>
@@ -38388,7 +41759,7 @@
       <c r="S65" s="41"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="151"/>
+      <c r="G66" s="154"/>
       <c r="H66" s="77"/>
       <c r="I66" s="77"/>
       <c r="J66" s="25" t="s">
@@ -38404,7 +41775,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="152"/>
+      <c r="G67" s="155"/>
       <c r="H67" s="78"/>
       <c r="I67" s="78"/>
       <c r="J67" s="26" t="s">
@@ -38796,15 +42167,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="153">
+      <c r="P1" s="156">
         <v>46059</v>
       </c>
-      <c r="Q1" s="154"/>
-      <c r="R1" s="154"/>
-      <c r="S1" s="154"/>
-      <c r="T1" s="154"/>
-      <c r="U1" s="154"/>
-      <c r="V1" s="155"/>
+      <c r="Q1" s="157"/>
+      <c r="R1" s="157"/>
+      <c r="S1" s="157"/>
+      <c r="T1" s="157"/>
+      <c r="U1" s="157"/>
+      <c r="V1" s="158"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -38827,60 +42198,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="147" t="s">
+      <c r="B4" s="150" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="156" t="s">
+      <c r="C4" s="159" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="166" t="s">
+      <c r="D4" s="169" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="157" t="s">
+      <c r="E4" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="158"/>
-      <c r="G4" s="159" t="s">
+      <c r="F4" s="161"/>
+      <c r="G4" s="162" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="167" t="s">
+      <c r="H4" s="170" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="161" t="s">
+      <c r="I4" s="164" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="167" t="s">
+      <c r="J4" s="170" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="163" t="s">
+      <c r="L4" s="166" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="164"/>
-      <c r="N4" s="164"/>
-      <c r="O4" s="164"/>
-      <c r="P4" s="164"/>
-      <c r="Q4" s="164"/>
-      <c r="R4" s="164"/>
-      <c r="S4" s="164"/>
-      <c r="T4" s="164"/>
-      <c r="U4" s="164"/>
-      <c r="V4" s="165"/>
+      <c r="M4" s="167"/>
+      <c r="N4" s="167"/>
+      <c r="O4" s="167"/>
+      <c r="P4" s="167"/>
+      <c r="Q4" s="167"/>
+      <c r="R4" s="167"/>
+      <c r="S4" s="167"/>
+      <c r="T4" s="167"/>
+      <c r="U4" s="167"/>
+      <c r="V4" s="168"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53"/>
-      <c r="B5" s="147"/>
-      <c r="C5" s="156"/>
-      <c r="D5" s="166"/>
+      <c r="B5" s="150"/>
+      <c r="C5" s="159"/>
+      <c r="D5" s="169"/>
       <c r="E5" s="52" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="140" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="160"/>
-      <c r="H5" s="168"/>
-      <c r="I5" s="162"/>
-      <c r="J5" s="168"/>
+      <c r="G5" s="163"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="165"/>
+      <c r="J5" s="171"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -41846,7 +45217,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="148" t="s">
+      <c r="G62" s="151" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="74"/>
@@ -41864,7 +45235,7 @@
       <c r="S62" s="35"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="149"/>
+      <c r="G63" s="152"/>
       <c r="H63" s="75"/>
       <c r="I63" s="75"/>
       <c r="J63" s="25" t="s">
@@ -41880,7 +45251,7 @@
       <c r="S63" s="38"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="150"/>
+      <c r="G64" s="153"/>
       <c r="H64" s="76"/>
       <c r="I64" s="76"/>
       <c r="J64" s="25" t="s">
@@ -41896,7 +45267,7 @@
       <c r="S64" s="41"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="151" t="s">
+      <c r="G65" s="154" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="77"/>
@@ -41914,7 +45285,7 @@
       <c r="S65" s="41"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="151"/>
+      <c r="G66" s="154"/>
       <c r="H66" s="77"/>
       <c r="I66" s="77"/>
       <c r="J66" s="25" t="s">
@@ -41930,7 +45301,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="152"/>
+      <c r="G67" s="155"/>
       <c r="H67" s="78"/>
       <c r="I67" s="78"/>
       <c r="J67" s="26" t="s">
@@ -42322,15 +45693,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="153">
+      <c r="P1" s="156">
         <v>46060</v>
       </c>
-      <c r="Q1" s="154"/>
-      <c r="R1" s="154"/>
-      <c r="S1" s="154"/>
-      <c r="T1" s="154"/>
-      <c r="U1" s="154"/>
-      <c r="V1" s="155"/>
+      <c r="Q1" s="157"/>
+      <c r="R1" s="157"/>
+      <c r="S1" s="157"/>
+      <c r="T1" s="157"/>
+      <c r="U1" s="157"/>
+      <c r="V1" s="158"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -42353,60 +45724,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="147" t="s">
+      <c r="B4" s="150" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="156" t="s">
+      <c r="C4" s="159" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="166" t="s">
+      <c r="D4" s="169" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="157" t="s">
+      <c r="E4" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="158"/>
-      <c r="G4" s="159" t="s">
+      <c r="F4" s="161"/>
+      <c r="G4" s="162" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="167" t="s">
+      <c r="H4" s="170" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="161" t="s">
+      <c r="I4" s="164" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="167" t="s">
+      <c r="J4" s="170" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="163" t="s">
+      <c r="L4" s="166" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="164"/>
-      <c r="N4" s="164"/>
-      <c r="O4" s="164"/>
-      <c r="P4" s="164"/>
-      <c r="Q4" s="164"/>
-      <c r="R4" s="164"/>
-      <c r="S4" s="164"/>
-      <c r="T4" s="164"/>
-      <c r="U4" s="164"/>
-      <c r="V4" s="165"/>
+      <c r="M4" s="167"/>
+      <c r="N4" s="167"/>
+      <c r="O4" s="167"/>
+      <c r="P4" s="167"/>
+      <c r="Q4" s="167"/>
+      <c r="R4" s="167"/>
+      <c r="S4" s="167"/>
+      <c r="T4" s="167"/>
+      <c r="U4" s="167"/>
+      <c r="V4" s="168"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53"/>
-      <c r="B5" s="147"/>
-      <c r="C5" s="156"/>
-      <c r="D5" s="166"/>
+      <c r="B5" s="150"/>
+      <c r="C5" s="159"/>
+      <c r="D5" s="169"/>
       <c r="E5" s="52" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="160"/>
-      <c r="H5" s="168"/>
-      <c r="I5" s="162"/>
-      <c r="J5" s="168"/>
+      <c r="G5" s="163"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="165"/>
+      <c r="J5" s="171"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -45340,7 +48711,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="148" t="s">
+      <c r="G62" s="151" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="74"/>
@@ -45358,7 +48729,7 @@
       <c r="S62" s="35"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="149"/>
+      <c r="G63" s="152"/>
       <c r="H63" s="75"/>
       <c r="I63" s="75"/>
       <c r="J63" s="25" t="s">
@@ -45374,7 +48745,7 @@
       <c r="S63" s="38"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="150"/>
+      <c r="G64" s="153"/>
       <c r="H64" s="76"/>
       <c r="I64" s="76"/>
       <c r="J64" s="25" t="s">
@@ -45390,7 +48761,7 @@
       <c r="S64" s="41"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="151" t="s">
+      <c r="G65" s="154" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="77"/>
@@ -45408,7 +48779,7 @@
       <c r="S65" s="41"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="151"/>
+      <c r="G66" s="154"/>
       <c r="H66" s="77"/>
       <c r="I66" s="77"/>
       <c r="J66" s="25" t="s">
@@ -45424,7 +48795,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="152"/>
+      <c r="G67" s="155"/>
       <c r="H67" s="78"/>
       <c r="I67" s="78"/>
       <c r="J67" s="26" t="s">
@@ -45816,15 +49187,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="153">
+      <c r="P1" s="156">
         <v>46062</v>
       </c>
-      <c r="Q1" s="154"/>
-      <c r="R1" s="154"/>
-      <c r="S1" s="154"/>
-      <c r="T1" s="154"/>
-      <c r="U1" s="154"/>
-      <c r="V1" s="155"/>
+      <c r="Q1" s="157"/>
+      <c r="R1" s="157"/>
+      <c r="S1" s="157"/>
+      <c r="T1" s="157"/>
+      <c r="U1" s="157"/>
+      <c r="V1" s="158"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -45847,60 +49218,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="147" t="s">
+      <c r="B4" s="150" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="156" t="s">
+      <c r="C4" s="159" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="166" t="s">
+      <c r="D4" s="169" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="157" t="s">
+      <c r="E4" s="160" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="158"/>
-      <c r="G4" s="159" t="s">
+      <c r="F4" s="161"/>
+      <c r="G4" s="162" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="167" t="s">
+      <c r="H4" s="170" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="161" t="s">
+      <c r="I4" s="164" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="167" t="s">
+      <c r="J4" s="170" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="163" t="s">
+      <c r="L4" s="166" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="164"/>
-      <c r="N4" s="164"/>
-      <c r="O4" s="164"/>
-      <c r="P4" s="164"/>
-      <c r="Q4" s="164"/>
-      <c r="R4" s="164"/>
-      <c r="S4" s="164"/>
-      <c r="T4" s="164"/>
-      <c r="U4" s="164"/>
-      <c r="V4" s="165"/>
+      <c r="M4" s="167"/>
+      <c r="N4" s="167"/>
+      <c r="O4" s="167"/>
+      <c r="P4" s="167"/>
+      <c r="Q4" s="167"/>
+      <c r="R4" s="167"/>
+      <c r="S4" s="167"/>
+      <c r="T4" s="167"/>
+      <c r="U4" s="167"/>
+      <c r="V4" s="168"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53"/>
-      <c r="B5" s="147"/>
-      <c r="C5" s="156"/>
-      <c r="D5" s="166"/>
+      <c r="B5" s="150"/>
+      <c r="C5" s="159"/>
+      <c r="D5" s="169"/>
       <c r="E5" s="52" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="160"/>
-      <c r="H5" s="168"/>
-      <c r="I5" s="162"/>
-      <c r="J5" s="168"/>
+      <c r="G5" s="163"/>
+      <c r="H5" s="171"/>
+      <c r="I5" s="165"/>
+      <c r="J5" s="171"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -48831,7 +52202,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="148" t="s">
+      <c r="G62" s="151" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="74"/>
@@ -48849,7 +52220,7 @@
       <c r="S62" s="35"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="149"/>
+      <c r="G63" s="152"/>
       <c r="H63" s="75"/>
       <c r="I63" s="75"/>
       <c r="J63" s="25" t="s">
@@ -48865,7 +52236,7 @@
       <c r="S63" s="38"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="150"/>
+      <c r="G64" s="153"/>
       <c r="H64" s="76"/>
       <c r="I64" s="76"/>
       <c r="J64" s="25" t="s">
@@ -48881,7 +52252,7 @@
       <c r="S64" s="41"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="151" t="s">
+      <c r="G65" s="154" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="77"/>
@@ -48899,7 +52270,7 @@
       <c r="S65" s="41"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="151"/>
+      <c r="G66" s="154"/>
       <c r="H66" s="77"/>
       <c r="I66" s="77"/>
       <c r="J66" s="25" t="s">
@@ -48915,7 +52286,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="152"/>
+      <c r="G67" s="155"/>
       <c r="H67" s="78"/>
       <c r="I67" s="78"/>
       <c r="J67" s="26" t="s">

--- a/GBDS FEBRUARY FILES 2026/DSSR GBDS MONTH OF FEBRUARY 2026.xlsx
+++ b/GBDS FEBRUARY FILES 2026/DSSR GBDS MONTH OF FEBRUARY 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS FEBRUARY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5928784-FBBC-4F3C-86D3-FC4592DE9968}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C1C53DB-75FA-4354-9A9A-B13E79BC9BD7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SAMPLE" sheetId="20" r:id="rId1"/>
@@ -29,6 +29,7 @@
     <sheet name="02,14" sheetId="83" r:id="rId14"/>
     <sheet name="EXAMPLE" sheetId="84" r:id="rId15"/>
     <sheet name="02,16" sheetId="85" r:id="rId16"/>
+    <sheet name="02,17" sheetId="86" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'02,02'!$A$1:$W$61</definedName>
@@ -45,6 +46,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="12">'02,13'!$A$1:$W$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="13">'02,14'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="15">'02,16'!$A$1:$Y$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="16">'02,17'!$A$1:$Y$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="14">EXAMPLE!$A$1:$W$92</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SAMPLE!$A$1:$Q$91</definedName>
   </definedNames>
@@ -271,8 +273,94 @@
 </comments>
 </file>
 
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{7A3F04B0-816B-4526-9E71-9A761D0D0DCB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory 
+Bottle Per Case
+All Route</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="0" shapeId="0" xr:uid="{12926FCD-D895-4CE7-89C1-124F2021D452}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Inventory
+Per Case</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="W5" authorId="0" shapeId="0" xr:uid="{097E92BE-EEF4-4952-AE05-4FE6132D9395}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Total Ending Inventory
+Bottle Per Case</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1754" uniqueCount="83">
   <si>
     <t>GUILLERMO BEVERAGE DISTRIBUTION SERVICES</t>
   </si>
@@ -1639,7 +1727,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="210">
+  <cellXfs count="213">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2202,6 +2290,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2623,11 +2720,11 @@
       <c r="J1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="193"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="194"/>
-      <c r="O1" s="195"/>
+      <c r="K1" s="196"/>
+      <c r="L1" s="197"/>
+      <c r="M1" s="197"/>
+      <c r="N1" s="197"/>
+      <c r="O1" s="198"/>
     </row>
     <row r="2" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -2646,44 +2743,44 @@
     <row r="3" spans="1:51" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:51" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="187" t="s">
+      <c r="B4" s="190" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="196" t="s">
+      <c r="C4" s="199" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="197" t="s">
+      <c r="D4" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="198"/>
-      <c r="F4" s="199" t="s">
+      <c r="E4" s="201"/>
+      <c r="F4" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="201" t="s">
+      <c r="G4" s="204" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="203" t="s">
+      <c r="I4" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="204"/>
-      <c r="K4" s="204"/>
-      <c r="L4" s="204"/>
-      <c r="M4" s="204"/>
-      <c r="N4" s="204"/>
-      <c r="O4" s="205"/>
+      <c r="J4" s="207"/>
+      <c r="K4" s="207"/>
+      <c r="L4" s="207"/>
+      <c r="M4" s="207"/>
+      <c r="N4" s="207"/>
+      <c r="O4" s="208"/>
     </row>
     <row r="5" spans="1:51" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53"/>
-      <c r="B5" s="187"/>
-      <c r="C5" s="196"/>
+      <c r="B5" s="190"/>
+      <c r="C5" s="199"/>
       <c r="D5" s="52" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="200"/>
-      <c r="G5" s="202"/>
+      <c r="F5" s="203"/>
+      <c r="G5" s="205"/>
       <c r="I5" s="4" t="s">
         <v>10</v>
       </c>
@@ -4364,7 +4461,7 @@
     </row>
     <row r="59" spans="1:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="60" spans="1:15" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F60" s="188" t="s">
+      <c r="F60" s="191" t="s">
         <v>65</v>
       </c>
       <c r="G60" s="24" t="s">
@@ -4376,7 +4473,7 @@
       <c r="L60" s="35"/>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F61" s="189"/>
+      <c r="F61" s="192"/>
       <c r="G61" s="25" t="s">
         <v>51</v>
       </c>
@@ -4386,7 +4483,7 @@
       <c r="L61" s="38"/>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F62" s="190"/>
+      <c r="F62" s="193"/>
       <c r="G62" s="25" t="s">
         <v>52</v>
       </c>
@@ -4396,7 +4493,7 @@
       <c r="L62" s="41"/>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F63" s="191" t="s">
+      <c r="F63" s="194" t="s">
         <v>64</v>
       </c>
       <c r="G63" s="25" t="s">
@@ -4408,7 +4505,7 @@
       <c r="L63" s="41"/>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="F64" s="191"/>
+      <c r="F64" s="194"/>
       <c r="G64" s="25" t="s">
         <v>51</v>
       </c>
@@ -4418,7 +4515,7 @@
       <c r="L64" s="38"/>
     </row>
     <row r="65" spans="2:15" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F65" s="192"/>
+      <c r="F65" s="195"/>
       <c r="G65" s="26" t="s">
         <v>52</v>
       </c>
@@ -4716,15 +4813,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="193">
+      <c r="P1" s="196">
         <v>46063</v>
       </c>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
-      <c r="V1" s="195"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
+      <c r="V1" s="198"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -4747,60 +4844,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="187" t="s">
+      <c r="B4" s="190" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="196" t="s">
+      <c r="C4" s="199" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="206" t="s">
+      <c r="D4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="197" t="s">
+      <c r="E4" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="198"/>
-      <c r="G4" s="199" t="s">
+      <c r="F4" s="201"/>
+      <c r="G4" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="207" t="s">
+      <c r="H4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="201" t="s">
+      <c r="I4" s="204" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="207" t="s">
+      <c r="J4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="203" t="s">
+      <c r="L4" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="204"/>
-      <c r="N4" s="204"/>
-      <c r="O4" s="204"/>
-      <c r="P4" s="204"/>
-      <c r="Q4" s="204"/>
-      <c r="R4" s="204"/>
-      <c r="S4" s="204"/>
-      <c r="T4" s="204"/>
-      <c r="U4" s="204"/>
-      <c r="V4" s="205"/>
+      <c r="M4" s="207"/>
+      <c r="N4" s="207"/>
+      <c r="O4" s="207"/>
+      <c r="P4" s="207"/>
+      <c r="Q4" s="207"/>
+      <c r="R4" s="207"/>
+      <c r="S4" s="207"/>
+      <c r="T4" s="207"/>
+      <c r="U4" s="207"/>
+      <c r="V4" s="208"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53"/>
-      <c r="B5" s="187"/>
-      <c r="C5" s="196"/>
-      <c r="D5" s="206"/>
+      <c r="B5" s="190"/>
+      <c r="C5" s="199"/>
+      <c r="D5" s="209"/>
       <c r="E5" s="52" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="200"/>
-      <c r="H5" s="208"/>
-      <c r="I5" s="202"/>
-      <c r="J5" s="208"/>
+      <c r="G5" s="203"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="205"/>
+      <c r="J5" s="211"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -7727,7 +7824,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="188" t="s">
+      <c r="G62" s="191" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="74"/>
@@ -7745,7 +7842,7 @@
       <c r="S62" s="35"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="189"/>
+      <c r="G63" s="192"/>
       <c r="H63" s="75"/>
       <c r="I63" s="75"/>
       <c r="J63" s="25" t="s">
@@ -7761,7 +7858,7 @@
       <c r="S63" s="38"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="190"/>
+      <c r="G64" s="193"/>
       <c r="H64" s="76"/>
       <c r="I64" s="76"/>
       <c r="J64" s="25" t="s">
@@ -7777,7 +7874,7 @@
       <c r="S64" s="41"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="191" t="s">
+      <c r="G65" s="194" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="77"/>
@@ -7795,7 +7892,7 @@
       <c r="S65" s="41"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="191"/>
+      <c r="G66" s="194"/>
       <c r="H66" s="77"/>
       <c r="I66" s="77"/>
       <c r="J66" s="25" t="s">
@@ -7811,7 +7908,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="192"/>
+      <c r="G67" s="195"/>
       <c r="H67" s="78"/>
       <c r="I67" s="78"/>
       <c r="J67" s="26" t="s">
@@ -8203,15 +8300,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="193">
+      <c r="P1" s="196">
         <v>46064</v>
       </c>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
-      <c r="V1" s="195"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
+      <c r="V1" s="198"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -8234,60 +8331,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="187" t="s">
+      <c r="B4" s="190" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="196" t="s">
+      <c r="C4" s="199" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="206" t="s">
+      <c r="D4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="197" t="s">
+      <c r="E4" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="198"/>
-      <c r="G4" s="199" t="s">
+      <c r="F4" s="201"/>
+      <c r="G4" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="207" t="s">
+      <c r="H4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="201" t="s">
+      <c r="I4" s="204" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="207" t="s">
+      <c r="J4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="203" t="s">
+      <c r="L4" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="204"/>
-      <c r="N4" s="204"/>
-      <c r="O4" s="204"/>
-      <c r="P4" s="204"/>
-      <c r="Q4" s="204"/>
-      <c r="R4" s="204"/>
-      <c r="S4" s="204"/>
-      <c r="T4" s="204"/>
-      <c r="U4" s="204"/>
-      <c r="V4" s="205"/>
+      <c r="M4" s="207"/>
+      <c r="N4" s="207"/>
+      <c r="O4" s="207"/>
+      <c r="P4" s="207"/>
+      <c r="Q4" s="207"/>
+      <c r="R4" s="207"/>
+      <c r="S4" s="207"/>
+      <c r="T4" s="207"/>
+      <c r="U4" s="207"/>
+      <c r="V4" s="208"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53"/>
-      <c r="B5" s="187"/>
-      <c r="C5" s="196"/>
-      <c r="D5" s="206"/>
+      <c r="B5" s="190"/>
+      <c r="C5" s="199"/>
+      <c r="D5" s="209"/>
       <c r="E5" s="52" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="146" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="200"/>
-      <c r="H5" s="208"/>
-      <c r="I5" s="202"/>
-      <c r="J5" s="208"/>
+      <c r="G5" s="203"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="205"/>
+      <c r="J5" s="211"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -11216,7 +11313,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="188" t="s">
+      <c r="G62" s="191" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="74"/>
@@ -11234,7 +11331,7 @@
       <c r="S62" s="35"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="189"/>
+      <c r="G63" s="192"/>
       <c r="H63" s="75"/>
       <c r="I63" s="75"/>
       <c r="J63" s="25" t="s">
@@ -11250,7 +11347,7 @@
       <c r="S63" s="38"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="190"/>
+      <c r="G64" s="193"/>
       <c r="H64" s="76"/>
       <c r="I64" s="76"/>
       <c r="J64" s="25" t="s">
@@ -11266,7 +11363,7 @@
       <c r="S64" s="41"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="191" t="s">
+      <c r="G65" s="194" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="77"/>
@@ -11284,7 +11381,7 @@
       <c r="S65" s="41"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="191"/>
+      <c r="G66" s="194"/>
       <c r="H66" s="77"/>
       <c r="I66" s="77"/>
       <c r="J66" s="25" t="s">
@@ -11300,7 +11397,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="192"/>
+      <c r="G67" s="195"/>
       <c r="H67" s="78"/>
       <c r="I67" s="78"/>
       <c r="J67" s="26" t="s">
@@ -11692,15 +11789,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="193">
+      <c r="P1" s="196">
         <v>46065</v>
       </c>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
-      <c r="V1" s="195"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
+      <c r="V1" s="198"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -11723,60 +11820,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="187" t="s">
+      <c r="B4" s="190" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="196" t="s">
+      <c r="C4" s="199" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="206" t="s">
+      <c r="D4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="197" t="s">
+      <c r="E4" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="198"/>
-      <c r="G4" s="199" t="s">
+      <c r="F4" s="201"/>
+      <c r="G4" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="207" t="s">
+      <c r="H4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="201" t="s">
+      <c r="I4" s="204" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="207" t="s">
+      <c r="J4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="203" t="s">
+      <c r="L4" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="204"/>
-      <c r="N4" s="204"/>
-      <c r="O4" s="204"/>
-      <c r="P4" s="204"/>
-      <c r="Q4" s="204"/>
-      <c r="R4" s="204"/>
-      <c r="S4" s="204"/>
-      <c r="T4" s="204"/>
-      <c r="U4" s="204"/>
-      <c r="V4" s="205"/>
+      <c r="M4" s="207"/>
+      <c r="N4" s="207"/>
+      <c r="O4" s="207"/>
+      <c r="P4" s="207"/>
+      <c r="Q4" s="207"/>
+      <c r="R4" s="207"/>
+      <c r="S4" s="207"/>
+      <c r="T4" s="207"/>
+      <c r="U4" s="207"/>
+      <c r="V4" s="208"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53"/>
-      <c r="B5" s="187"/>
-      <c r="C5" s="196"/>
-      <c r="D5" s="206"/>
+      <c r="B5" s="190"/>
+      <c r="C5" s="199"/>
+      <c r="D5" s="209"/>
       <c r="E5" s="52" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="146" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="200"/>
-      <c r="H5" s="208"/>
-      <c r="I5" s="202"/>
-      <c r="J5" s="208"/>
+      <c r="G5" s="203"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="205"/>
+      <c r="J5" s="211"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -14687,7 +14784,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="188" t="s">
+      <c r="G62" s="191" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="74"/>
@@ -14705,7 +14802,7 @@
       <c r="S62" s="35"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="189"/>
+      <c r="G63" s="192"/>
       <c r="H63" s="75"/>
       <c r="I63" s="75"/>
       <c r="J63" s="25" t="s">
@@ -14721,7 +14818,7 @@
       <c r="S63" s="38"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="190"/>
+      <c r="G64" s="193"/>
       <c r="H64" s="76"/>
       <c r="I64" s="76"/>
       <c r="J64" s="25" t="s">
@@ -14737,7 +14834,7 @@
       <c r="S64" s="41"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="191" t="s">
+      <c r="G65" s="194" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="77"/>
@@ -14755,7 +14852,7 @@
       <c r="S65" s="41"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="191"/>
+      <c r="G66" s="194"/>
       <c r="H66" s="77"/>
       <c r="I66" s="77"/>
       <c r="J66" s="25" t="s">
@@ -14771,7 +14868,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="192"/>
+      <c r="G67" s="195"/>
       <c r="H67" s="78"/>
       <c r="I67" s="78"/>
       <c r="J67" s="26" t="s">
@@ -15163,15 +15260,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="193">
+      <c r="P1" s="196">
         <v>46066</v>
       </c>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
-      <c r="V1" s="195"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
+      <c r="V1" s="198"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -15194,60 +15291,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="187" t="s">
+      <c r="B4" s="190" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="196" t="s">
+      <c r="C4" s="199" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="206" t="s">
+      <c r="D4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="197" t="s">
+      <c r="E4" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="198"/>
-      <c r="G4" s="199" t="s">
+      <c r="F4" s="201"/>
+      <c r="G4" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="207" t="s">
+      <c r="H4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="201" t="s">
+      <c r="I4" s="204" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="207" t="s">
+      <c r="J4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="203" t="s">
+      <c r="L4" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="204"/>
-      <c r="N4" s="204"/>
-      <c r="O4" s="204"/>
-      <c r="P4" s="204"/>
-      <c r="Q4" s="204"/>
-      <c r="R4" s="204"/>
-      <c r="S4" s="204"/>
-      <c r="T4" s="204"/>
-      <c r="U4" s="204"/>
-      <c r="V4" s="205"/>
+      <c r="M4" s="207"/>
+      <c r="N4" s="207"/>
+      <c r="O4" s="207"/>
+      <c r="P4" s="207"/>
+      <c r="Q4" s="207"/>
+      <c r="R4" s="207"/>
+      <c r="S4" s="207"/>
+      <c r="T4" s="207"/>
+      <c r="U4" s="207"/>
+      <c r="V4" s="208"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53"/>
-      <c r="B5" s="187"/>
-      <c r="C5" s="196"/>
-      <c r="D5" s="206"/>
+      <c r="B5" s="190"/>
+      <c r="C5" s="199"/>
+      <c r="D5" s="209"/>
       <c r="E5" s="52" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="115" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="200"/>
-      <c r="H5" s="208"/>
-      <c r="I5" s="202"/>
-      <c r="J5" s="208"/>
+      <c r="G5" s="203"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="205"/>
+      <c r="J5" s="211"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -18145,7 +18242,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="188" t="s">
+      <c r="G62" s="191" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="74"/>
@@ -18163,7 +18260,7 @@
       <c r="S62" s="35"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="189"/>
+      <c r="G63" s="192"/>
       <c r="H63" s="75"/>
       <c r="I63" s="75"/>
       <c r="J63" s="25" t="s">
@@ -18179,7 +18276,7 @@
       <c r="S63" s="38"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="190"/>
+      <c r="G64" s="193"/>
       <c r="H64" s="76"/>
       <c r="I64" s="76"/>
       <c r="J64" s="25" t="s">
@@ -18195,7 +18292,7 @@
       <c r="S64" s="41"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="191" t="s">
+      <c r="G65" s="194" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="77"/>
@@ -18213,7 +18310,7 @@
       <c r="S65" s="41"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="191"/>
+      <c r="G66" s="194"/>
       <c r="H66" s="77"/>
       <c r="I66" s="77"/>
       <c r="J66" s="25" t="s">
@@ -18229,7 +18326,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="192"/>
+      <c r="G67" s="195"/>
       <c r="H67" s="78"/>
       <c r="I67" s="78"/>
       <c r="J67" s="26" t="s">
@@ -18623,17 +18720,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="193">
+      <c r="P1" s="196">
         <v>46067</v>
       </c>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
-      <c r="V1" s="194"/>
-      <c r="W1" s="194"/>
-      <c r="X1" s="195"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
+      <c r="V1" s="197"/>
+      <c r="W1" s="197"/>
+      <c r="X1" s="198"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -18658,62 +18755,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="187" t="s">
+      <c r="B4" s="190" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="196" t="s">
+      <c r="C4" s="199" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="206" t="s">
+      <c r="D4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="197" t="s">
+      <c r="E4" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="198"/>
-      <c r="G4" s="199" t="s">
+      <c r="F4" s="201"/>
+      <c r="G4" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="207" t="s">
+      <c r="H4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="201" t="s">
+      <c r="I4" s="204" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="207" t="s">
+      <c r="J4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="203" t="s">
+      <c r="L4" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="204"/>
-      <c r="N4" s="204"/>
-      <c r="O4" s="204"/>
-      <c r="P4" s="204"/>
-      <c r="Q4" s="204"/>
-      <c r="R4" s="204"/>
-      <c r="S4" s="204"/>
-      <c r="T4" s="204"/>
-      <c r="U4" s="204"/>
-      <c r="V4" s="209"/>
-      <c r="W4" s="204"/>
-      <c r="X4" s="205"/>
+      <c r="M4" s="207"/>
+      <c r="N4" s="207"/>
+      <c r="O4" s="207"/>
+      <c r="P4" s="207"/>
+      <c r="Q4" s="207"/>
+      <c r="R4" s="207"/>
+      <c r="S4" s="207"/>
+      <c r="T4" s="207"/>
+      <c r="U4" s="207"/>
+      <c r="V4" s="212"/>
+      <c r="W4" s="207"/>
+      <c r="X4" s="208"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53"/>
-      <c r="B5" s="187"/>
-      <c r="C5" s="196"/>
-      <c r="D5" s="206"/>
+      <c r="B5" s="190"/>
+      <c r="C5" s="199"/>
+      <c r="D5" s="209"/>
       <c r="E5" s="52" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="149" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="200"/>
-      <c r="H5" s="208"/>
-      <c r="I5" s="202"/>
-      <c r="J5" s="208"/>
+      <c r="G5" s="203"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="205"/>
+      <c r="J5" s="211"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -22179,7 +22276,7 @@
       <c r="V61" s="185"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="188" t="s">
+      <c r="G62" s="191" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="74"/>
@@ -22197,7 +22294,7 @@
       <c r="S62" s="35"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="189"/>
+      <c r="G63" s="192"/>
       <c r="H63" s="75"/>
       <c r="I63" s="75"/>
       <c r="J63" s="25" t="s">
@@ -22213,7 +22310,7 @@
       <c r="S63" s="38"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="190"/>
+      <c r="G64" s="193"/>
       <c r="H64" s="76"/>
       <c r="I64" s="76"/>
       <c r="J64" s="25" t="s">
@@ -22229,7 +22326,7 @@
       <c r="S64" s="41"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="191" t="s">
+      <c r="G65" s="194" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="77"/>
@@ -22247,7 +22344,7 @@
       <c r="S65" s="41"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="191"/>
+      <c r="G66" s="194"/>
       <c r="H66" s="77"/>
       <c r="I66" s="77"/>
       <c r="J66" s="25" t="s">
@@ -22263,7 +22360,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="192"/>
+      <c r="G67" s="195"/>
       <c r="H67" s="78"/>
       <c r="I67" s="78"/>
       <c r="J67" s="26" t="s">
@@ -22656,13 +22753,13 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="193"/>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
-      <c r="V1" s="195"/>
+      <c r="P1" s="196"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
+      <c r="V1" s="198"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -22685,60 +22782,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="187" t="s">
+      <c r="B4" s="190" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="196" t="s">
+      <c r="C4" s="199" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="206" t="s">
+      <c r="D4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="197" t="s">
+      <c r="E4" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="198"/>
-      <c r="G4" s="199" t="s">
+      <c r="F4" s="201"/>
+      <c r="G4" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="207" t="s">
+      <c r="H4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="201" t="s">
+      <c r="I4" s="204" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="207" t="s">
+      <c r="J4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="203" t="s">
+      <c r="L4" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="204"/>
-      <c r="N4" s="204"/>
-      <c r="O4" s="204"/>
-      <c r="P4" s="204"/>
-      <c r="Q4" s="204"/>
-      <c r="R4" s="204"/>
-      <c r="S4" s="204"/>
-      <c r="T4" s="204"/>
-      <c r="U4" s="204"/>
-      <c r="V4" s="205"/>
+      <c r="M4" s="207"/>
+      <c r="N4" s="207"/>
+      <c r="O4" s="207"/>
+      <c r="P4" s="207"/>
+      <c r="Q4" s="207"/>
+      <c r="R4" s="207"/>
+      <c r="S4" s="207"/>
+      <c r="T4" s="207"/>
+      <c r="U4" s="207"/>
+      <c r="V4" s="208"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53"/>
-      <c r="B5" s="187"/>
-      <c r="C5" s="196"/>
-      <c r="D5" s="206"/>
+      <c r="B5" s="190"/>
+      <c r="C5" s="199"/>
+      <c r="D5" s="209"/>
       <c r="E5" s="52" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="152" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="200"/>
-      <c r="H5" s="208"/>
-      <c r="I5" s="202"/>
-      <c r="J5" s="208"/>
+      <c r="G5" s="203"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="205"/>
+      <c r="J5" s="211"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -24916,7 +25013,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="188" t="s">
+      <c r="G62" s="191" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="74"/>
@@ -24934,7 +25031,7 @@
       <c r="S62" s="35"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="189"/>
+      <c r="G63" s="192"/>
       <c r="H63" s="75"/>
       <c r="I63" s="75"/>
       <c r="J63" s="25" t="s">
@@ -24950,7 +25047,7 @@
       <c r="S63" s="38"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="190"/>
+      <c r="G64" s="193"/>
       <c r="H64" s="76"/>
       <c r="I64" s="76"/>
       <c r="J64" s="25" t="s">
@@ -24966,7 +25063,7 @@
       <c r="S64" s="41"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="191" t="s">
+      <c r="G65" s="194" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="77"/>
@@ -24984,7 +25081,7 @@
       <c r="S65" s="41"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="191"/>
+      <c r="G66" s="194"/>
       <c r="H66" s="77"/>
       <c r="I66" s="77"/>
       <c r="J66" s="25" t="s">
@@ -25000,7 +25097,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="192"/>
+      <c r="G67" s="195"/>
       <c r="H67" s="78"/>
       <c r="I67" s="78"/>
       <c r="J67" s="26" t="s">
@@ -25395,17 +25492,17 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="193">
+      <c r="P1" s="196">
         <v>46069</v>
       </c>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
-      <c r="V1" s="194"/>
-      <c r="W1" s="194"/>
-      <c r="X1" s="195"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
+      <c r="V1" s="197"/>
+      <c r="W1" s="197"/>
+      <c r="X1" s="198"/>
     </row>
     <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -25430,62 +25527,62 @@
     <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="187" t="s">
+      <c r="B4" s="190" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="196" t="s">
+      <c r="C4" s="199" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="206" t="s">
+      <c r="D4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="197" t="s">
+      <c r="E4" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="198"/>
-      <c r="G4" s="199" t="s">
+      <c r="F4" s="201"/>
+      <c r="G4" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="207" t="s">
+      <c r="H4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="201" t="s">
+      <c r="I4" s="204" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="207" t="s">
+      <c r="J4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="203" t="s">
+      <c r="L4" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="204"/>
-      <c r="N4" s="204"/>
-      <c r="O4" s="204"/>
-      <c r="P4" s="204"/>
-      <c r="Q4" s="204"/>
-      <c r="R4" s="204"/>
-      <c r="S4" s="204"/>
-      <c r="T4" s="204"/>
-      <c r="U4" s="204"/>
-      <c r="V4" s="209"/>
-      <c r="W4" s="204"/>
-      <c r="X4" s="205"/>
+      <c r="M4" s="207"/>
+      <c r="N4" s="207"/>
+      <c r="O4" s="207"/>
+      <c r="P4" s="207"/>
+      <c r="Q4" s="207"/>
+      <c r="R4" s="207"/>
+      <c r="S4" s="207"/>
+      <c r="T4" s="207"/>
+      <c r="U4" s="207"/>
+      <c r="V4" s="212"/>
+      <c r="W4" s="207"/>
+      <c r="X4" s="208"/>
     </row>
     <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53"/>
-      <c r="B5" s="187"/>
-      <c r="C5" s="196"/>
-      <c r="D5" s="206"/>
+      <c r="B5" s="190"/>
+      <c r="C5" s="199"/>
+      <c r="D5" s="209"/>
       <c r="E5" s="52" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="155" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="200"/>
-      <c r="H5" s="208"/>
-      <c r="I5" s="202"/>
-      <c r="J5" s="208"/>
+      <c r="G5" s="203"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="205"/>
+      <c r="J5" s="211"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -25650,7 +25747,9 @@
       <c r="B8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="100"/>
+      <c r="C8" s="100">
+        <v>33</v>
+      </c>
       <c r="D8" s="101"/>
       <c r="E8" s="91"/>
       <c r="F8" s="91"/>
@@ -25658,7 +25757,7 @@
       <c r="H8" s="93"/>
       <c r="I8" s="93">
         <f>C8-G8</f>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J8" s="103">
         <f t="shared" ref="J8:J12" si="0">D8-H8</f>
@@ -25690,7 +25789,7 @@
       </c>
       <c r="W8" s="157">
         <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="X8" s="30"/>
       <c r="AL8" s="12"/>
@@ -25725,7 +25824,9 @@
       <c r="B9" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="104"/>
+      <c r="C9" s="104">
+        <v>95</v>
+      </c>
       <c r="D9" s="105"/>
       <c r="E9" s="106"/>
       <c r="F9" s="106"/>
@@ -25733,7 +25834,7 @@
       <c r="H9" s="108"/>
       <c r="I9" s="107">
         <f t="shared" ref="I9:J59" si="4">C9-G9</f>
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J9" s="166">
         <f t="shared" si="0"/>
@@ -25765,7 +25866,7 @@
       </c>
       <c r="W9" s="158">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2280</v>
       </c>
       <c r="X9" s="66"/>
       <c r="AL9" s="12"/>
@@ -25875,15 +25976,19 @@
       <c r="B11" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="100"/>
+      <c r="C11" s="100">
+        <v>64</v>
+      </c>
       <c r="D11" s="101"/>
       <c r="E11" s="91"/>
       <c r="F11" s="91"/>
-      <c r="G11" s="102"/>
+      <c r="G11" s="102">
+        <v>3</v>
+      </c>
       <c r="H11" s="93"/>
       <c r="I11" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="J11" s="103">
         <f t="shared" si="0"/>
@@ -25894,11 +25999,13 @@
       <c r="M11" s="91"/>
       <c r="N11" s="91"/>
       <c r="O11" s="91"/>
-      <c r="P11" s="91"/>
+      <c r="P11" s="91">
+        <v>3</v>
+      </c>
       <c r="Q11" s="92"/>
       <c r="R11" s="129">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S11" s="127">
         <f t="shared" si="1"/>
@@ -25907,15 +26014,15 @@
       <c r="T11" s="44"/>
       <c r="U11" s="28">
         <f>L11*24+N11*24+P11*24</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="V11" s="162">
         <f>U11/24</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W11" s="157">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1464</v>
       </c>
       <c r="X11" s="30"/>
       <c r="AL11" s="12"/>
@@ -25950,7 +26057,9 @@
       <c r="B12" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="100"/>
+      <c r="C12" s="100">
+        <v>1</v>
+      </c>
       <c r="D12" s="101"/>
       <c r="E12" s="91"/>
       <c r="F12" s="91"/>
@@ -25958,7 +26067,7 @@
       <c r="H12" s="93"/>
       <c r="I12" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="103">
         <f t="shared" si="0"/>
@@ -25990,7 +26099,7 @@
       </c>
       <c r="W12" s="157">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="X12" s="30"/>
       <c r="AL12" s="12"/>
@@ -26025,47 +26134,67 @@
       <c r="B13" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="104"/>
-      <c r="D13" s="105"/>
+      <c r="C13" s="104">
+        <v>3552</v>
+      </c>
+      <c r="D13" s="105">
+        <v>3</v>
+      </c>
       <c r="E13" s="106"/>
       <c r="F13" s="106"/>
-      <c r="G13" s="107"/>
-      <c r="H13" s="108"/>
+      <c r="G13" s="107">
+        <v>38</v>
+      </c>
+      <c r="H13" s="108">
+        <v>13</v>
+      </c>
       <c r="I13" s="116">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3514</v>
       </c>
       <c r="J13" s="166">
         <f>D13-H13</f>
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="K13" s="68"/>
-      <c r="L13" s="94"/>
-      <c r="M13" s="94"/>
-      <c r="N13" s="94"/>
-      <c r="O13" s="94"/>
-      <c r="P13" s="94"/>
-      <c r="Q13" s="95"/>
+      <c r="L13" s="94">
+        <v>13</v>
+      </c>
+      <c r="M13" s="94">
+        <v>3</v>
+      </c>
+      <c r="N13" s="94">
+        <v>15</v>
+      </c>
+      <c r="O13" s="94">
+        <v>6</v>
+      </c>
+      <c r="P13" s="94">
+        <v>10</v>
+      </c>
+      <c r="Q13" s="95">
+        <v>4</v>
+      </c>
       <c r="R13" s="169">
         <f>L13+N13+P13</f>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="S13" s="171">
         <f>M13+O13+Q13</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="T13" s="68"/>
       <c r="U13" s="67">
         <f>L13*24+N13*24+P13*24</f>
-        <v>0</v>
+        <v>912</v>
       </c>
       <c r="V13" s="56">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="W13" s="158">
         <f>I13*24+J13</f>
-        <v>0</v>
+        <v>84326</v>
       </c>
       <c r="X13" s="66"/>
       <c r="Y13" s="2"/>
@@ -26107,7 +26236,9 @@
       <c r="B14" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="100"/>
+      <c r="C14" s="100">
+        <v>5</v>
+      </c>
       <c r="D14" s="101"/>
       <c r="E14" s="91"/>
       <c r="F14" s="91"/>
@@ -26115,7 +26246,7 @@
       <c r="H14" s="93"/>
       <c r="I14" s="165">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J14" s="167">
         <f t="shared" si="4"/>
@@ -26147,7 +26278,7 @@
       </c>
       <c r="W14" s="157">
         <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="X14" s="30"/>
       <c r="AL14" s="12"/>
@@ -26407,7 +26538,9 @@
       <c r="B18" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="100"/>
+      <c r="C18" s="100">
+        <v>4</v>
+      </c>
       <c r="D18" s="101"/>
       <c r="E18" s="91"/>
       <c r="F18" s="91"/>
@@ -26415,7 +26548,7 @@
       <c r="H18" s="93"/>
       <c r="I18" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J18" s="103">
         <f t="shared" si="4"/>
@@ -26447,7 +26580,7 @@
       </c>
       <c r="W18" s="157">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X18" s="30"/>
       <c r="AL18" s="12"/>
@@ -26557,7 +26690,9 @@
       <c r="B20" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="100"/>
+      <c r="C20" s="100">
+        <v>4</v>
+      </c>
       <c r="D20" s="101"/>
       <c r="E20" s="91"/>
       <c r="F20" s="91"/>
@@ -26565,7 +26700,7 @@
       <c r="H20" s="93"/>
       <c r="I20" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J20" s="103">
         <f t="shared" si="4"/>
@@ -26597,7 +26732,7 @@
       </c>
       <c r="W20" s="157">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X20" s="30"/>
       <c r="AL20" s="12"/>
@@ -26632,7 +26767,9 @@
       <c r="B21" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="100"/>
+      <c r="C21" s="100">
+        <v>6</v>
+      </c>
       <c r="D21" s="101"/>
       <c r="E21" s="91"/>
       <c r="F21" s="91"/>
@@ -26640,7 +26777,7 @@
       <c r="H21" s="93"/>
       <c r="I21" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J21" s="103">
         <f t="shared" si="4"/>
@@ -26672,7 +26809,7 @@
       </c>
       <c r="W21" s="157">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="X21" s="30"/>
       <c r="AL21" s="12"/>
@@ -26707,7 +26844,9 @@
       <c r="B22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="100"/>
+      <c r="C22" s="100">
+        <v>4</v>
+      </c>
       <c r="D22" s="101"/>
       <c r="E22" s="91"/>
       <c r="F22" s="91"/>
@@ -26715,7 +26854,7 @@
       <c r="H22" s="93"/>
       <c r="I22" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J22" s="103">
         <f t="shared" si="4"/>
@@ -26747,7 +26886,7 @@
       </c>
       <c r="W22" s="157">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="X22" s="30"/>
       <c r="AL22" s="12"/>
@@ -26782,7 +26921,9 @@
       <c r="B23" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="100"/>
+      <c r="C23" s="100">
+        <v>2</v>
+      </c>
       <c r="D23" s="101"/>
       <c r="E23" s="91"/>
       <c r="F23" s="91"/>
@@ -26790,7 +26931,7 @@
       <c r="H23" s="93"/>
       <c r="I23" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" s="103">
         <f t="shared" si="4"/>
@@ -26822,7 +26963,7 @@
       </c>
       <c r="W23" s="157">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X23" s="30"/>
       <c r="Y23" s="2"/>
@@ -26864,7 +27005,9 @@
       <c r="B24" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="100"/>
+      <c r="C24" s="100">
+        <v>48</v>
+      </c>
       <c r="D24" s="101"/>
       <c r="E24" s="91"/>
       <c r="F24" s="91"/>
@@ -26872,7 +27015,7 @@
       <c r="H24" s="93"/>
       <c r="I24" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="J24" s="103">
         <f t="shared" si="4"/>
@@ -26904,7 +27047,7 @@
       </c>
       <c r="W24" s="157">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>1152</v>
       </c>
       <c r="X24" s="30"/>
       <c r="Y24" s="2"/>
@@ -26946,7 +27089,9 @@
       <c r="B25" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="100"/>
+      <c r="C25" s="100">
+        <v>7</v>
+      </c>
       <c r="D25" s="101"/>
       <c r="E25" s="91"/>
       <c r="F25" s="91"/>
@@ -26954,7 +27099,7 @@
       <c r="H25" s="93"/>
       <c r="I25" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J25" s="103">
         <f t="shared" si="4"/>
@@ -26986,7 +27131,7 @@
       </c>
       <c r="W25" s="157">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="X25" s="30"/>
       <c r="AL25" s="12"/>
@@ -27021,19 +27166,23 @@
       <c r="B26" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="100"/>
-      <c r="D26" s="101"/>
+      <c r="C26" s="100">
+        <v>89</v>
+      </c>
+      <c r="D26" s="101">
+        <v>23</v>
+      </c>
       <c r="E26" s="91"/>
       <c r="F26" s="91"/>
       <c r="G26" s="102"/>
       <c r="H26" s="93"/>
       <c r="I26" s="93">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="J26" s="103">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K26" s="44"/>
       <c r="L26" s="91"/>
@@ -27061,7 +27210,7 @@
       </c>
       <c r="W26" s="157">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>2159</v>
       </c>
       <c r="X26" s="30"/>
       <c r="BE26" s="14" t="e">
@@ -27195,6 +27344,3972 @@
       <c r="B29" s="13" t="s">
         <v>25</v>
       </c>
+      <c r="C29" s="100">
+        <v>50</v>
+      </c>
+      <c r="D29" s="101"/>
+      <c r="E29" s="91"/>
+      <c r="F29" s="91"/>
+      <c r="G29" s="102">
+        <v>13</v>
+      </c>
+      <c r="H29" s="93"/>
+      <c r="I29" s="93">
+        <f t="shared" si="4"/>
+        <v>37</v>
+      </c>
+      <c r="J29" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K29" s="45"/>
+      <c r="L29" s="91">
+        <v>9</v>
+      </c>
+      <c r="M29" s="91"/>
+      <c r="N29" s="91">
+        <v>3</v>
+      </c>
+      <c r="O29" s="91"/>
+      <c r="P29" s="91">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="92"/>
+      <c r="R29" s="129">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="S29" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T29" s="45"/>
+      <c r="U29" s="28">
+        <f t="shared" si="5"/>
+        <v>312</v>
+      </c>
+      <c r="V29" s="162">
+        <f t="shared" si="6"/>
+        <v>13</v>
+      </c>
+      <c r="W29" s="157">
+        <f t="shared" si="8"/>
+        <v>888</v>
+      </c>
+      <c r="X29" s="30"/>
+      <c r="Y29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+      <c r="AJ29" s="2"/>
+      <c r="AK29" s="2"/>
+    </row>
+    <row r="30" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="100"/>
+      <c r="D30" s="101"/>
+      <c r="E30" s="91"/>
+      <c r="F30" s="91"/>
+      <c r="G30" s="102"/>
+      <c r="H30" s="93"/>
+      <c r="I30" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K30" s="44"/>
+      <c r="L30" s="91"/>
+      <c r="M30" s="91"/>
+      <c r="N30" s="91"/>
+      <c r="O30" s="91"/>
+      <c r="P30" s="91"/>
+      <c r="Q30" s="92"/>
+      <c r="R30" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T30" s="44"/>
+      <c r="U30" s="28">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V30" s="162">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W30" s="157">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X30" s="30"/>
+    </row>
+    <row r="31" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="100">
+        <v>64</v>
+      </c>
+      <c r="D31" s="101"/>
+      <c r="E31" s="91"/>
+      <c r="F31" s="91"/>
+      <c r="G31" s="102"/>
+      <c r="H31" s="93"/>
+      <c r="I31" s="93">
+        <f t="shared" si="4"/>
+        <v>64</v>
+      </c>
+      <c r="J31" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="44"/>
+      <c r="L31" s="91"/>
+      <c r="M31" s="91"/>
+      <c r="N31" s="91"/>
+      <c r="O31" s="91"/>
+      <c r="P31" s="91"/>
+      <c r="Q31" s="92"/>
+      <c r="R31" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S31" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T31" s="44"/>
+      <c r="U31" s="28">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V31" s="162">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W31" s="157">
+        <f t="shared" si="8"/>
+        <v>1536</v>
+      </c>
+      <c r="X31" s="30"/>
+    </row>
+    <row r="32" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="100"/>
+      <c r="D32" s="101"/>
+      <c r="E32" s="91"/>
+      <c r="F32" s="91"/>
+      <c r="G32" s="102"/>
+      <c r="H32" s="93"/>
+      <c r="I32" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="44"/>
+      <c r="L32" s="91"/>
+      <c r="M32" s="91"/>
+      <c r="N32" s="91"/>
+      <c r="O32" s="91"/>
+      <c r="P32" s="91"/>
+      <c r="Q32" s="92"/>
+      <c r="R32" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T32" s="44"/>
+      <c r="U32" s="28">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V32" s="162">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W32" s="157">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="30"/>
+    </row>
+    <row r="33" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="100"/>
+      <c r="D33" s="101"/>
+      <c r="E33" s="91"/>
+      <c r="F33" s="91"/>
+      <c r="G33" s="102"/>
+      <c r="H33" s="93"/>
+      <c r="I33" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K33" s="44"/>
+      <c r="L33" s="91"/>
+      <c r="M33" s="91"/>
+      <c r="N33" s="91"/>
+      <c r="O33" s="91"/>
+      <c r="P33" s="91"/>
+      <c r="Q33" s="92"/>
+      <c r="R33" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S33" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T33" s="44"/>
+      <c r="U33" s="28">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V33" s="162">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W33" s="157">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X33" s="30"/>
+    </row>
+    <row r="34" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" s="100"/>
+      <c r="D34" s="101"/>
+      <c r="E34" s="91"/>
+      <c r="F34" s="91"/>
+      <c r="G34" s="102"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="44"/>
+      <c r="L34" s="91"/>
+      <c r="M34" s="91"/>
+      <c r="N34" s="91"/>
+      <c r="O34" s="91"/>
+      <c r="P34" s="91"/>
+      <c r="Q34" s="92"/>
+      <c r="R34" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S34" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T34" s="44"/>
+      <c r="U34" s="28">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V34" s="162">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W34" s="157">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="30"/>
+    </row>
+    <row r="35" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <f t="shared" si="3"/>
+        <v>28</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="100">
+        <v>109</v>
+      </c>
+      <c r="D35" s="101">
+        <v>17</v>
+      </c>
+      <c r="E35" s="91"/>
+      <c r="F35" s="91"/>
+      <c r="G35" s="102">
+        <v>5</v>
+      </c>
+      <c r="H35" s="93"/>
+      <c r="I35" s="93">
+        <f t="shared" si="4"/>
+        <v>104</v>
+      </c>
+      <c r="J35" s="103">
+        <f t="shared" si="4"/>
+        <v>17</v>
+      </c>
+      <c r="K35" s="44"/>
+      <c r="L35" s="91">
+        <v>5</v>
+      </c>
+      <c r="M35" s="91"/>
+      <c r="N35" s="91"/>
+      <c r="O35" s="91"/>
+      <c r="P35" s="91"/>
+      <c r="Q35" s="92"/>
+      <c r="R35" s="129">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="S35" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T35" s="44"/>
+      <c r="U35" s="28">
+        <f t="shared" si="5"/>
+        <v>120</v>
+      </c>
+      <c r="V35" s="162">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="W35" s="157">
+        <f t="shared" si="8"/>
+        <v>2513</v>
+      </c>
+      <c r="X35" s="30"/>
+    </row>
+    <row r="36" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <f t="shared" si="3"/>
+        <v>29</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="100"/>
+      <c r="D36" s="101"/>
+      <c r="E36" s="91"/>
+      <c r="F36" s="91"/>
+      <c r="G36" s="102"/>
+      <c r="H36" s="93"/>
+      <c r="I36" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="44"/>
+      <c r="L36" s="91"/>
+      <c r="M36" s="91"/>
+      <c r="N36" s="91"/>
+      <c r="O36" s="91"/>
+      <c r="P36" s="91"/>
+      <c r="Q36" s="92"/>
+      <c r="R36" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S36" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T36" s="44"/>
+      <c r="U36" s="28">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="162">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="157">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="30"/>
+    </row>
+    <row r="37" spans="1:26" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C37" s="100"/>
+      <c r="D37" s="101"/>
+      <c r="E37" s="91"/>
+      <c r="F37" s="91"/>
+      <c r="G37" s="102"/>
+      <c r="H37" s="93"/>
+      <c r="I37" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J37" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K37" s="44"/>
+      <c r="L37" s="91"/>
+      <c r="M37" s="91"/>
+      <c r="N37" s="91"/>
+      <c r="O37" s="91"/>
+      <c r="P37" s="91"/>
+      <c r="Q37" s="92"/>
+      <c r="R37" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S37" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T37" s="44"/>
+      <c r="U37" s="28">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V37" s="162">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W37" s="157">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X37" s="30"/>
+    </row>
+    <row r="38" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <f t="shared" si="3"/>
+        <v>31</v>
+      </c>
+      <c r="B38" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="104">
+        <v>4535</v>
+      </c>
+      <c r="D38" s="105">
+        <v>2</v>
+      </c>
+      <c r="E38" s="106"/>
+      <c r="F38" s="106"/>
+      <c r="G38" s="107">
+        <v>163</v>
+      </c>
+      <c r="H38" s="108"/>
+      <c r="I38" s="116">
+        <f t="shared" si="4"/>
+        <v>4372</v>
+      </c>
+      <c r="J38" s="166">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="K38" s="64"/>
+      <c r="L38" s="94">
+        <v>118</v>
+      </c>
+      <c r="M38" s="94"/>
+      <c r="N38" s="94"/>
+      <c r="O38" s="94"/>
+      <c r="P38" s="94">
+        <v>45</v>
+      </c>
+      <c r="Q38" s="95"/>
+      <c r="R38" s="169">
+        <f t="shared" si="7"/>
+        <v>163</v>
+      </c>
+      <c r="S38" s="171">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="64"/>
+      <c r="U38" s="67">
+        <f>L38*6+N38*6+P38*6</f>
+        <v>978</v>
+      </c>
+      <c r="V38" s="172">
+        <f>U38/6</f>
+        <v>163</v>
+      </c>
+      <c r="W38" s="158">
+        <f>I38*6+J38</f>
+        <v>26234</v>
+      </c>
+      <c r="X38" s="66"/>
+    </row>
+    <row r="39" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <f t="shared" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="100">
+        <v>4</v>
+      </c>
+      <c r="D39" s="101"/>
+      <c r="E39" s="91"/>
+      <c r="F39" s="91"/>
+      <c r="G39" s="102"/>
+      <c r="H39" s="93"/>
+      <c r="I39" s="165">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J39" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K39" s="44"/>
+      <c r="L39" s="91"/>
+      <c r="M39" s="91"/>
+      <c r="N39" s="91"/>
+      <c r="O39" s="91"/>
+      <c r="P39" s="91"/>
+      <c r="Q39" s="92"/>
+      <c r="R39" s="168">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S39" s="170">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T39" s="44"/>
+      <c r="U39" s="28">
+        <f t="shared" ref="U39:U41" si="9">L39*24+N39*24+P39*24</f>
+        <v>0</v>
+      </c>
+      <c r="V39" s="173">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W39" s="157">
+        <f t="shared" ref="W39:W41" si="10">I39*24+J39</f>
+        <v>96</v>
+      </c>
+      <c r="X39" s="30"/>
+    </row>
+    <row r="40" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="B40" s="117" t="s">
+        <v>76</v>
+      </c>
+      <c r="C40" s="118"/>
+      <c r="D40" s="119"/>
+      <c r="E40" s="120"/>
+      <c r="F40" s="120"/>
+      <c r="G40" s="121"/>
+      <c r="H40" s="116"/>
+      <c r="I40" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="44"/>
+      <c r="L40" s="91"/>
+      <c r="M40" s="91"/>
+      <c r="N40" s="91"/>
+      <c r="O40" s="91"/>
+      <c r="P40" s="91"/>
+      <c r="Q40" s="92"/>
+      <c r="R40" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="44"/>
+      <c r="U40" s="122">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="162">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W40" s="159">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="X40" s="164"/>
+    </row>
+    <row r="41" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <f t="shared" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="B41" s="54" t="s">
+        <v>35</v>
+      </c>
+      <c r="C41" s="104">
+        <v>698</v>
+      </c>
+      <c r="D41" s="105"/>
+      <c r="E41" s="106"/>
+      <c r="F41" s="106"/>
+      <c r="G41" s="107"/>
+      <c r="H41" s="108"/>
+      <c r="I41" s="116">
+        <f t="shared" si="4"/>
+        <v>698</v>
+      </c>
+      <c r="J41" s="166">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K41" s="64"/>
+      <c r="L41" s="91"/>
+      <c r="M41" s="91"/>
+      <c r="N41" s="91"/>
+      <c r="O41" s="91"/>
+      <c r="P41" s="91"/>
+      <c r="Q41" s="92"/>
+      <c r="R41" s="174">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S41" s="171">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T41" s="64"/>
+      <c r="U41" s="55">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="V41" s="56">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W41" s="56">
+        <f t="shared" si="10"/>
+        <v>16752</v>
+      </c>
+      <c r="X41" s="66"/>
+    </row>
+    <row r="42" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="B42" s="59" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="109">
+        <v>1678</v>
+      </c>
+      <c r="D42" s="110"/>
+      <c r="E42" s="96"/>
+      <c r="F42" s="96"/>
+      <c r="G42" s="111">
+        <v>2</v>
+      </c>
+      <c r="H42" s="112"/>
+      <c r="I42" s="111">
+        <f t="shared" si="4"/>
+        <v>1676</v>
+      </c>
+      <c r="J42" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="69"/>
+      <c r="L42" s="96">
+        <v>2</v>
+      </c>
+      <c r="M42" s="96"/>
+      <c r="N42" s="96"/>
+      <c r="O42" s="96"/>
+      <c r="P42" s="96"/>
+      <c r="Q42" s="97"/>
+      <c r="R42" s="175">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="S42" s="180">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T42" s="69"/>
+      <c r="U42" s="60">
+        <f>L42*12+N42*12+P42*12</f>
+        <v>24</v>
+      </c>
+      <c r="V42" s="61">
+        <f>U42/12</f>
+        <v>2</v>
+      </c>
+      <c r="W42" s="160">
+        <f>I42*12+J42</f>
+        <v>20112</v>
+      </c>
+      <c r="X42" s="63"/>
+    </row>
+    <row r="43" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="100"/>
+      <c r="D43" s="101"/>
+      <c r="E43" s="91"/>
+      <c r="F43" s="91"/>
+      <c r="G43" s="102"/>
+      <c r="H43" s="93"/>
+      <c r="I43" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J43" s="166">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="44"/>
+      <c r="L43" s="91"/>
+      <c r="M43" s="91"/>
+      <c r="N43" s="91"/>
+      <c r="O43" s="91"/>
+      <c r="P43" s="91"/>
+      <c r="Q43" s="92"/>
+      <c r="R43" s="174">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="179">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="44"/>
+      <c r="U43" s="28"/>
+      <c r="V43" s="27"/>
+      <c r="W43" s="157"/>
+      <c r="X43" s="30"/>
+    </row>
+    <row r="44" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <f t="shared" si="3"/>
+        <v>37</v>
+      </c>
+      <c r="B44" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="104">
+        <f>28565</f>
+        <v>28565</v>
+      </c>
+      <c r="D44" s="105">
+        <v>4</v>
+      </c>
+      <c r="E44" s="106">
+        <v>3672</v>
+      </c>
+      <c r="F44" s="106"/>
+      <c r="G44" s="107">
+        <v>1029</v>
+      </c>
+      <c r="H44" s="108"/>
+      <c r="I44" s="93">
+        <f>C44+E44-G44</f>
+        <v>31208</v>
+      </c>
+      <c r="J44" s="181">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="K44" s="64"/>
+      <c r="L44" s="94">
+        <v>287</v>
+      </c>
+      <c r="M44" s="94"/>
+      <c r="N44" s="94">
+        <v>439</v>
+      </c>
+      <c r="O44" s="94"/>
+      <c r="P44" s="94">
+        <v>303</v>
+      </c>
+      <c r="Q44" s="95"/>
+      <c r="R44" s="176">
+        <f t="shared" si="7"/>
+        <v>1029</v>
+      </c>
+      <c r="S44" s="180">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T44" s="64"/>
+      <c r="U44" s="67">
+        <f>L44*6+N44*6+P44*6</f>
+        <v>6174</v>
+      </c>
+      <c r="V44" s="162">
+        <f>U44/6</f>
+        <v>1029</v>
+      </c>
+      <c r="W44" s="158">
+        <f>I44*6+J44</f>
+        <v>187252</v>
+      </c>
+      <c r="X44" s="66"/>
+      <c r="Z44" s="50"/>
+    </row>
+    <row r="45" spans="1:26" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3">
+        <f t="shared" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="100"/>
+      <c r="D45" s="101"/>
+      <c r="E45" s="91"/>
+      <c r="F45" s="91"/>
+      <c r="G45" s="102"/>
+      <c r="H45" s="93"/>
+      <c r="I45" s="116">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J45" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="44"/>
+      <c r="L45" s="91"/>
+      <c r="M45" s="91"/>
+      <c r="N45" s="91"/>
+      <c r="O45" s="91"/>
+      <c r="P45" s="91"/>
+      <c r="Q45" s="92"/>
+      <c r="R45" s="168">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="179">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T45" s="44"/>
+      <c r="U45" s="28"/>
+      <c r="V45" s="172"/>
+      <c r="W45" s="157"/>
+      <c r="X45" s="30"/>
+    </row>
+    <row r="46" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <f t="shared" si="3"/>
+        <v>39</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="100"/>
+      <c r="D46" s="101"/>
+      <c r="E46" s="91"/>
+      <c r="F46" s="91"/>
+      <c r="G46" s="102"/>
+      <c r="H46" s="93"/>
+      <c r="I46" s="165">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K46" s="44"/>
+      <c r="L46" s="91"/>
+      <c r="M46" s="91"/>
+      <c r="N46" s="91"/>
+      <c r="O46" s="91"/>
+      <c r="P46" s="91"/>
+      <c r="Q46" s="92"/>
+      <c r="R46" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S46" s="178">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="44"/>
+      <c r="U46" s="28">
+        <f t="shared" ref="U46:U47" si="11">L46*24+N46*24+P46*24</f>
+        <v>0</v>
+      </c>
+      <c r="V46" s="173">
+        <f t="shared" ref="V46:V47" si="12">U46/24</f>
+        <v>0</v>
+      </c>
+      <c r="W46" s="157">
+        <f t="shared" ref="W46:W47" si="13">I46*24+J46</f>
+        <v>0</v>
+      </c>
+      <c r="X46" s="30"/>
+    </row>
+    <row r="47" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="100"/>
+      <c r="D47" s="101"/>
+      <c r="E47" s="91"/>
+      <c r="F47" s="91"/>
+      <c r="G47" s="102"/>
+      <c r="H47" s="93"/>
+      <c r="I47" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J47" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K47" s="44"/>
+      <c r="L47" s="91"/>
+      <c r="M47" s="91"/>
+      <c r="N47" s="91"/>
+      <c r="O47" s="91"/>
+      <c r="P47" s="91"/>
+      <c r="Q47" s="92"/>
+      <c r="R47" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="44"/>
+      <c r="U47" s="28">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="V47" s="162">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="W47" s="157">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="X47" s="30"/>
+    </row>
+    <row r="48" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C48" s="100">
+        <v>2365</v>
+      </c>
+      <c r="D48" s="101">
+        <v>5</v>
+      </c>
+      <c r="E48" s="91"/>
+      <c r="F48" s="91"/>
+      <c r="G48" s="102"/>
+      <c r="H48" s="93"/>
+      <c r="I48" s="93">
+        <f t="shared" si="4"/>
+        <v>2365</v>
+      </c>
+      <c r="J48" s="103">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="K48" s="44"/>
+      <c r="L48" s="91"/>
+      <c r="M48" s="91"/>
+      <c r="N48" s="91"/>
+      <c r="O48" s="91"/>
+      <c r="P48" s="91"/>
+      <c r="Q48" s="92"/>
+      <c r="R48" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S48" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T48" s="44"/>
+      <c r="U48" s="28">
+        <f>L48*6+N48*6+P48*6</f>
+        <v>0</v>
+      </c>
+      <c r="V48" s="162">
+        <f>U48/6</f>
+        <v>0</v>
+      </c>
+      <c r="W48" s="157">
+        <f>I48*6+J48</f>
+        <v>14195</v>
+      </c>
+      <c r="X48" s="30"/>
+    </row>
+    <row r="49" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="100"/>
+      <c r="D49" s="101"/>
+      <c r="E49" s="91"/>
+      <c r="F49" s="91"/>
+      <c r="G49" s="102"/>
+      <c r="H49" s="93"/>
+      <c r="I49" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J49" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="44"/>
+      <c r="L49" s="91"/>
+      <c r="M49" s="91"/>
+      <c r="N49" s="91"/>
+      <c r="O49" s="91"/>
+      <c r="P49" s="91"/>
+      <c r="Q49" s="92"/>
+      <c r="R49" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T49" s="44"/>
+      <c r="U49" s="28">
+        <f t="shared" ref="U49:U51" si="14">L49*24+N49*24+P49*24</f>
+        <v>0</v>
+      </c>
+      <c r="V49" s="162">
+        <f t="shared" ref="V49:V51" si="15">U49/24</f>
+        <v>0</v>
+      </c>
+      <c r="W49" s="157">
+        <f t="shared" ref="W49:W51" si="16">I49*24+J49</f>
+        <v>0</v>
+      </c>
+      <c r="X49" s="30"/>
+    </row>
+    <row r="50" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3">
+        <f t="shared" si="3"/>
+        <v>43</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="100"/>
+      <c r="D50" s="101"/>
+      <c r="E50" s="91"/>
+      <c r="F50" s="91"/>
+      <c r="G50" s="102"/>
+      <c r="H50" s="93"/>
+      <c r="I50" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="44"/>
+      <c r="L50" s="91"/>
+      <c r="M50" s="91"/>
+      <c r="N50" s="91"/>
+      <c r="O50" s="91"/>
+      <c r="P50" s="91"/>
+      <c r="Q50" s="92"/>
+      <c r="R50" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T50" s="44"/>
+      <c r="U50" s="28">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V50" s="162">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W50" s="157">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X50" s="30"/>
+    </row>
+    <row r="51" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="B51" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="100"/>
+      <c r="D51" s="101"/>
+      <c r="E51" s="91"/>
+      <c r="F51" s="91"/>
+      <c r="G51" s="102"/>
+      <c r="H51" s="93"/>
+      <c r="I51" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="44"/>
+      <c r="L51" s="91"/>
+      <c r="M51" s="91"/>
+      <c r="N51" s="91"/>
+      <c r="O51" s="91"/>
+      <c r="P51" s="91"/>
+      <c r="Q51" s="92"/>
+      <c r="R51" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T51" s="44"/>
+      <c r="U51" s="28">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="V51" s="162">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="W51" s="157">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="X51" s="30"/>
+    </row>
+    <row r="52" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="100">
+        <v>34</v>
+      </c>
+      <c r="D52" s="101"/>
+      <c r="E52" s="91"/>
+      <c r="F52" s="91"/>
+      <c r="G52" s="102"/>
+      <c r="H52" s="93"/>
+      <c r="I52" s="93">
+        <f t="shared" si="4"/>
+        <v>34</v>
+      </c>
+      <c r="J52" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="44"/>
+      <c r="L52" s="91"/>
+      <c r="M52" s="91"/>
+      <c r="N52" s="91"/>
+      <c r="O52" s="91"/>
+      <c r="P52" s="91"/>
+      <c r="Q52" s="92"/>
+      <c r="R52" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T52" s="44"/>
+      <c r="U52" s="28">
+        <f>L52*6+N52*6+P52*6</f>
+        <v>0</v>
+      </c>
+      <c r="V52" s="162">
+        <f>U52/6</f>
+        <v>0</v>
+      </c>
+      <c r="W52" s="157">
+        <f>I52*6+J52</f>
+        <v>204</v>
+      </c>
+      <c r="X52" s="30"/>
+    </row>
+    <row r="53" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3">
+        <f t="shared" si="3"/>
+        <v>46</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C53" s="100"/>
+      <c r="D53" s="101"/>
+      <c r="E53" s="91"/>
+      <c r="F53" s="91"/>
+      <c r="G53" s="102"/>
+      <c r="H53" s="93"/>
+      <c r="I53" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="44"/>
+      <c r="L53" s="91"/>
+      <c r="M53" s="91"/>
+      <c r="N53" s="91"/>
+      <c r="O53" s="91"/>
+      <c r="P53" s="91"/>
+      <c r="Q53" s="92"/>
+      <c r="R53" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="44"/>
+      <c r="U53" s="28">
+        <f t="shared" ref="U53:U54" si="17">L53*24+N53*24+P53*24</f>
+        <v>0</v>
+      </c>
+      <c r="V53" s="162">
+        <f t="shared" ref="V53:V54" si="18">U53/24</f>
+        <v>0</v>
+      </c>
+      <c r="W53" s="157">
+        <f t="shared" ref="W53:W54" si="19">I53*24+J53</f>
+        <v>0</v>
+      </c>
+      <c r="X53" s="30"/>
+    </row>
+    <row r="54" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="100">
+        <v>2</v>
+      </c>
+      <c r="D54" s="101"/>
+      <c r="E54" s="91"/>
+      <c r="F54" s="91"/>
+      <c r="G54" s="102"/>
+      <c r="H54" s="93"/>
+      <c r="I54" s="93">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J54" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="44"/>
+      <c r="L54" s="91"/>
+      <c r="M54" s="91"/>
+      <c r="N54" s="91"/>
+      <c r="O54" s="91"/>
+      <c r="P54" s="91"/>
+      <c r="Q54" s="92"/>
+      <c r="R54" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T54" s="44"/>
+      <c r="U54" s="28">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="V54" s="162">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="W54" s="157">
+        <f t="shared" si="19"/>
+        <v>48</v>
+      </c>
+      <c r="X54" s="30"/>
+    </row>
+    <row r="55" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3">
+        <f t="shared" si="3"/>
+        <v>48</v>
+      </c>
+      <c r="B55" s="13"/>
+      <c r="C55" s="100"/>
+      <c r="D55" s="101"/>
+      <c r="E55" s="91"/>
+      <c r="F55" s="91"/>
+      <c r="G55" s="102"/>
+      <c r="H55" s="93"/>
+      <c r="I55" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J55" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="44"/>
+      <c r="L55" s="91"/>
+      <c r="M55" s="91"/>
+      <c r="N55" s="91"/>
+      <c r="O55" s="91"/>
+      <c r="P55" s="91"/>
+      <c r="Q55" s="92"/>
+      <c r="R55" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="44"/>
+      <c r="U55" s="28"/>
+      <c r="V55" s="162"/>
+      <c r="W55" s="157"/>
+      <c r="X55" s="30"/>
+    </row>
+    <row r="56" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="B56" s="13"/>
+      <c r="C56" s="100"/>
+      <c r="D56" s="101"/>
+      <c r="E56" s="91"/>
+      <c r="F56" s="91"/>
+      <c r="G56" s="102"/>
+      <c r="H56" s="93"/>
+      <c r="I56" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="44"/>
+      <c r="L56" s="91"/>
+      <c r="M56" s="91"/>
+      <c r="N56" s="91"/>
+      <c r="O56" s="91"/>
+      <c r="P56" s="91"/>
+      <c r="Q56" s="92"/>
+      <c r="R56" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T56" s="44"/>
+      <c r="U56" s="28"/>
+      <c r="V56" s="162"/>
+      <c r="W56" s="157"/>
+      <c r="X56" s="30"/>
+    </row>
+    <row r="57" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="B57" s="13"/>
+      <c r="C57" s="100"/>
+      <c r="D57" s="101"/>
+      <c r="E57" s="91"/>
+      <c r="F57" s="91"/>
+      <c r="G57" s="102"/>
+      <c r="H57" s="93"/>
+      <c r="I57" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="44"/>
+      <c r="L57" s="91"/>
+      <c r="M57" s="91"/>
+      <c r="N57" s="91"/>
+      <c r="O57" s="91"/>
+      <c r="P57" s="91"/>
+      <c r="Q57" s="92"/>
+      <c r="R57" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T57" s="44"/>
+      <c r="U57" s="28"/>
+      <c r="V57" s="162"/>
+      <c r="W57" s="157"/>
+      <c r="X57" s="30"/>
+    </row>
+    <row r="58" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3">
+        <f t="shared" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="B58" s="13"/>
+      <c r="C58" s="100"/>
+      <c r="D58" s="101"/>
+      <c r="E58" s="91"/>
+      <c r="F58" s="91"/>
+      <c r="G58" s="102"/>
+      <c r="H58" s="93"/>
+      <c r="I58" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="44"/>
+      <c r="L58" s="91"/>
+      <c r="M58" s="91"/>
+      <c r="N58" s="91"/>
+      <c r="O58" s="91"/>
+      <c r="P58" s="91"/>
+      <c r="Q58" s="92"/>
+      <c r="R58" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T58" s="44"/>
+      <c r="U58" s="28"/>
+      <c r="V58" s="162"/>
+      <c r="W58" s="157"/>
+      <c r="X58" s="30"/>
+    </row>
+    <row r="59" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3">
+        <f t="shared" si="3"/>
+        <v>52</v>
+      </c>
+      <c r="B59" s="13"/>
+      <c r="C59" s="100"/>
+      <c r="D59" s="101"/>
+      <c r="E59" s="91"/>
+      <c r="F59" s="91"/>
+      <c r="G59" s="102"/>
+      <c r="H59" s="93"/>
+      <c r="I59" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="44"/>
+      <c r="L59" s="91"/>
+      <c r="M59" s="91"/>
+      <c r="N59" s="91"/>
+      <c r="O59" s="91"/>
+      <c r="P59" s="91"/>
+      <c r="Q59" s="92"/>
+      <c r="R59" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T59" s="44"/>
+      <c r="U59" s="28"/>
+      <c r="V59" s="162"/>
+      <c r="W59" s="157"/>
+      <c r="X59" s="30"/>
+    </row>
+    <row r="60" spans="1:24" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" s="46">
+        <f>SUM(C8:C59)</f>
+        <v>42018</v>
+      </c>
+      <c r="D60" s="71">
+        <f>SUM(D8:D59)</f>
+        <v>54</v>
+      </c>
+      <c r="E60" s="47">
+        <f>SUM(E8:E59)</f>
+        <v>3672</v>
+      </c>
+      <c r="F60" s="47"/>
+      <c r="G60" s="31">
+        <f>SUM(G8:G59)</f>
+        <v>1253</v>
+      </c>
+      <c r="H60" s="73">
+        <f>SUM(H8:H59)</f>
+        <v>13</v>
+      </c>
+      <c r="I60" s="73">
+        <f>SUM(I8:I59)</f>
+        <v>44437</v>
+      </c>
+      <c r="J60" s="48">
+        <f>SUM(J8:J59)</f>
+        <v>41</v>
+      </c>
+      <c r="K60" s="49"/>
+      <c r="L60" s="98">
+        <f t="shared" ref="L60:S60" si="20">SUM(L8:L59)</f>
+        <v>434</v>
+      </c>
+      <c r="M60" s="98">
+        <f t="shared" si="20"/>
+        <v>3</v>
+      </c>
+      <c r="N60" s="98">
+        <f t="shared" si="20"/>
+        <v>457</v>
+      </c>
+      <c r="O60" s="98">
+        <f t="shared" si="20"/>
+        <v>6</v>
+      </c>
+      <c r="P60" s="98">
+        <f t="shared" si="20"/>
+        <v>362</v>
+      </c>
+      <c r="Q60" s="99">
+        <f t="shared" si="20"/>
+        <v>4</v>
+      </c>
+      <c r="R60" s="128">
+        <f t="shared" si="20"/>
+        <v>1253</v>
+      </c>
+      <c r="S60" s="125">
+        <f t="shared" si="20"/>
+        <v>13</v>
+      </c>
+      <c r="T60" s="49"/>
+      <c r="U60" s="46">
+        <f>SUM(U8:U59)</f>
+        <v>8592</v>
+      </c>
+      <c r="V60" s="184">
+        <f>SUM(V8:V59)</f>
+        <v>1253</v>
+      </c>
+      <c r="W60" s="161">
+        <f>SUM(W8:W59)</f>
+        <v>362795</v>
+      </c>
+      <c r="X60" s="48"/>
+    </row>
+    <row r="61" spans="1:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="V61" s="185"/>
+    </row>
+    <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G62" s="191" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" s="74"/>
+      <c r="I62" s="74"/>
+      <c r="J62" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="L62" s="33"/>
+      <c r="M62" s="79"/>
+      <c r="N62" s="34"/>
+      <c r="O62" s="34"/>
+      <c r="P62" s="34"/>
+      <c r="Q62" s="85"/>
+      <c r="R62" s="85"/>
+      <c r="S62" s="35"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G63" s="192"/>
+      <c r="H63" s="75"/>
+      <c r="I63" s="75"/>
+      <c r="J63" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="L63" s="36"/>
+      <c r="M63" s="80"/>
+      <c r="N63" s="37"/>
+      <c r="O63" s="37"/>
+      <c r="P63" s="37"/>
+      <c r="Q63" s="86"/>
+      <c r="R63" s="86"/>
+      <c r="S63" s="38"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G64" s="193"/>
+      <c r="H64" s="76"/>
+      <c r="I64" s="76"/>
+      <c r="J64" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="L64" s="39"/>
+      <c r="M64" s="81"/>
+      <c r="N64" s="40"/>
+      <c r="O64" s="40"/>
+      <c r="P64" s="40"/>
+      <c r="Q64" s="87"/>
+      <c r="R64" s="87"/>
+      <c r="S64" s="41"/>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G65" s="194" t="s">
+        <v>64</v>
+      </c>
+      <c r="H65" s="77"/>
+      <c r="I65" s="77"/>
+      <c r="J65" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="L65" s="39"/>
+      <c r="M65" s="81"/>
+      <c r="N65" s="40"/>
+      <c r="O65" s="40"/>
+      <c r="P65" s="40"/>
+      <c r="Q65" s="87"/>
+      <c r="R65" s="87"/>
+      <c r="S65" s="41"/>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="G66" s="194"/>
+      <c r="H66" s="77"/>
+      <c r="I66" s="77"/>
+      <c r="J66" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="L66" s="36"/>
+      <c r="M66" s="80"/>
+      <c r="N66" s="37"/>
+      <c r="O66" s="37"/>
+      <c r="P66" s="37"/>
+      <c r="Q66" s="86"/>
+      <c r="R66" s="86"/>
+      <c r="S66" s="38"/>
+    </row>
+    <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G67" s="195"/>
+      <c r="H67" s="78"/>
+      <c r="I67" s="78"/>
+      <c r="J67" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="L67" s="42"/>
+      <c r="M67" s="82"/>
+      <c r="N67" s="43"/>
+      <c r="O67" s="43"/>
+      <c r="P67" s="43"/>
+      <c r="Q67" s="88"/>
+      <c r="R67" s="88"/>
+      <c r="S67" s="32"/>
+    </row>
+    <row r="68" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:24" ht="49.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B69" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="153" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="154"/>
+      <c r="E69" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="L69" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="M69" s="83"/>
+      <c r="N69" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="O69" s="21"/>
+      <c r="P69" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q69" s="89"/>
+      <c r="R69" s="89"/>
+      <c r="S69" s="182" t="s">
+        <v>55</v>
+      </c>
+      <c r="X69" s="183" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B70" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="23"/>
+      <c r="L70" s="11"/>
+      <c r="M70" s="11"/>
+      <c r="N70" s="11"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="11"/>
+      <c r="Q70" s="11"/>
+      <c r="R70" s="11"/>
+      <c r="S70" s="11"/>
+      <c r="X70" s="23"/>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B71" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="23"/>
+      <c r="L71" s="23"/>
+      <c r="M71" s="23"/>
+      <c r="N71" s="23"/>
+      <c r="O71" s="23"/>
+      <c r="P71" s="23"/>
+      <c r="Q71" s="23"/>
+      <c r="R71" s="23"/>
+      <c r="S71" s="23"/>
+      <c r="X71" s="23"/>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B72" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="23"/>
+      <c r="L72" s="23"/>
+      <c r="M72" s="23"/>
+      <c r="N72" s="23"/>
+      <c r="O72" s="23"/>
+      <c r="P72" s="23"/>
+      <c r="Q72" s="23"/>
+      <c r="R72" s="23"/>
+      <c r="S72" s="23"/>
+      <c r="X72" s="23"/>
+    </row>
+    <row r="73" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B74" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C74" s="23"/>
+      <c r="D74" s="23"/>
+      <c r="E74" s="23"/>
+      <c r="L74" s="23"/>
+      <c r="M74" s="23"/>
+      <c r="N74" s="23"/>
+      <c r="O74" s="23"/>
+      <c r="P74" s="23"/>
+      <c r="Q74" s="23"/>
+      <c r="R74" s="23"/>
+      <c r="S74" s="23"/>
+      <c r="X74" s="23"/>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B75" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C75" s="23"/>
+      <c r="D75" s="23"/>
+      <c r="E75" s="23"/>
+      <c r="L75" s="23"/>
+      <c r="M75" s="23"/>
+      <c r="N75" s="23"/>
+      <c r="O75" s="23"/>
+      <c r="P75" s="23"/>
+      <c r="Q75" s="23"/>
+      <c r="R75" s="23"/>
+      <c r="S75" s="23"/>
+      <c r="X75" s="23"/>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B76" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" s="23"/>
+      <c r="D76" s="23"/>
+      <c r="E76" s="23"/>
+      <c r="L76" s="23"/>
+      <c r="M76" s="23"/>
+      <c r="N76" s="23"/>
+      <c r="O76" s="23"/>
+      <c r="P76" s="23"/>
+      <c r="Q76" s="23"/>
+      <c r="R76" s="23"/>
+      <c r="S76" s="23"/>
+      <c r="X76" s="23"/>
+    </row>
+    <row r="77" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B78" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C78" s="23"/>
+      <c r="D78" s="23"/>
+      <c r="E78" s="23"/>
+      <c r="L78" s="23"/>
+      <c r="M78" s="23"/>
+      <c r="N78" s="23"/>
+      <c r="O78" s="23"/>
+      <c r="P78" s="23"/>
+      <c r="Q78" s="23"/>
+      <c r="R78" s="23"/>
+      <c r="S78" s="23"/>
+      <c r="X78" s="23"/>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B79" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C79" s="23"/>
+      <c r="D79" s="23"/>
+      <c r="E79" s="23"/>
+      <c r="L79" s="23"/>
+      <c r="M79" s="23"/>
+      <c r="N79" s="23"/>
+      <c r="O79" s="23"/>
+      <c r="P79" s="23"/>
+      <c r="Q79" s="23"/>
+      <c r="R79" s="23"/>
+      <c r="S79" s="23"/>
+      <c r="X79" s="23"/>
+    </row>
+    <row r="80" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B80" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80" s="23"/>
+      <c r="D80" s="23"/>
+      <c r="E80" s="23"/>
+      <c r="L80" s="23"/>
+      <c r="M80" s="23"/>
+      <c r="N80" s="23"/>
+      <c r="O80" s="23"/>
+      <c r="P80" s="23"/>
+      <c r="Q80" s="23"/>
+      <c r="R80" s="23"/>
+      <c r="S80" s="23"/>
+      <c r="X80" s="23"/>
+    </row>
+    <row r="81" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B82" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="23"/>
+      <c r="D82" s="23"/>
+      <c r="E82" s="23"/>
+      <c r="L82" s="23"/>
+      <c r="M82" s="23"/>
+      <c r="N82" s="23"/>
+      <c r="O82" s="23"/>
+      <c r="P82" s="23"/>
+      <c r="Q82" s="23"/>
+      <c r="R82" s="23"/>
+      <c r="S82" s="23"/>
+      <c r="X82" s="23"/>
+    </row>
+    <row r="83" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B83" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C83" s="23"/>
+      <c r="D83" s="23"/>
+      <c r="E83" s="23"/>
+      <c r="L83" s="23"/>
+      <c r="M83" s="23"/>
+      <c r="N83" s="23"/>
+      <c r="O83" s="23"/>
+      <c r="P83" s="23"/>
+      <c r="Q83" s="23"/>
+      <c r="R83" s="23"/>
+      <c r="S83" s="23"/>
+      <c r="X83" s="23"/>
+    </row>
+    <row r="84" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B84" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="23"/>
+      <c r="L84" s="23"/>
+      <c r="M84" s="23"/>
+      <c r="N84" s="23"/>
+      <c r="O84" s="23"/>
+      <c r="P84" s="23"/>
+      <c r="Q84" s="23"/>
+      <c r="R84" s="23"/>
+      <c r="S84" s="23"/>
+      <c r="X84" s="23"/>
+    </row>
+    <row r="85" spans="2:24" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B86" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" s="23"/>
+      <c r="D86" s="23"/>
+      <c r="E86" s="23"/>
+      <c r="L86" s="23"/>
+      <c r="M86" s="23"/>
+      <c r="N86" s="23"/>
+      <c r="O86" s="23"/>
+      <c r="P86" s="23"/>
+      <c r="Q86" s="23"/>
+      <c r="R86" s="23"/>
+      <c r="S86" s="23"/>
+      <c r="X86" s="23"/>
+    </row>
+    <row r="87" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B87" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" s="23"/>
+      <c r="D87" s="23"/>
+      <c r="E87" s="23"/>
+      <c r="L87" s="23"/>
+      <c r="M87" s="23"/>
+      <c r="N87" s="23"/>
+      <c r="O87" s="23"/>
+      <c r="P87" s="23"/>
+      <c r="Q87" s="23"/>
+      <c r="R87" s="23"/>
+      <c r="S87" s="23"/>
+      <c r="X87" s="23"/>
+    </row>
+    <row r="88" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B88" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="23"/>
+      <c r="D88" s="23"/>
+      <c r="E88" s="23"/>
+      <c r="L88" s="23"/>
+      <c r="M88" s="23"/>
+      <c r="N88" s="23"/>
+      <c r="O88" s="23"/>
+      <c r="P88" s="23"/>
+      <c r="Q88" s="23"/>
+      <c r="R88" s="23"/>
+      <c r="S88" s="23"/>
+      <c r="X88" s="23"/>
+    </row>
+    <row r="90" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B90" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C90" s="23"/>
+      <c r="D90" s="23"/>
+      <c r="E90" s="23"/>
+      <c r="L90" s="23"/>
+      <c r="M90" s="23"/>
+      <c r="N90" s="23"/>
+      <c r="O90" s="23"/>
+      <c r="P90" s="23"/>
+      <c r="Q90" s="23"/>
+      <c r="R90" s="23"/>
+      <c r="S90" s="23"/>
+      <c r="X90" s="23"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="G62:G64"/>
+    <mergeCell ref="G65:G67"/>
+    <mergeCell ref="P1:X1"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:X4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="51" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74C55B6C-C4ED-4E2B-8620-2CD5D9C6EBBF}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH90"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="1.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.85546875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5703125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.5703125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="1.28515625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.7109375" style="2" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="2" style="2" customWidth="1"/>
+    <col min="26" max="26" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="55" width="7.28515625" style="2" customWidth="1"/>
+    <col min="56" max="56" width="1.5703125" style="2" customWidth="1"/>
+    <col min="57" max="57" width="9.42578125" style="2" customWidth="1"/>
+    <col min="58" max="58" width="1.28515625" style="2" customWidth="1"/>
+    <col min="59" max="59" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="10.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="61" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="196">
+        <v>46070</v>
+      </c>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
+      <c r="V1" s="197"/>
+      <c r="W1" s="197"/>
+      <c r="X1" s="198"/>
+    </row>
+    <row r="2" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+    </row>
+    <row r="3" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:60" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="53"/>
+      <c r="B4" s="190" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="199" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="209" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="200" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="201"/>
+      <c r="G4" s="202" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="210" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="204" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="210" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="206" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="207"/>
+      <c r="N4" s="207"/>
+      <c r="O4" s="207"/>
+      <c r="P4" s="207"/>
+      <c r="Q4" s="207"/>
+      <c r="R4" s="207"/>
+      <c r="S4" s="207"/>
+      <c r="T4" s="207"/>
+      <c r="U4" s="207"/>
+      <c r="V4" s="212"/>
+      <c r="W4" s="207"/>
+      <c r="X4" s="208"/>
+    </row>
+    <row r="5" spans="1:60" s="3" customFormat="1" ht="57" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="53"/>
+      <c r="B5" s="190"/>
+      <c r="C5" s="199"/>
+      <c r="D5" s="209"/>
+      <c r="E5" s="52" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="189" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="203"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="205"/>
+      <c r="J5" s="211"/>
+      <c r="L5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M5" s="90" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="90" t="s">
+        <v>75</v>
+      </c>
+      <c r="P5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q5" s="90" t="s">
+        <v>75</v>
+      </c>
+      <c r="R5" s="130" t="s">
+        <v>13</v>
+      </c>
+      <c r="S5" s="124" t="s">
+        <v>75</v>
+      </c>
+      <c r="T5" s="7"/>
+      <c r="U5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" s="163" t="s">
+        <v>79</v>
+      </c>
+      <c r="W5" s="156" t="s">
+        <v>81</v>
+      </c>
+      <c r="X5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="9"/>
+      <c r="AV5" s="9"/>
+      <c r="AW5" s="9"/>
+      <c r="AX5" s="9"/>
+      <c r="AY5" s="9"/>
+      <c r="AZ5" s="9"/>
+      <c r="BA5" s="9"/>
+      <c r="BB5" s="9"/>
+      <c r="BC5" s="9"/>
+      <c r="BD5" s="9"/>
+      <c r="BE5" s="9"/>
+      <c r="BF5" s="9"/>
+      <c r="BG5" s="9"/>
+      <c r="BH5" s="9"/>
+    </row>
+    <row r="6" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="10"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="27"/>
+      <c r="P6" s="27"/>
+      <c r="Q6" s="84"/>
+      <c r="R6" s="131"/>
+      <c r="S6" s="126"/>
+      <c r="T6" s="44"/>
+      <c r="U6" s="28"/>
+      <c r="V6" s="27"/>
+      <c r="W6" s="157"/>
+      <c r="X6" s="30"/>
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="9"/>
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="9"/>
+      <c r="AU6" s="9"/>
+      <c r="AV6" s="9"/>
+      <c r="AW6" s="9"/>
+      <c r="AX6" s="9"/>
+      <c r="AY6" s="9"/>
+      <c r="AZ6" s="9"/>
+      <c r="BA6" s="9"/>
+      <c r="BB6" s="9"/>
+      <c r="BC6" s="9"/>
+      <c r="BD6" s="9"/>
+      <c r="BE6" s="9"/>
+      <c r="BF6" s="9"/>
+      <c r="BG6" s="9"/>
+      <c r="BH6" s="9"/>
+    </row>
+    <row r="7" spans="1:60" s="3" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="10"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="72"/>
+      <c r="I7" s="72"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="44"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="27"/>
+      <c r="N7" s="27"/>
+      <c r="O7" s="27"/>
+      <c r="P7" s="27"/>
+      <c r="Q7" s="84"/>
+      <c r="R7" s="131"/>
+      <c r="S7" s="126"/>
+      <c r="T7" s="44"/>
+      <c r="U7" s="28"/>
+      <c r="V7" s="162"/>
+      <c r="W7" s="157"/>
+      <c r="X7" s="30"/>
+      <c r="AL7" s="9"/>
+      <c r="AM7" s="9"/>
+      <c r="AN7" s="9"/>
+      <c r="AO7" s="9"/>
+      <c r="AP7" s="9"/>
+      <c r="AQ7" s="9"/>
+      <c r="AR7" s="9"/>
+      <c r="AS7" s="9"/>
+      <c r="AT7" s="9"/>
+      <c r="AU7" s="9"/>
+      <c r="AV7" s="9"/>
+      <c r="AW7" s="9"/>
+      <c r="AX7" s="9"/>
+      <c r="AY7" s="9"/>
+      <c r="AZ7" s="9"/>
+      <c r="BA7" s="9"/>
+      <c r="BB7" s="9"/>
+      <c r="BC7" s="9"/>
+      <c r="BD7" s="9"/>
+      <c r="BE7" s="9"/>
+      <c r="BF7" s="9"/>
+      <c r="BG7" s="9"/>
+      <c r="BH7" s="9"/>
+    </row>
+    <row r="8" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>1</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="100"/>
+      <c r="D8" s="101"/>
+      <c r="E8" s="91"/>
+      <c r="F8" s="91"/>
+      <c r="G8" s="102"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="93">
+        <f>C8-G8</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="103">
+        <f t="shared" ref="J8:J12" si="0">D8-H8</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="44"/>
+      <c r="L8" s="91"/>
+      <c r="M8" s="91"/>
+      <c r="N8" s="91"/>
+      <c r="O8" s="91"/>
+      <c r="P8" s="91"/>
+      <c r="Q8" s="92"/>
+      <c r="R8" s="129">
+        <f t="shared" ref="R8:S12" si="1">L8+N8+P8</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="127">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="44"/>
+      <c r="U8" s="28">
+        <f>L8*24+N8*24+P8*24</f>
+        <v>0</v>
+      </c>
+      <c r="V8" s="162">
+        <f>U8/24</f>
+        <v>0</v>
+      </c>
+      <c r="W8" s="157">
+        <f t="shared" ref="W8:W12" si="2">I8*24+J8</f>
+        <v>0</v>
+      </c>
+      <c r="X8" s="30"/>
+      <c r="AL8" s="12"/>
+      <c r="AM8" s="12"/>
+      <c r="AN8" s="12"/>
+      <c r="AO8" s="12"/>
+      <c r="AP8" s="12"/>
+      <c r="AQ8" s="12"/>
+      <c r="AR8" s="12"/>
+      <c r="AS8" s="12"/>
+      <c r="AT8" s="12"/>
+      <c r="AU8" s="12"/>
+      <c r="AV8" s="12"/>
+      <c r="AW8" s="12"/>
+      <c r="AX8" s="12"/>
+      <c r="AY8" s="12"/>
+      <c r="AZ8" s="12"/>
+      <c r="BA8" s="12"/>
+      <c r="BB8" s="12"/>
+      <c r="BC8" s="12"/>
+      <c r="BD8" s="12"/>
+      <c r="BE8" s="12"/>
+      <c r="BF8" s="12"/>
+      <c r="BG8" s="12"/>
+      <c r="BH8" s="12"/>
+    </row>
+    <row r="9" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f t="shared" ref="A9:A59" si="3">A8+1</f>
+        <v>2</v>
+      </c>
+      <c r="B9" s="54" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="104"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="106"/>
+      <c r="F9" s="106"/>
+      <c r="G9" s="107"/>
+      <c r="H9" s="108"/>
+      <c r="I9" s="107">
+        <f t="shared" ref="I9:J59" si="4">C9-G9</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="166">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="64"/>
+      <c r="L9" s="94"/>
+      <c r="M9" s="94"/>
+      <c r="N9" s="94"/>
+      <c r="O9" s="94"/>
+      <c r="P9" s="94"/>
+      <c r="Q9" s="95"/>
+      <c r="R9" s="174">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S9" s="171">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="64"/>
+      <c r="U9" s="67">
+        <f>L9*24+N9*24+P9*24</f>
+        <v>0</v>
+      </c>
+      <c r="V9" s="172">
+        <f>U9/24</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="158">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X9" s="66"/>
+      <c r="AL9" s="12"/>
+      <c r="AM9" s="12"/>
+      <c r="AN9" s="12"/>
+      <c r="AO9" s="12"/>
+      <c r="AP9" s="12"/>
+      <c r="AQ9" s="12"/>
+      <c r="AR9" s="12"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="12"/>
+      <c r="AU9" s="12"/>
+      <c r="AV9" s="12"/>
+      <c r="AW9" s="12"/>
+      <c r="AX9" s="12"/>
+      <c r="AY9" s="12"/>
+      <c r="AZ9" s="12"/>
+      <c r="BA9" s="12"/>
+      <c r="BB9" s="12"/>
+      <c r="BC9" s="12"/>
+      <c r="BD9" s="12"/>
+      <c r="BE9" s="12"/>
+      <c r="BF9" s="12"/>
+      <c r="BG9" s="12"/>
+      <c r="BH9" s="12"/>
+    </row>
+    <row r="10" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="100"/>
+      <c r="D10" s="101"/>
+      <c r="E10" s="91"/>
+      <c r="F10" s="91"/>
+      <c r="G10" s="102"/>
+      <c r="H10" s="93"/>
+      <c r="I10" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="167">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K10" s="44"/>
+      <c r="L10" s="91"/>
+      <c r="M10" s="91"/>
+      <c r="N10" s="91"/>
+      <c r="O10" s="91"/>
+      <c r="P10" s="91"/>
+      <c r="Q10" s="92"/>
+      <c r="R10" s="175">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S10" s="170">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T10" s="44"/>
+      <c r="U10" s="28">
+        <f>L10*24+N10*24+P10*24</f>
+        <v>0</v>
+      </c>
+      <c r="V10" s="173">
+        <f>U10/24</f>
+        <v>0</v>
+      </c>
+      <c r="W10" s="157">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X10" s="30"/>
+      <c r="AL10" s="12"/>
+      <c r="AM10" s="12"/>
+      <c r="AN10" s="12"/>
+      <c r="AO10" s="12"/>
+      <c r="AP10" s="12"/>
+      <c r="AQ10" s="12"/>
+      <c r="AR10" s="12"/>
+      <c r="AS10" s="12"/>
+      <c r="AT10" s="12"/>
+      <c r="AU10" s="12"/>
+      <c r="AV10" s="12"/>
+      <c r="AW10" s="12"/>
+      <c r="AX10" s="12"/>
+      <c r="AY10" s="12"/>
+      <c r="AZ10" s="12"/>
+      <c r="BA10" s="12"/>
+      <c r="BB10" s="12"/>
+      <c r="BC10" s="12"/>
+      <c r="BD10" s="12"/>
+      <c r="BE10" s="12"/>
+      <c r="BF10" s="12"/>
+      <c r="BG10" s="12"/>
+      <c r="BH10" s="12"/>
+    </row>
+    <row r="11" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="100"/>
+      <c r="D11" s="101"/>
+      <c r="E11" s="91"/>
+      <c r="F11" s="91"/>
+      <c r="G11" s="102"/>
+      <c r="H11" s="93"/>
+      <c r="I11" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="103">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="44"/>
+      <c r="L11" s="91"/>
+      <c r="M11" s="91"/>
+      <c r="N11" s="91"/>
+      <c r="O11" s="91"/>
+      <c r="P11" s="91"/>
+      <c r="Q11" s="92"/>
+      <c r="R11" s="129">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S11" s="127">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T11" s="44"/>
+      <c r="U11" s="28">
+        <f>L11*24+N11*24+P11*24</f>
+        <v>0</v>
+      </c>
+      <c r="V11" s="162">
+        <f>U11/24</f>
+        <v>0</v>
+      </c>
+      <c r="W11" s="157">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X11" s="30"/>
+      <c r="AL11" s="12"/>
+      <c r="AM11" s="12"/>
+      <c r="AN11" s="12"/>
+      <c r="AO11" s="12"/>
+      <c r="AP11" s="12"/>
+      <c r="AQ11" s="12"/>
+      <c r="AR11" s="12"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="12"/>
+      <c r="AU11" s="12"/>
+      <c r="AV11" s="12"/>
+      <c r="AW11" s="12"/>
+      <c r="AX11" s="12"/>
+      <c r="AY11" s="12"/>
+      <c r="AZ11" s="12"/>
+      <c r="BA11" s="12"/>
+      <c r="BB11" s="12"/>
+      <c r="BC11" s="12"/>
+      <c r="BD11" s="12"/>
+      <c r="BE11" s="12"/>
+      <c r="BF11" s="12"/>
+      <c r="BG11" s="12"/>
+      <c r="BH11" s="12"/>
+    </row>
+    <row r="12" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="100"/>
+      <c r="D12" s="101"/>
+      <c r="E12" s="91"/>
+      <c r="F12" s="91"/>
+      <c r="G12" s="102"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="103">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K12" s="44"/>
+      <c r="L12" s="91"/>
+      <c r="M12" s="91"/>
+      <c r="N12" s="91"/>
+      <c r="O12" s="91"/>
+      <c r="P12" s="91"/>
+      <c r="Q12" s="92"/>
+      <c r="R12" s="129">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S12" s="127">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="T12" s="44"/>
+      <c r="U12" s="28">
+        <f t="shared" ref="U12:U37" si="5">L12*24+N12*24+P12*24</f>
+        <v>0</v>
+      </c>
+      <c r="V12" s="162">
+        <f t="shared" ref="V12:V41" si="6">U12/24</f>
+        <v>0</v>
+      </c>
+      <c r="W12" s="157">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X12" s="30"/>
+      <c r="AL12" s="12"/>
+      <c r="AM12" s="12"/>
+      <c r="AN12" s="12"/>
+      <c r="AO12" s="12"/>
+      <c r="AP12" s="12"/>
+      <c r="AQ12" s="12"/>
+      <c r="AR12" s="12"/>
+      <c r="AS12" s="12"/>
+      <c r="AT12" s="12"/>
+      <c r="AU12" s="12"/>
+      <c r="AV12" s="12"/>
+      <c r="AW12" s="12"/>
+      <c r="AX12" s="12"/>
+      <c r="AY12" s="12"/>
+      <c r="AZ12" s="12"/>
+      <c r="BA12" s="12"/>
+      <c r="BB12" s="12"/>
+      <c r="BC12" s="12"/>
+      <c r="BD12" s="12"/>
+      <c r="BE12" s="12"/>
+      <c r="BF12" s="12"/>
+      <c r="BG12" s="12"/>
+      <c r="BH12" s="12"/>
+    </row>
+    <row r="13" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="B13" s="54" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="104"/>
+      <c r="D13" s="105"/>
+      <c r="E13" s="106"/>
+      <c r="F13" s="106"/>
+      <c r="G13" s="107"/>
+      <c r="H13" s="108"/>
+      <c r="I13" s="116">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="166">
+        <f>D13-H13</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="68"/>
+      <c r="L13" s="94"/>
+      <c r="M13" s="94"/>
+      <c r="N13" s="94"/>
+      <c r="O13" s="94"/>
+      <c r="P13" s="94"/>
+      <c r="Q13" s="95"/>
+      <c r="R13" s="169">
+        <f>L13+N13+P13</f>
+        <v>0</v>
+      </c>
+      <c r="S13" s="171">
+        <f>M13+O13+Q13</f>
+        <v>0</v>
+      </c>
+      <c r="T13" s="68"/>
+      <c r="U13" s="67">
+        <f>L13*24+N13*24+P13*24</f>
+        <v>0</v>
+      </c>
+      <c r="V13" s="56">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W13" s="158">
+        <f>I13*24+J13</f>
+        <v>0</v>
+      </c>
+      <c r="X13" s="66"/>
+      <c r="Y13" s="2"/>
+      <c r="AD13" s="2"/>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="2"/>
+      <c r="AI13" s="2"/>
+      <c r="AJ13" s="2"/>
+      <c r="AK13" s="2"/>
+      <c r="AL13" s="12"/>
+      <c r="AM13" s="12"/>
+      <c r="AN13" s="12"/>
+      <c r="AO13" s="12"/>
+      <c r="AP13" s="12"/>
+      <c r="AQ13" s="12"/>
+      <c r="AR13" s="12"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="12"/>
+      <c r="AU13" s="12"/>
+      <c r="AV13" s="12"/>
+      <c r="AW13" s="12"/>
+      <c r="AX13" s="12"/>
+      <c r="AY13" s="12"/>
+      <c r="AZ13" s="12"/>
+      <c r="BA13" s="12"/>
+      <c r="BB13" s="12"/>
+      <c r="BC13" s="12"/>
+      <c r="BD13" s="12"/>
+      <c r="BE13" s="12"/>
+      <c r="BF13" s="12"/>
+      <c r="BG13" s="12"/>
+      <c r="BH13" s="12"/>
+    </row>
+    <row r="14" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="100"/>
+      <c r="D14" s="101"/>
+      <c r="E14" s="91"/>
+      <c r="F14" s="91"/>
+      <c r="G14" s="102"/>
+      <c r="H14" s="93"/>
+      <c r="I14" s="165">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="167">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="44"/>
+      <c r="L14" s="91"/>
+      <c r="M14" s="91"/>
+      <c r="N14" s="91"/>
+      <c r="O14" s="91"/>
+      <c r="P14" s="91"/>
+      <c r="Q14" s="92"/>
+      <c r="R14" s="168">
+        <f t="shared" ref="R14:S59" si="7">L14+N14+P14</f>
+        <v>0</v>
+      </c>
+      <c r="S14" s="170">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T14" s="44"/>
+      <c r="U14" s="28">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V14" s="27">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W14" s="157">
+        <f t="shared" ref="W14:W37" si="8">I14*24+J14</f>
+        <v>0</v>
+      </c>
+      <c r="X14" s="30"/>
+      <c r="AL14" s="12"/>
+      <c r="AM14" s="12"/>
+      <c r="AN14" s="12"/>
+      <c r="AO14" s="12"/>
+      <c r="AP14" s="12"/>
+      <c r="AQ14" s="12"/>
+      <c r="AR14" s="12"/>
+      <c r="AS14" s="12"/>
+      <c r="AT14" s="12"/>
+      <c r="AU14" s="12"/>
+      <c r="AV14" s="12"/>
+      <c r="AW14" s="12"/>
+      <c r="AX14" s="12"/>
+      <c r="AY14" s="12"/>
+      <c r="AZ14" s="12"/>
+      <c r="BA14" s="12"/>
+      <c r="BB14" s="12"/>
+      <c r="BC14" s="12"/>
+      <c r="BD14" s="12"/>
+      <c r="BE14" s="12"/>
+      <c r="BF14" s="12"/>
+      <c r="BG14" s="12"/>
+      <c r="BH14" s="12"/>
+    </row>
+    <row r="15" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="100"/>
+      <c r="D15" s="101"/>
+      <c r="E15" s="91"/>
+      <c r="F15" s="91"/>
+      <c r="G15" s="102"/>
+      <c r="H15" s="93"/>
+      <c r="I15" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="44"/>
+      <c r="L15" s="91"/>
+      <c r="M15" s="91"/>
+      <c r="N15" s="91"/>
+      <c r="O15" s="91"/>
+      <c r="P15" s="91"/>
+      <c r="Q15" s="92"/>
+      <c r="R15" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T15" s="44"/>
+      <c r="U15" s="28">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V15" s="162">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W15" s="157">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X15" s="30"/>
+      <c r="AL15" s="12"/>
+      <c r="AM15" s="12"/>
+      <c r="AN15" s="12"/>
+      <c r="AO15" s="12"/>
+      <c r="AP15" s="12"/>
+      <c r="AQ15" s="12"/>
+      <c r="AR15" s="12"/>
+      <c r="AS15" s="12"/>
+      <c r="AT15" s="12"/>
+      <c r="AU15" s="12"/>
+      <c r="AV15" s="12"/>
+      <c r="AW15" s="12"/>
+      <c r="AX15" s="12"/>
+      <c r="AY15" s="12"/>
+      <c r="AZ15" s="12"/>
+      <c r="BA15" s="12"/>
+      <c r="BB15" s="12"/>
+      <c r="BC15" s="12"/>
+      <c r="BD15" s="12"/>
+      <c r="BE15" s="12"/>
+      <c r="BF15" s="12"/>
+      <c r="BG15" s="12"/>
+      <c r="BH15" s="12"/>
+    </row>
+    <row r="16" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="100"/>
+      <c r="D16" s="101"/>
+      <c r="E16" s="91"/>
+      <c r="F16" s="91"/>
+      <c r="G16" s="102"/>
+      <c r="H16" s="93"/>
+      <c r="I16" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="44"/>
+      <c r="L16" s="91"/>
+      <c r="M16" s="91"/>
+      <c r="N16" s="91"/>
+      <c r="O16" s="91"/>
+      <c r="P16" s="91"/>
+      <c r="Q16" s="92"/>
+      <c r="R16" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S16" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T16" s="44"/>
+      <c r="U16" s="28">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="162">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W16" s="157">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="30"/>
+      <c r="AL16" s="12"/>
+      <c r="AM16" s="12"/>
+      <c r="AN16" s="12"/>
+      <c r="AO16" s="12"/>
+      <c r="AP16" s="12"/>
+      <c r="AQ16" s="12"/>
+      <c r="AR16" s="12"/>
+      <c r="AS16" s="12"/>
+      <c r="AT16" s="12"/>
+      <c r="AU16" s="12"/>
+      <c r="AV16" s="12"/>
+      <c r="AW16" s="12"/>
+      <c r="AX16" s="12"/>
+      <c r="AY16" s="12"/>
+      <c r="AZ16" s="12"/>
+      <c r="BA16" s="12"/>
+      <c r="BB16" s="12"/>
+      <c r="BC16" s="12"/>
+      <c r="BD16" s="12"/>
+      <c r="BE16" s="12"/>
+      <c r="BF16" s="12"/>
+      <c r="BG16" s="12"/>
+      <c r="BH16" s="12"/>
+    </row>
+    <row r="17" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="100"/>
+      <c r="D17" s="101"/>
+      <c r="E17" s="91"/>
+      <c r="F17" s="91"/>
+      <c r="G17" s="102"/>
+      <c r="H17" s="93"/>
+      <c r="I17" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="44"/>
+      <c r="L17" s="91"/>
+      <c r="M17" s="91"/>
+      <c r="N17" s="91"/>
+      <c r="O17" s="91"/>
+      <c r="P17" s="91"/>
+      <c r="Q17" s="92"/>
+      <c r="R17" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S17" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T17" s="44"/>
+      <c r="U17" s="28">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="162">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W17" s="157">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="30"/>
+      <c r="AL17" s="12"/>
+      <c r="AM17" s="12"/>
+      <c r="AN17" s="12"/>
+      <c r="AO17" s="12"/>
+      <c r="AP17" s="12"/>
+      <c r="AQ17" s="12"/>
+      <c r="AR17" s="12"/>
+      <c r="AS17" s="12"/>
+      <c r="AT17" s="12"/>
+      <c r="AU17" s="12"/>
+      <c r="AV17" s="12"/>
+      <c r="AW17" s="12"/>
+      <c r="AX17" s="12"/>
+      <c r="AY17" s="12"/>
+      <c r="AZ17" s="12"/>
+      <c r="BA17" s="12"/>
+      <c r="BB17" s="12"/>
+      <c r="BC17" s="12"/>
+      <c r="BD17" s="12"/>
+      <c r="BE17" s="12"/>
+      <c r="BF17" s="12"/>
+      <c r="BG17" s="12"/>
+      <c r="BH17" s="12"/>
+    </row>
+    <row r="18" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="100"/>
+      <c r="D18" s="101"/>
+      <c r="E18" s="91"/>
+      <c r="F18" s="91"/>
+      <c r="G18" s="102"/>
+      <c r="H18" s="93"/>
+      <c r="I18" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="44"/>
+      <c r="L18" s="91"/>
+      <c r="M18" s="91"/>
+      <c r="N18" s="91"/>
+      <c r="O18" s="91"/>
+      <c r="P18" s="91"/>
+      <c r="Q18" s="92"/>
+      <c r="R18" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S18" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T18" s="44"/>
+      <c r="U18" s="28">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V18" s="162">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W18" s="157">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X18" s="30"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+      <c r="AS18" s="12"/>
+      <c r="AT18" s="12"/>
+      <c r="AU18" s="12"/>
+      <c r="AV18" s="12"/>
+      <c r="AW18" s="12"/>
+      <c r="AX18" s="12"/>
+      <c r="AY18" s="12"/>
+      <c r="AZ18" s="12"/>
+      <c r="BA18" s="12"/>
+      <c r="BB18" s="12"/>
+      <c r="BC18" s="12"/>
+      <c r="BD18" s="12"/>
+      <c r="BE18" s="12"/>
+      <c r="BF18" s="12"/>
+      <c r="BG18" s="12"/>
+      <c r="BH18" s="12"/>
+    </row>
+    <row r="19" spans="1:60" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="100"/>
+      <c r="D19" s="101"/>
+      <c r="E19" s="91"/>
+      <c r="F19" s="91"/>
+      <c r="G19" s="102"/>
+      <c r="H19" s="93"/>
+      <c r="I19" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="44"/>
+      <c r="L19" s="91"/>
+      <c r="M19" s="91"/>
+      <c r="N19" s="91"/>
+      <c r="O19" s="91"/>
+      <c r="P19" s="91"/>
+      <c r="Q19" s="92"/>
+      <c r="R19" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S19" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T19" s="44"/>
+      <c r="U19" s="28">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="162">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="157">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X19" s="30"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="12"/>
+      <c r="AN19" s="12"/>
+      <c r="AO19" s="12"/>
+      <c r="AP19" s="12"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="12"/>
+      <c r="AS19" s="12"/>
+      <c r="AT19" s="12"/>
+      <c r="AU19" s="12"/>
+      <c r="AV19" s="12"/>
+      <c r="AW19" s="12"/>
+      <c r="AX19" s="12"/>
+      <c r="AY19" s="12"/>
+      <c r="AZ19" s="12"/>
+      <c r="BA19" s="12"/>
+      <c r="BB19" s="12"/>
+      <c r="BC19" s="12"/>
+      <c r="BD19" s="12"/>
+      <c r="BE19" s="12"/>
+      <c r="BF19" s="12"/>
+      <c r="BG19" s="12"/>
+      <c r="BH19" s="12"/>
+    </row>
+    <row r="20" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="100"/>
+      <c r="D20" s="101"/>
+      <c r="E20" s="91"/>
+      <c r="F20" s="91"/>
+      <c r="G20" s="102"/>
+      <c r="H20" s="93"/>
+      <c r="I20" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="44"/>
+      <c r="L20" s="91"/>
+      <c r="M20" s="91"/>
+      <c r="N20" s="91"/>
+      <c r="O20" s="91"/>
+      <c r="P20" s="91"/>
+      <c r="Q20" s="92"/>
+      <c r="R20" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T20" s="44"/>
+      <c r="U20" s="28">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V20" s="162">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W20" s="157">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X20" s="30"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="12"/>
+      <c r="AN20" s="12"/>
+      <c r="AO20" s="12"/>
+      <c r="AP20" s="12"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="12"/>
+      <c r="AS20" s="12"/>
+      <c r="AT20" s="12"/>
+      <c r="AU20" s="12"/>
+      <c r="AV20" s="12"/>
+      <c r="AW20" s="12"/>
+      <c r="AX20" s="12"/>
+      <c r="AY20" s="12"/>
+      <c r="AZ20" s="12"/>
+      <c r="BA20" s="12"/>
+      <c r="BB20" s="12"/>
+      <c r="BC20" s="12"/>
+      <c r="BD20" s="12"/>
+      <c r="BE20" s="12"/>
+      <c r="BF20" s="12"/>
+      <c r="BG20" s="12"/>
+      <c r="BH20" s="12"/>
+    </row>
+    <row r="21" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="100"/>
+      <c r="D21" s="101"/>
+      <c r="E21" s="91"/>
+      <c r="F21" s="91"/>
+      <c r="G21" s="102"/>
+      <c r="H21" s="93"/>
+      <c r="I21" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="44"/>
+      <c r="L21" s="91"/>
+      <c r="M21" s="91"/>
+      <c r="N21" s="91"/>
+      <c r="O21" s="91"/>
+      <c r="P21" s="91"/>
+      <c r="Q21" s="92"/>
+      <c r="R21" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T21" s="44"/>
+      <c r="U21" s="28">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V21" s="162">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W21" s="157">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X21" s="30"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="12"/>
+      <c r="AN21" s="12"/>
+      <c r="AO21" s="12"/>
+      <c r="AP21" s="12"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="12"/>
+      <c r="AS21" s="12"/>
+      <c r="AT21" s="12"/>
+      <c r="AU21" s="12"/>
+      <c r="AV21" s="12"/>
+      <c r="AW21" s="12"/>
+      <c r="AX21" s="12"/>
+      <c r="AY21" s="12"/>
+      <c r="AZ21" s="12"/>
+      <c r="BA21" s="12"/>
+      <c r="BB21" s="12"/>
+      <c r="BC21" s="12"/>
+      <c r="BD21" s="12"/>
+      <c r="BE21" s="12"/>
+      <c r="BF21" s="12"/>
+      <c r="BG21" s="12"/>
+      <c r="BH21" s="12"/>
+    </row>
+    <row r="22" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="100"/>
+      <c r="D22" s="101"/>
+      <c r="E22" s="91"/>
+      <c r="F22" s="91"/>
+      <c r="G22" s="102"/>
+      <c r="H22" s="93"/>
+      <c r="I22" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="44"/>
+      <c r="L22" s="91"/>
+      <c r="M22" s="91"/>
+      <c r="N22" s="91"/>
+      <c r="O22" s="91"/>
+      <c r="P22" s="91"/>
+      <c r="Q22" s="92"/>
+      <c r="R22" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S22" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T22" s="44"/>
+      <c r="U22" s="28">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V22" s="162">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W22" s="157">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X22" s="30"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="12"/>
+      <c r="AN22" s="12"/>
+      <c r="AO22" s="12"/>
+      <c r="AP22" s="12"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="12"/>
+      <c r="AS22" s="12"/>
+      <c r="AT22" s="12"/>
+      <c r="AU22" s="12"/>
+      <c r="AV22" s="12"/>
+      <c r="AW22" s="12"/>
+      <c r="AX22" s="12"/>
+      <c r="AY22" s="12"/>
+      <c r="AZ22" s="12"/>
+      <c r="BA22" s="12"/>
+      <c r="BB22" s="12"/>
+      <c r="BC22" s="12"/>
+      <c r="BD22" s="12"/>
+      <c r="BE22" s="12"/>
+      <c r="BF22" s="12"/>
+      <c r="BG22" s="12"/>
+      <c r="BH22" s="12"/>
+    </row>
+    <row r="23" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="100"/>
+      <c r="D23" s="101"/>
+      <c r="E23" s="91"/>
+      <c r="F23" s="91"/>
+      <c r="G23" s="102"/>
+      <c r="H23" s="93"/>
+      <c r="I23" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="45"/>
+      <c r="L23" s="91"/>
+      <c r="M23" s="91"/>
+      <c r="N23" s="91"/>
+      <c r="O23" s="91"/>
+      <c r="P23" s="91"/>
+      <c r="Q23" s="92"/>
+      <c r="R23" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S23" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T23" s="45"/>
+      <c r="U23" s="28">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V23" s="162">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W23" s="157">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X23" s="30"/>
+      <c r="Y23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AG23" s="2"/>
+      <c r="AH23" s="2"/>
+      <c r="AI23" s="2"/>
+      <c r="AJ23" s="2"/>
+      <c r="AK23" s="2"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="12"/>
+      <c r="AN23" s="12"/>
+      <c r="AO23" s="12"/>
+      <c r="AP23" s="12"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="12"/>
+      <c r="AS23" s="12"/>
+      <c r="AT23" s="12"/>
+      <c r="AU23" s="12"/>
+      <c r="AV23" s="12"/>
+      <c r="AW23" s="12"/>
+      <c r="AX23" s="12"/>
+      <c r="AY23" s="12"/>
+      <c r="AZ23" s="12"/>
+      <c r="BA23" s="12"/>
+      <c r="BB23" s="12"/>
+      <c r="BC23" s="12"/>
+      <c r="BD23" s="12"/>
+      <c r="BE23" s="12"/>
+      <c r="BF23" s="12"/>
+      <c r="BG23" s="12"/>
+      <c r="BH23" s="12"/>
+    </row>
+    <row r="24" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="100"/>
+      <c r="D24" s="101"/>
+      <c r="E24" s="91"/>
+      <c r="F24" s="91"/>
+      <c r="G24" s="102"/>
+      <c r="H24" s="93"/>
+      <c r="I24" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="45"/>
+      <c r="L24" s="91"/>
+      <c r="M24" s="91"/>
+      <c r="N24" s="91"/>
+      <c r="O24" s="91"/>
+      <c r="P24" s="91"/>
+      <c r="Q24" s="92"/>
+      <c r="R24" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S24" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T24" s="45"/>
+      <c r="U24" s="28">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V24" s="162">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W24" s="157">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X24" s="30"/>
+      <c r="Y24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="2"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="12"/>
+      <c r="AN24" s="12"/>
+      <c r="AO24" s="12"/>
+      <c r="AP24" s="12"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="12"/>
+      <c r="AS24" s="12"/>
+      <c r="AT24" s="12"/>
+      <c r="AU24" s="12"/>
+      <c r="AV24" s="12"/>
+      <c r="AW24" s="12"/>
+      <c r="AX24" s="12"/>
+      <c r="AY24" s="12"/>
+      <c r="AZ24" s="12"/>
+      <c r="BA24" s="12"/>
+      <c r="BB24" s="12"/>
+      <c r="BC24" s="12"/>
+      <c r="BD24" s="12"/>
+      <c r="BE24" s="12"/>
+      <c r="BF24" s="12"/>
+      <c r="BG24" s="12"/>
+      <c r="BH24" s="12"/>
+    </row>
+    <row r="25" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="100"/>
+      <c r="D25" s="101"/>
+      <c r="E25" s="91"/>
+      <c r="F25" s="91"/>
+      <c r="G25" s="102"/>
+      <c r="H25" s="93"/>
+      <c r="I25" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="44"/>
+      <c r="L25" s="91"/>
+      <c r="M25" s="91"/>
+      <c r="N25" s="91"/>
+      <c r="O25" s="91"/>
+      <c r="P25" s="91"/>
+      <c r="Q25" s="92"/>
+      <c r="R25" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S25" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T25" s="44"/>
+      <c r="U25" s="28">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V25" s="162">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W25" s="157">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X25" s="30"/>
+      <c r="AL25" s="12"/>
+      <c r="AM25" s="12"/>
+      <c r="AN25" s="12"/>
+      <c r="AO25" s="12"/>
+      <c r="AP25" s="12"/>
+      <c r="AQ25" s="12"/>
+      <c r="AR25" s="12"/>
+      <c r="AS25" s="12"/>
+      <c r="AT25" s="12"/>
+      <c r="AU25" s="12"/>
+      <c r="AV25" s="12"/>
+      <c r="AW25" s="12"/>
+      <c r="AX25" s="12"/>
+      <c r="AY25" s="12"/>
+      <c r="AZ25" s="12"/>
+      <c r="BA25" s="12"/>
+      <c r="BB25" s="12"/>
+      <c r="BC25" s="12"/>
+      <c r="BD25" s="12"/>
+      <c r="BE25" s="12"/>
+      <c r="BF25" s="12"/>
+      <c r="BG25" s="12"/>
+      <c r="BH25" s="12"/>
+    </row>
+    <row r="26" spans="1:60" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="100"/>
+      <c r="D26" s="101"/>
+      <c r="E26" s="91"/>
+      <c r="F26" s="91"/>
+      <c r="G26" s="102"/>
+      <c r="H26" s="93"/>
+      <c r="I26" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="44"/>
+      <c r="L26" s="91"/>
+      <c r="M26" s="91"/>
+      <c r="N26" s="91"/>
+      <c r="O26" s="91"/>
+      <c r="P26" s="91"/>
+      <c r="Q26" s="92"/>
+      <c r="R26" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S26" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T26" s="44"/>
+      <c r="U26" s="28">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="162">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W26" s="157">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X26" s="30"/>
+      <c r="BE26" s="14" t="e">
+        <f>#REF!-BE25</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="100"/>
+      <c r="D27" s="101"/>
+      <c r="E27" s="91"/>
+      <c r="F27" s="91"/>
+      <c r="G27" s="102"/>
+      <c r="H27" s="93"/>
+      <c r="I27" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J27" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="45"/>
+      <c r="L27" s="91"/>
+      <c r="M27" s="91"/>
+      <c r="N27" s="91"/>
+      <c r="O27" s="91"/>
+      <c r="P27" s="91"/>
+      <c r="Q27" s="92"/>
+      <c r="R27" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T27" s="45"/>
+      <c r="U27" s="28">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V27" s="162">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W27" s="157">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X27" s="30"/>
+      <c r="Y27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="2"/>
+    </row>
+    <row r="28" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="100"/>
+      <c r="D28" s="101"/>
+      <c r="E28" s="91"/>
+      <c r="F28" s="91"/>
+      <c r="G28" s="102"/>
+      <c r="H28" s="93"/>
+      <c r="I28" s="93">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="45"/>
+      <c r="L28" s="91"/>
+      <c r="M28" s="91"/>
+      <c r="N28" s="91"/>
+      <c r="O28" s="91"/>
+      <c r="P28" s="91"/>
+      <c r="Q28" s="92"/>
+      <c r="R28" s="129">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="127">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T28" s="45"/>
+      <c r="U28" s="28">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="162">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="157">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="X28" s="30"/>
+      <c r="Y28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+    </row>
+    <row r="29" spans="1:60" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>25</v>
+      </c>
       <c r="C29" s="100"/>
       <c r="D29" s="101"/>
       <c r="E29" s="91"/>
@@ -28819,7 +32934,7 @@
       <c r="V61" s="185"/>
     </row>
     <row r="62" spans="1:24" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="188" t="s">
+      <c r="G62" s="191" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="74"/>
@@ -28837,7 +32952,7 @@
       <c r="S62" s="35"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G63" s="189"/>
+      <c r="G63" s="192"/>
       <c r="H63" s="75"/>
       <c r="I63" s="75"/>
       <c r="J63" s="25" t="s">
@@ -28853,7 +32968,7 @@
       <c r="S63" s="38"/>
     </row>
     <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="G64" s="190"/>
+      <c r="G64" s="193"/>
       <c r="H64" s="76"/>
       <c r="I64" s="76"/>
       <c r="J64" s="25" t="s">
@@ -28869,7 +32984,7 @@
       <c r="S64" s="41"/>
     </row>
     <row r="65" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G65" s="191" t="s">
+      <c r="G65" s="194" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="77"/>
@@ -28887,7 +33002,7 @@
       <c r="S65" s="41"/>
     </row>
     <row r="66" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="G66" s="191"/>
+      <c r="G66" s="194"/>
       <c r="H66" s="77"/>
       <c r="I66" s="77"/>
       <c r="J66" s="25" t="s">
@@ -28903,7 +33018,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:24" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="192"/>
+      <c r="G67" s="195"/>
       <c r="H67" s="78"/>
       <c r="I67" s="78"/>
       <c r="J67" s="26" t="s">
@@ -28923,10 +33038,10 @@
       <c r="B69" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C69" s="153" t="s">
+      <c r="C69" s="187" t="s">
         <v>3</v>
       </c>
-      <c r="D69" s="154"/>
+      <c r="D69" s="188"/>
       <c r="E69" s="19" t="s">
         <v>54</v>
       </c>
@@ -29296,15 +33411,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="193">
+      <c r="P1" s="196">
         <v>46055</v>
       </c>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
-      <c r="V1" s="195"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
+      <c r="V1" s="198"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -29327,60 +33442,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="187" t="s">
+      <c r="B4" s="190" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="196" t="s">
+      <c r="C4" s="199" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="206" t="s">
+      <c r="D4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="197" t="s">
+      <c r="E4" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="198"/>
-      <c r="G4" s="199" t="s">
+      <c r="F4" s="201"/>
+      <c r="G4" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="207" t="s">
+      <c r="H4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="201" t="s">
+      <c r="I4" s="204" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="207" t="s">
+      <c r="J4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="203" t="s">
+      <c r="L4" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="204"/>
-      <c r="N4" s="204"/>
-      <c r="O4" s="204"/>
-      <c r="P4" s="204"/>
-      <c r="Q4" s="204"/>
-      <c r="R4" s="204"/>
-      <c r="S4" s="204"/>
-      <c r="T4" s="204"/>
-      <c r="U4" s="204"/>
-      <c r="V4" s="205"/>
+      <c r="M4" s="207"/>
+      <c r="N4" s="207"/>
+      <c r="O4" s="207"/>
+      <c r="P4" s="207"/>
+      <c r="Q4" s="207"/>
+      <c r="R4" s="207"/>
+      <c r="S4" s="207"/>
+      <c r="T4" s="207"/>
+      <c r="U4" s="207"/>
+      <c r="V4" s="208"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53"/>
-      <c r="B5" s="187"/>
-      <c r="C5" s="196"/>
-      <c r="D5" s="206"/>
+      <c r="B5" s="190"/>
+      <c r="C5" s="199"/>
+      <c r="D5" s="209"/>
       <c r="E5" s="52" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="134" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="200"/>
-      <c r="H5" s="208"/>
-      <c r="I5" s="202"/>
-      <c r="J5" s="208"/>
+      <c r="G5" s="203"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="205"/>
+      <c r="J5" s="211"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -32304,7 +36419,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="188" t="s">
+      <c r="G62" s="191" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="74"/>
@@ -32322,7 +36437,7 @@
       <c r="S62" s="35"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="189"/>
+      <c r="G63" s="192"/>
       <c r="H63" s="75"/>
       <c r="I63" s="75"/>
       <c r="J63" s="25" t="s">
@@ -32338,7 +36453,7 @@
       <c r="S63" s="38"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="190"/>
+      <c r="G64" s="193"/>
       <c r="H64" s="76"/>
       <c r="I64" s="76"/>
       <c r="J64" s="25" t="s">
@@ -32354,7 +36469,7 @@
       <c r="S64" s="41"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="191" t="s">
+      <c r="G65" s="194" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="77"/>
@@ -32372,7 +36487,7 @@
       <c r="S65" s="41"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="191"/>
+      <c r="G66" s="194"/>
       <c r="H66" s="77"/>
       <c r="I66" s="77"/>
       <c r="J66" s="25" t="s">
@@ -32388,7 +36503,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="192"/>
+      <c r="G67" s="195"/>
       <c r="H67" s="78"/>
       <c r="I67" s="78"/>
       <c r="J67" s="26" t="s">
@@ -32780,15 +36895,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="193">
+      <c r="P1" s="196">
         <v>46056</v>
       </c>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
-      <c r="V1" s="195"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
+      <c r="V1" s="198"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -32811,60 +36926,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="187" t="s">
+      <c r="B4" s="190" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="196" t="s">
+      <c r="C4" s="199" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="206" t="s">
+      <c r="D4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="197" t="s">
+      <c r="E4" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="198"/>
-      <c r="G4" s="199" t="s">
+      <c r="F4" s="201"/>
+      <c r="G4" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="207" t="s">
+      <c r="H4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="201" t="s">
+      <c r="I4" s="204" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="207" t="s">
+      <c r="J4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="203" t="s">
+      <c r="L4" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="204"/>
-      <c r="N4" s="204"/>
-      <c r="O4" s="204"/>
-      <c r="P4" s="204"/>
-      <c r="Q4" s="204"/>
-      <c r="R4" s="204"/>
-      <c r="S4" s="204"/>
-      <c r="T4" s="204"/>
-      <c r="U4" s="204"/>
-      <c r="V4" s="205"/>
+      <c r="M4" s="207"/>
+      <c r="N4" s="207"/>
+      <c r="O4" s="207"/>
+      <c r="P4" s="207"/>
+      <c r="Q4" s="207"/>
+      <c r="R4" s="207"/>
+      <c r="S4" s="207"/>
+      <c r="T4" s="207"/>
+      <c r="U4" s="207"/>
+      <c r="V4" s="208"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53"/>
-      <c r="B5" s="187"/>
-      <c r="C5" s="196"/>
-      <c r="D5" s="206"/>
+      <c r="B5" s="190"/>
+      <c r="C5" s="199"/>
+      <c r="D5" s="209"/>
       <c r="E5" s="52" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="134" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="200"/>
-      <c r="H5" s="208"/>
-      <c r="I5" s="202"/>
-      <c r="J5" s="208"/>
+      <c r="G5" s="203"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="205"/>
+      <c r="J5" s="211"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -35826,7 +39941,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="188" t="s">
+      <c r="G62" s="191" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="74"/>
@@ -35844,7 +39959,7 @@
       <c r="S62" s="35"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="189"/>
+      <c r="G63" s="192"/>
       <c r="H63" s="75"/>
       <c r="I63" s="75"/>
       <c r="J63" s="25" t="s">
@@ -35860,7 +39975,7 @@
       <c r="S63" s="38"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="190"/>
+      <c r="G64" s="193"/>
       <c r="H64" s="76"/>
       <c r="I64" s="76"/>
       <c r="J64" s="25" t="s">
@@ -35876,7 +39991,7 @@
       <c r="S64" s="41"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="191" t="s">
+      <c r="G65" s="194" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="77"/>
@@ -35894,7 +40009,7 @@
       <c r="S65" s="41"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="191"/>
+      <c r="G66" s="194"/>
       <c r="H66" s="77"/>
       <c r="I66" s="77"/>
       <c r="J66" s="25" t="s">
@@ -35910,7 +40025,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="192"/>
+      <c r="G67" s="195"/>
       <c r="H67" s="78"/>
       <c r="I67" s="78"/>
       <c r="J67" s="26" t="s">
@@ -36302,15 +40417,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="193">
+      <c r="P1" s="196">
         <v>46057</v>
       </c>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
-      <c r="V1" s="195"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
+      <c r="V1" s="198"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -36333,60 +40448,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="187" t="s">
+      <c r="B4" s="190" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="196" t="s">
+      <c r="C4" s="199" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="206" t="s">
+      <c r="D4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="197" t="s">
+      <c r="E4" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="198"/>
-      <c r="G4" s="199" t="s">
+      <c r="F4" s="201"/>
+      <c r="G4" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="207" t="s">
+      <c r="H4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="201" t="s">
+      <c r="I4" s="204" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="207" t="s">
+      <c r="J4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="203" t="s">
+      <c r="L4" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="204"/>
-      <c r="N4" s="204"/>
-      <c r="O4" s="204"/>
-      <c r="P4" s="204"/>
-      <c r="Q4" s="204"/>
-      <c r="R4" s="204"/>
-      <c r="S4" s="204"/>
-      <c r="T4" s="204"/>
-      <c r="U4" s="204"/>
-      <c r="V4" s="205"/>
+      <c r="M4" s="207"/>
+      <c r="N4" s="207"/>
+      <c r="O4" s="207"/>
+      <c r="P4" s="207"/>
+      <c r="Q4" s="207"/>
+      <c r="R4" s="207"/>
+      <c r="S4" s="207"/>
+      <c r="T4" s="207"/>
+      <c r="U4" s="207"/>
+      <c r="V4" s="208"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53"/>
-      <c r="B5" s="187"/>
-      <c r="C5" s="196"/>
-      <c r="D5" s="206"/>
+      <c r="B5" s="190"/>
+      <c r="C5" s="199"/>
+      <c r="D5" s="209"/>
       <c r="E5" s="52" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="137" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="200"/>
-      <c r="H5" s="208"/>
-      <c r="I5" s="202"/>
-      <c r="J5" s="208"/>
+      <c r="G5" s="203"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="205"/>
+      <c r="J5" s="211"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -39324,7 +43439,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="188" t="s">
+      <c r="G62" s="191" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="74"/>
@@ -39342,7 +43457,7 @@
       <c r="S62" s="35"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="189"/>
+      <c r="G63" s="192"/>
       <c r="H63" s="75"/>
       <c r="I63" s="75"/>
       <c r="J63" s="25" t="s">
@@ -39358,7 +43473,7 @@
       <c r="S63" s="38"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="190"/>
+      <c r="G64" s="193"/>
       <c r="H64" s="76"/>
       <c r="I64" s="76"/>
       <c r="J64" s="25" t="s">
@@ -39374,7 +43489,7 @@
       <c r="S64" s="41"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="191" t="s">
+      <c r="G65" s="194" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="77"/>
@@ -39392,7 +43507,7 @@
       <c r="S65" s="41"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="191"/>
+      <c r="G66" s="194"/>
       <c r="H66" s="77"/>
       <c r="I66" s="77"/>
       <c r="J66" s="25" t="s">
@@ -39408,7 +43523,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="192"/>
+      <c r="G67" s="195"/>
       <c r="H67" s="78"/>
       <c r="I67" s="78"/>
       <c r="J67" s="26" t="s">
@@ -39800,15 +43915,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="193">
+      <c r="P1" s="196">
         <v>46058</v>
       </c>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
-      <c r="V1" s="195"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
+      <c r="V1" s="198"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -39831,60 +43946,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="187" t="s">
+      <c r="B4" s="190" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="196" t="s">
+      <c r="C4" s="199" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="206" t="s">
+      <c r="D4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="197" t="s">
+      <c r="E4" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="198"/>
-      <c r="G4" s="199" t="s">
+      <c r="F4" s="201"/>
+      <c r="G4" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="207" t="s">
+      <c r="H4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="201" t="s">
+      <c r="I4" s="204" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="207" t="s">
+      <c r="J4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="203" t="s">
+      <c r="L4" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="204"/>
-      <c r="N4" s="204"/>
-      <c r="O4" s="204"/>
-      <c r="P4" s="204"/>
-      <c r="Q4" s="204"/>
-      <c r="R4" s="204"/>
-      <c r="S4" s="204"/>
-      <c r="T4" s="204"/>
-      <c r="U4" s="204"/>
-      <c r="V4" s="205"/>
+      <c r="M4" s="207"/>
+      <c r="N4" s="207"/>
+      <c r="O4" s="207"/>
+      <c r="P4" s="207"/>
+      <c r="Q4" s="207"/>
+      <c r="R4" s="207"/>
+      <c r="S4" s="207"/>
+      <c r="T4" s="207"/>
+      <c r="U4" s="207"/>
+      <c r="V4" s="208"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53"/>
-      <c r="B5" s="187"/>
-      <c r="C5" s="196"/>
-      <c r="D5" s="206"/>
+      <c r="B5" s="190"/>
+      <c r="C5" s="199"/>
+      <c r="D5" s="209"/>
       <c r="E5" s="52" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="137" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="200"/>
-      <c r="H5" s="208"/>
-      <c r="I5" s="202"/>
-      <c r="J5" s="208"/>
+      <c r="G5" s="203"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="205"/>
+      <c r="J5" s="211"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -42845,7 +46960,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="188" t="s">
+      <c r="G62" s="191" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="74"/>
@@ -42863,7 +46978,7 @@
       <c r="S62" s="35"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="189"/>
+      <c r="G63" s="192"/>
       <c r="H63" s="75"/>
       <c r="I63" s="75"/>
       <c r="J63" s="25" t="s">
@@ -42879,7 +46994,7 @@
       <c r="S63" s="38"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="190"/>
+      <c r="G64" s="193"/>
       <c r="H64" s="76"/>
       <c r="I64" s="76"/>
       <c r="J64" s="25" t="s">
@@ -42895,7 +47010,7 @@
       <c r="S64" s="41"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="191" t="s">
+      <c r="G65" s="194" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="77"/>
@@ -42913,7 +47028,7 @@
       <c r="S65" s="41"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="191"/>
+      <c r="G66" s="194"/>
       <c r="H66" s="77"/>
       <c r="I66" s="77"/>
       <c r="J66" s="25" t="s">
@@ -42929,7 +47044,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="192"/>
+      <c r="G67" s="195"/>
       <c r="H67" s="78"/>
       <c r="I67" s="78"/>
       <c r="J67" s="26" t="s">
@@ -43321,15 +47436,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="193">
+      <c r="P1" s="196">
         <v>46058</v>
       </c>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
-      <c r="V1" s="195"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
+      <c r="V1" s="198"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -43352,60 +47467,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="187" t="s">
+      <c r="B4" s="190" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="196" t="s">
+      <c r="C4" s="199" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="206" t="s">
+      <c r="D4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="197" t="s">
+      <c r="E4" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="198"/>
-      <c r="G4" s="199" t="s">
+      <c r="F4" s="201"/>
+      <c r="G4" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="207" t="s">
+      <c r="H4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="201" t="s">
+      <c r="I4" s="204" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="207" t="s">
+      <c r="J4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="203" t="s">
+      <c r="L4" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="204"/>
-      <c r="N4" s="204"/>
-      <c r="O4" s="204"/>
-      <c r="P4" s="204"/>
-      <c r="Q4" s="204"/>
-      <c r="R4" s="204"/>
-      <c r="S4" s="204"/>
-      <c r="T4" s="204"/>
-      <c r="U4" s="204"/>
-      <c r="V4" s="205"/>
+      <c r="M4" s="207"/>
+      <c r="N4" s="207"/>
+      <c r="O4" s="207"/>
+      <c r="P4" s="207"/>
+      <c r="Q4" s="207"/>
+      <c r="R4" s="207"/>
+      <c r="S4" s="207"/>
+      <c r="T4" s="207"/>
+      <c r="U4" s="207"/>
+      <c r="V4" s="208"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53"/>
-      <c r="B5" s="187"/>
-      <c r="C5" s="196"/>
-      <c r="D5" s="206"/>
+      <c r="B5" s="190"/>
+      <c r="C5" s="199"/>
+      <c r="D5" s="209"/>
       <c r="E5" s="52" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="200"/>
-      <c r="H5" s="208"/>
-      <c r="I5" s="202"/>
-      <c r="J5" s="208"/>
+      <c r="G5" s="203"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="205"/>
+      <c r="J5" s="211"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -46214,7 +50329,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="188" t="s">
+      <c r="G62" s="191" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="74"/>
@@ -46232,7 +50347,7 @@
       <c r="S62" s="35"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="189"/>
+      <c r="G63" s="192"/>
       <c r="H63" s="75"/>
       <c r="I63" s="75"/>
       <c r="J63" s="25" t="s">
@@ -46248,7 +50363,7 @@
       <c r="S63" s="38"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="190"/>
+      <c r="G64" s="193"/>
       <c r="H64" s="76"/>
       <c r="I64" s="76"/>
       <c r="J64" s="25" t="s">
@@ -46264,7 +50379,7 @@
       <c r="S64" s="41"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="191" t="s">
+      <c r="G65" s="194" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="77"/>
@@ -46282,7 +50397,7 @@
       <c r="S65" s="41"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="191"/>
+      <c r="G66" s="194"/>
       <c r="H66" s="77"/>
       <c r="I66" s="77"/>
       <c r="J66" s="25" t="s">
@@ -46298,7 +50413,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="192"/>
+      <c r="G67" s="195"/>
       <c r="H67" s="78"/>
       <c r="I67" s="78"/>
       <c r="J67" s="26" t="s">
@@ -46690,15 +50805,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="193">
+      <c r="P1" s="196">
         <v>46059</v>
       </c>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
-      <c r="V1" s="195"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
+      <c r="V1" s="198"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -46721,60 +50836,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="187" t="s">
+      <c r="B4" s="190" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="196" t="s">
+      <c r="C4" s="199" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="206" t="s">
+      <c r="D4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="197" t="s">
+      <c r="E4" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="198"/>
-      <c r="G4" s="199" t="s">
+      <c r="F4" s="201"/>
+      <c r="G4" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="207" t="s">
+      <c r="H4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="201" t="s">
+      <c r="I4" s="204" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="207" t="s">
+      <c r="J4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="203" t="s">
+      <c r="L4" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="204"/>
-      <c r="N4" s="204"/>
-      <c r="O4" s="204"/>
-      <c r="P4" s="204"/>
-      <c r="Q4" s="204"/>
-      <c r="R4" s="204"/>
-      <c r="S4" s="204"/>
-      <c r="T4" s="204"/>
-      <c r="U4" s="204"/>
-      <c r="V4" s="205"/>
+      <c r="M4" s="207"/>
+      <c r="N4" s="207"/>
+      <c r="O4" s="207"/>
+      <c r="P4" s="207"/>
+      <c r="Q4" s="207"/>
+      <c r="R4" s="207"/>
+      <c r="S4" s="207"/>
+      <c r="T4" s="207"/>
+      <c r="U4" s="207"/>
+      <c r="V4" s="208"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53"/>
-      <c r="B5" s="187"/>
-      <c r="C5" s="196"/>
-      <c r="D5" s="206"/>
+      <c r="B5" s="190"/>
+      <c r="C5" s="199"/>
+      <c r="D5" s="209"/>
       <c r="E5" s="52" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="140" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="200"/>
-      <c r="H5" s="208"/>
-      <c r="I5" s="202"/>
-      <c r="J5" s="208"/>
+      <c r="G5" s="203"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="205"/>
+      <c r="J5" s="211"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -49740,7 +53855,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="188" t="s">
+      <c r="G62" s="191" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="74"/>
@@ -49758,7 +53873,7 @@
       <c r="S62" s="35"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="189"/>
+      <c r="G63" s="192"/>
       <c r="H63" s="75"/>
       <c r="I63" s="75"/>
       <c r="J63" s="25" t="s">
@@ -49774,7 +53889,7 @@
       <c r="S63" s="38"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="190"/>
+      <c r="G64" s="193"/>
       <c r="H64" s="76"/>
       <c r="I64" s="76"/>
       <c r="J64" s="25" t="s">
@@ -49790,7 +53905,7 @@
       <c r="S64" s="41"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="191" t="s">
+      <c r="G65" s="194" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="77"/>
@@ -49808,7 +53923,7 @@
       <c r="S65" s="41"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="191"/>
+      <c r="G66" s="194"/>
       <c r="H66" s="77"/>
       <c r="I66" s="77"/>
       <c r="J66" s="25" t="s">
@@ -49824,7 +53939,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="192"/>
+      <c r="G67" s="195"/>
       <c r="H67" s="78"/>
       <c r="I67" s="78"/>
       <c r="J67" s="26" t="s">
@@ -50216,15 +54331,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="193">
+      <c r="P1" s="196">
         <v>46060</v>
       </c>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
-      <c r="V1" s="195"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
+      <c r="V1" s="198"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -50247,60 +54362,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="187" t="s">
+      <c r="B4" s="190" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="196" t="s">
+      <c r="C4" s="199" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="206" t="s">
+      <c r="D4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="197" t="s">
+      <c r="E4" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="198"/>
-      <c r="G4" s="199" t="s">
+      <c r="F4" s="201"/>
+      <c r="G4" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="207" t="s">
+      <c r="H4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="201" t="s">
+      <c r="I4" s="204" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="207" t="s">
+      <c r="J4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="203" t="s">
+      <c r="L4" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="204"/>
-      <c r="N4" s="204"/>
-      <c r="O4" s="204"/>
-      <c r="P4" s="204"/>
-      <c r="Q4" s="204"/>
-      <c r="R4" s="204"/>
-      <c r="S4" s="204"/>
-      <c r="T4" s="204"/>
-      <c r="U4" s="204"/>
-      <c r="V4" s="205"/>
+      <c r="M4" s="207"/>
+      <c r="N4" s="207"/>
+      <c r="O4" s="207"/>
+      <c r="P4" s="207"/>
+      <c r="Q4" s="207"/>
+      <c r="R4" s="207"/>
+      <c r="S4" s="207"/>
+      <c r="T4" s="207"/>
+      <c r="U4" s="207"/>
+      <c r="V4" s="208"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53"/>
-      <c r="B5" s="187"/>
-      <c r="C5" s="196"/>
-      <c r="D5" s="206"/>
+      <c r="B5" s="190"/>
+      <c r="C5" s="199"/>
+      <c r="D5" s="209"/>
       <c r="E5" s="52" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="200"/>
-      <c r="H5" s="208"/>
-      <c r="I5" s="202"/>
-      <c r="J5" s="208"/>
+      <c r="G5" s="203"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="205"/>
+      <c r="J5" s="211"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -53234,7 +57349,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="188" t="s">
+      <c r="G62" s="191" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="74"/>
@@ -53252,7 +57367,7 @@
       <c r="S62" s="35"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="189"/>
+      <c r="G63" s="192"/>
       <c r="H63" s="75"/>
       <c r="I63" s="75"/>
       <c r="J63" s="25" t="s">
@@ -53268,7 +57383,7 @@
       <c r="S63" s="38"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="190"/>
+      <c r="G64" s="193"/>
       <c r="H64" s="76"/>
       <c r="I64" s="76"/>
       <c r="J64" s="25" t="s">
@@ -53284,7 +57399,7 @@
       <c r="S64" s="41"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="191" t="s">
+      <c r="G65" s="194" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="77"/>
@@ -53302,7 +57417,7 @@
       <c r="S65" s="41"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="191"/>
+      <c r="G66" s="194"/>
       <c r="H66" s="77"/>
       <c r="I66" s="77"/>
       <c r="J66" s="25" t="s">
@@ -53318,7 +57433,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="192"/>
+      <c r="G67" s="195"/>
       <c r="H67" s="78"/>
       <c r="I67" s="78"/>
       <c r="J67" s="26" t="s">
@@ -53710,15 +57825,15 @@
       <c r="N1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="193">
+      <c r="P1" s="196">
         <v>46062</v>
       </c>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
-      <c r="V1" s="195"/>
+      <c r="Q1" s="197"/>
+      <c r="R1" s="197"/>
+      <c r="S1" s="197"/>
+      <c r="T1" s="197"/>
+      <c r="U1" s="197"/>
+      <c r="V1" s="198"/>
     </row>
     <row r="2" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
@@ -53741,60 +57856,60 @@
     <row r="3" spans="1:58" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:58" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="53"/>
-      <c r="B4" s="187" t="s">
+      <c r="B4" s="190" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="196" t="s">
+      <c r="C4" s="199" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="206" t="s">
+      <c r="D4" s="209" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="197" t="s">
+      <c r="E4" s="200" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="198"/>
-      <c r="G4" s="199" t="s">
+      <c r="F4" s="201"/>
+      <c r="G4" s="202" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="207" t="s">
+      <c r="H4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="I4" s="201" t="s">
+      <c r="I4" s="204" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="207" t="s">
+      <c r="J4" s="210" t="s">
         <v>75</v>
       </c>
-      <c r="L4" s="203" t="s">
+      <c r="L4" s="206" t="s">
         <v>7</v>
       </c>
-      <c r="M4" s="204"/>
-      <c r="N4" s="204"/>
-      <c r="O4" s="204"/>
-      <c r="P4" s="204"/>
-      <c r="Q4" s="204"/>
-      <c r="R4" s="204"/>
-      <c r="S4" s="204"/>
-      <c r="T4" s="204"/>
-      <c r="U4" s="204"/>
-      <c r="V4" s="205"/>
+      <c r="M4" s="207"/>
+      <c r="N4" s="207"/>
+      <c r="O4" s="207"/>
+      <c r="P4" s="207"/>
+      <c r="Q4" s="207"/>
+      <c r="R4" s="207"/>
+      <c r="S4" s="207"/>
+      <c r="T4" s="207"/>
+      <c r="U4" s="207"/>
+      <c r="V4" s="208"/>
     </row>
     <row r="5" spans="1:58" s="3" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="53"/>
-      <c r="B5" s="187"/>
-      <c r="C5" s="196"/>
-      <c r="D5" s="206"/>
+      <c r="B5" s="190"/>
+      <c r="C5" s="199"/>
+      <c r="D5" s="209"/>
       <c r="E5" s="52" t="s">
         <v>8</v>
       </c>
       <c r="F5" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="200"/>
-      <c r="H5" s="208"/>
-      <c r="I5" s="202"/>
-      <c r="J5" s="208"/>
+      <c r="G5" s="203"/>
+      <c r="H5" s="211"/>
+      <c r="I5" s="205"/>
+      <c r="J5" s="211"/>
       <c r="L5" s="4" t="s">
         <v>10</v>
       </c>
@@ -56725,7 +60840,7 @@
     </row>
     <row r="61" spans="1:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="62" spans="1:22" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G62" s="188" t="s">
+      <c r="G62" s="191" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="74"/>
@@ -56743,7 +60858,7 @@
       <c r="S62" s="35"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G63" s="189"/>
+      <c r="G63" s="192"/>
       <c r="H63" s="75"/>
       <c r="I63" s="75"/>
       <c r="J63" s="25" t="s">
@@ -56759,7 +60874,7 @@
       <c r="S63" s="38"/>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G64" s="190"/>
+      <c r="G64" s="193"/>
       <c r="H64" s="76"/>
       <c r="I64" s="76"/>
       <c r="J64" s="25" t="s">
@@ -56775,7 +60890,7 @@
       <c r="S64" s="41"/>
     </row>
     <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G65" s="191" t="s">
+      <c r="G65" s="194" t="s">
         <v>64</v>
       </c>
       <c r="H65" s="77"/>
@@ -56793,7 +60908,7 @@
       <c r="S65" s="41"/>
     </row>
     <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="G66" s="191"/>
+      <c r="G66" s="194"/>
       <c r="H66" s="77"/>
       <c r="I66" s="77"/>
       <c r="J66" s="25" t="s">
@@ -56809,7 +60924,7 @@
       <c r="S66" s="38"/>
     </row>
     <row r="67" spans="2:22" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G67" s="192"/>
+      <c r="G67" s="195"/>
       <c r="H67" s="78"/>
       <c r="I67" s="78"/>
       <c r="J67" s="26" t="s">
